--- a/data/Wine Recommended Order.xlsx
+++ b/data/Wine Recommended Order.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Transfer Plan" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Wine Recommended Order.xlsx
+++ b/data/Wine Recommended Order.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Transfer Plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Wine Recommended Order.xlsx
+++ b/data/Wine Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Wine Recommended Order.xlsx
+++ b/data/Wine Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Wine Recommended Order.xlsx
+++ b/data/Wine Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Wine Recommended Order.xlsx
+++ b/data/Wine Recommended Order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Transfer Plan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,55 +452,65 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>LY wk</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Gross Need</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Buy Units</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Buy Cases</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Net Buy $</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>GM %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Discount %</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Deal Terms</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Buy Month</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
@@ -534,29 +544,35 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
+        <v>-38</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I2" t="n">
         <v>229</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>240</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>10</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>2.7</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>649</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>51</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -586,29 +602,35 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>-40</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
         <v>26</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>24</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>2</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>100</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin over 95% - check retail</t>
         </is>
@@ -642,33 +664,39 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
+        <v>-35</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I4" t="n">
         <v>16</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>24</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>3.93</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>94</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>44</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: Feb, May, Aug)</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -697,7 +725,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -706,20 +734,26 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>100</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin over 95% - check retail</t>
         </is>
@@ -748,7 +782,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -757,20 +791,26 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
         <v>4.62</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>5</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>71</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -795,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -804,20 +844,26 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
         <v>7.97</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>8</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>56</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -842,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -851,20 +897,26 @@
         <v>1</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
         <v>19</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>19</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>34</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -889,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -898,20 +950,26 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
         <v>16</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>16</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>24</v>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -936,29 +994,35 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
         <v>6.26</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>6</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>43</v>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -988,29 +1052,35 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
+        <v>-52</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>15</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>12</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>2.66</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>32</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>-7</v>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
         <is>
           <t>Margin looks off - check retail/cost</t>
         </is>
@@ -1044,29 +1114,35 @@
         <v>1.3</v>
       </c>
       <c r="G12" t="n">
+        <v>-36</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>51</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>24</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>24</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>100</v>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin over 95% - check retail</t>
         </is>
@@ -1100,29 +1176,35 @@
         <v>1.4</v>
       </c>
       <c r="G13" t="n">
+        <v>17</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I13" t="n">
         <v>8</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>6</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>7.86</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>47</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>37</v>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1152,29 +1234,35 @@
         <v>1.6</v>
       </c>
       <c r="G14" t="n">
+        <v>-24</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I14" t="n">
         <v>14</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>20</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>4.35</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>87</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>46</v>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1204,29 +1292,35 @@
         <v>2</v>
       </c>
       <c r="G15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I15" t="n">
         <v>11</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
         <v>12</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>6</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>72</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>40</v>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1256,29 +1350,35 @@
         <v>2.4</v>
       </c>
       <c r="G16" t="n">
+        <v>18</v>
+      </c>
+      <c r="H16" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="I16" t="n">
         <v>181</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>30</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>156</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>13</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>8.369999999999999</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>1305</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>30</v>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1308,29 +1408,35 @@
         <v>2.4</v>
       </c>
       <c r="G17" t="n">
+        <v>19</v>
+      </c>
+      <c r="H17" t="n">
+        <v>70</v>
+      </c>
+      <c r="I17" t="n">
         <v>163</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>45</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>120</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>10</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>4.37</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>525</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>33</v>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1360,29 +1466,35 @@
         <v>2.4</v>
       </c>
       <c r="G18" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I18" t="n">
         <v>12</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>12</v>
+      </c>
+      <c r="L18" t="n">
         <v>2</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>6.95</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>83</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>50</v>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1412,29 +1524,35 @@
         <v>2.4</v>
       </c>
       <c r="G19" t="n">
+        <v>170</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>7</v>
       </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>12</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>18</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>216</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>40</v>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1464,29 +1582,35 @@
         <v>2.7</v>
       </c>
       <c r="G20" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="I20" t="n">
         <v>12</v>
       </c>
       <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>12</v>
+      </c>
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>12.73</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>153</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>27</v>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1516,29 +1640,35 @@
         <v>2.8</v>
       </c>
       <c r="G21" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="I21" t="n">
         <v>24</v>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>24</v>
+      </c>
+      <c r="L21" t="n">
         <v>4</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>7.72</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>185</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>38</v>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1568,29 +1698,35 @@
         <v>3.1</v>
       </c>
       <c r="G22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I22" t="n">
         <v>26</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>11</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>12</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>6.67</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>80</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>47</v>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1620,33 +1756,39 @@
         <v>3.1</v>
       </c>
       <c r="G23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>66</v>
+      </c>
+      <c r="I23" t="n">
         <v>94</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>22</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>72</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>12</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>20.34</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>1465</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>-2</v>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
         <is>
           <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov)</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>Margin looks off - check retail/cost</t>
         </is>
@@ -1680,29 +1822,35 @@
         <v>3.2</v>
       </c>
       <c r="G24" t="n">
+        <v>14</v>
+      </c>
+      <c r="H24" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="I24" t="n">
         <v>94</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>33</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>60</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>5</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>8.76</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>525</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>27</v>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1732,33 +1880,39 @@
         <v>3.3</v>
       </c>
       <c r="G25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="I25" t="n">
         <v>99</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>29</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>72</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>12</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>13.09</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>942</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>35</v>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
         <is>
           <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov)</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1788,29 +1942,35 @@
         <v>3.3</v>
       </c>
       <c r="G26" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="I26" t="n">
         <v>122</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>77</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>48</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>8</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>4.14</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>199</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>68</v>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1840,29 +2000,35 @@
         <v>3.4</v>
       </c>
       <c r="G27" t="n">
+        <v>7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>20</v>
+      </c>
+      <c r="I27" t="n">
         <v>78</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>50</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>24</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>10.29</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>247</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>26</v>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1892,33 +2058,39 @@
         <v>3.5</v>
       </c>
       <c r="G28" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H28" t="n">
+        <v>89</v>
+      </c>
+      <c r="I28" t="n">
         <v>86</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>34</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>54</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>9</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>14.01</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>756</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>30</v>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
         <is>
           <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov)</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1948,29 +2120,35 @@
         <v>3.5</v>
       </c>
       <c r="G29" t="n">
+        <v>38</v>
+      </c>
+      <c r="H29" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="I29" t="n">
         <v>86</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>35</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>48</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>4</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>7.92</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>380</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>43</v>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2000,29 +2178,35 @@
         <v>3.5</v>
       </c>
       <c r="G30" t="n">
+        <v>9</v>
+      </c>
+      <c r="H30" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="I30" t="n">
         <v>92</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>59</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>36</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>3</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>296</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>32</v>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2052,29 +2236,35 @@
         <v>3.5</v>
       </c>
       <c r="G31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="I31" t="n">
         <v>77</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>48</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>20</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>2.82</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>56</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>60</v>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2104,29 +2294,35 @@
         <v>3.5</v>
       </c>
       <c r="G32" t="n">
+        <v>16</v>
+      </c>
+      <c r="H32" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I32" t="n">
         <v>37</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>24</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>12</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>2</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>5.77</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>69</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>56</v>
       </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2156,29 +2352,35 @@
         <v>3.6</v>
       </c>
       <c r="G33" t="n">
+        <v>44</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I33" t="n">
         <v>13</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>4</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>12</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>2</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>11.33</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>136</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>43</v>
       </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2208,29 +2410,35 @@
         <v>3.7</v>
       </c>
       <c r="G34" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H34" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="I34" t="n">
         <v>98</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>75</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>24</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>2</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>4.4</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>106</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>62</v>
       </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2260,29 +2468,35 @@
         <v>3.8</v>
       </c>
       <c r="G35" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H35" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="I35" t="n">
         <v>139</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>122</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>12</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>5.93</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>71</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>60</v>
       </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2312,29 +2526,35 @@
         <v>3.8</v>
       </c>
       <c r="G36" t="n">
+        <v>27</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
         <v>13</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>4</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>9</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>14.67</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>132</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>27</v>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2347,7 +2567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2383,55 +2603,65 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>LY wk</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Gross Need</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Buy Units</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Buy Cases</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Net Buy $</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>GM %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Discount %</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Deal Terms</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Buy Month</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
@@ -2465,29 +2695,35 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
+        <v>-40</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>26</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>24</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>2</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>100</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin over 95% - check retail</t>
         </is>
@@ -2521,33 +2757,39 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>-35</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I3" t="n">
         <v>16</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>24</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>3.93</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>94</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>44</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>Off-month, buy anyway - urgent (deal: Feb, May, Aug)</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>Off buy-month - confirm timing</t>
         </is>
@@ -2576,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -2585,20 +2827,26 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>100</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin over 95% - check retail</t>
         </is>
@@ -2632,29 +2880,35 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
+        <v>-52</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>15</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>12</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>2.66</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>32</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>-7</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
         <is>
           <t>Margin looks off - check retail/cost</t>
         </is>
@@ -2688,29 +2942,35 @@
         <v>1.3</v>
       </c>
       <c r="G6" t="n">
+        <v>-36</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>51</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>24</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>24</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>100</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
         <is>
           <t>No cost data - verify price; Margin over 95% - check retail</t>
         </is>
@@ -2744,33 +3004,39 @@
         <v>3.1</v>
       </c>
       <c r="G7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>66</v>
+      </c>
+      <c r="I7" t="n">
         <v>94</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>22</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>72</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>12</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>20.34</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>1465</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>-2</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov)</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>Margin looks off - check retail/cost</t>
         </is>
@@ -2787,7 +3053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2823,45 +3089,55 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>LY wk</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Gross Need</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Transfer</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Buy Units</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Buy Cases</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Unit Cost</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Net Buy $</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>GM %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Discount %</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Deal Terms</t>
         </is>
@@ -2895,27 +3171,33 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
+        <v>38</v>
+      </c>
+      <c r="H2" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="I2" t="n">
         <v>118</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>59</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>60</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>5</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>6</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>360</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>40</v>
       </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2940,27 +3222,33 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>-25</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>10</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>48</v>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2990,27 +3278,33 @@
         <v>3.2</v>
       </c>
       <c r="G4" t="n">
+        <v>65</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I4" t="n">
         <v>99</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>52</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>48</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>4</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>17.33</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>832</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>38</v>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3040,27 +3334,33 @@
         <v>2.7</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I5" t="n">
         <v>54</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>56</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>14</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>14</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>784</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>33</v>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3090,27 +3390,33 @@
         <v>3.7</v>
       </c>
       <c r="G6" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I6" t="n">
         <v>30</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>10</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>20</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>5</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>14</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>280</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>33</v>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3140,27 +3446,33 @@
         <v>2.2</v>
       </c>
       <c r="G7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I7" t="n">
         <v>64</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>60</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>15</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>9.42</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>565</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>48</v>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3185,27 +3497,33 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
         <v>28.67</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>29</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>25</v>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Wine Recommended Order.xlsx
+++ b/data/Wine Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/Wine Recommended Order.xlsx
+++ b/data/Wine Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S119"/>
+  <dimension ref="A1:S118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1995,25 +1995,21 @@
         <v>18</v>
       </c>
       <c r="K27" t="n">
-        <v>336</v>
+        <v>276</v>
       </c>
       <c r="L27" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="M27" t="n">
         <v>8.279999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>2782</v>
+        <v>2285</v>
       </c>
       <c r="O27" t="n">
         <v>31</v>
       </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
     </row>
@@ -5078,21 +5074,25 @@
         <v>85</v>
       </c>
       <c r="K79" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L79" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M79" t="n">
         <v>7.08</v>
       </c>
       <c r="N79" t="n">
-        <v>170</v>
+        <v>425</v>
       </c>
       <c r="O79" t="n">
         <v>53</v>
       </c>
-      <c r="Q79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
     </row>
@@ -5463,83 +5463,79 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Black Box Pinot Noir 3L Box</t>
+          <t>Raza Vinho Verde 750ml</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>081434710017</t>
+          <t>5600379041236</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>The Wine Company</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>193</v>
+        <v>126</v>
       </c>
       <c r="F86" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="G86" t="n">
-        <v>-15</v>
+        <v>80</v>
       </c>
       <c r="H86" t="n">
-        <v>43.8</v>
+        <v>14.2</v>
       </c>
       <c r="I86" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="J86" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="K86" t="n">
-        <v>132</v>
+        <v>12</v>
       </c>
       <c r="L86" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>4.72</v>
+        <v>5.19</v>
       </c>
       <c r="N86" t="n">
-        <v>623</v>
+        <v>62</v>
       </c>
       <c r="O86" t="n">
-        <v>76</v>
-      </c>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($623 to next deal) - confirm</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Black Box Deep Dark Cabernet 3L Box</t>
+          <t>Black Box Pinot Noir 3L Box</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>085000034552</t>
+          <t>081434710017</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5548,37 +5544,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>90</v>
+        <v>193</v>
       </c>
       <c r="F87" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="G87" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="H87" t="n">
-        <v>15</v>
+        <v>43.8</v>
       </c>
       <c r="I87" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K87" t="n">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="L87" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="M87" t="n">
-        <v>16.03</v>
+        <v>4.72</v>
       </c>
       <c r="N87" t="n">
-        <v>866</v>
+        <v>623</v>
       </c>
       <c r="O87" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
@@ -5588,24 +5584,24 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($866 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($623 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Dark Horse Pinot Grigio 750ml</t>
+          <t>Black Box Deep Dark Cabernet 3L Box</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>085000025284</t>
+          <t>085000034552</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5614,37 +5610,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="F88" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="G88" t="n">
-        <v>12</v>
+        <v>-16</v>
       </c>
       <c r="H88" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="I88" t="n">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="J88" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="L88" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M88" t="n">
-        <v>5.05</v>
+        <v>16.03</v>
       </c>
       <c r="N88" t="n">
-        <v>364</v>
+        <v>866</v>
       </c>
       <c r="O88" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
@@ -5654,24 +5650,24 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($364 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($866 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Black Box Red Elegance 3L Box</t>
+          <t>Dark Horse Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>081434700193</t>
+          <t>085000025284</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5680,37 +5676,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="F89" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="G89" t="n">
-        <v>-3</v>
+        <v>12</v>
       </c>
       <c r="H89" t="n">
-        <v>21.5</v>
+        <v>24</v>
       </c>
       <c r="I89" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="J89" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="K89" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L89" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M89" t="n">
-        <v>15.44</v>
+        <v>5.05</v>
       </c>
       <c r="N89" t="n">
-        <v>741</v>
+        <v>364</v>
       </c>
       <c r="O89" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
@@ -5720,90 +5716,90 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($741 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($364 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Pacific Rim Sweet Riesling 750ml</t>
+          <t>Black Box Red Elegance 3L Box</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>899552102276</t>
+          <t>081434700193</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="F90" t="n">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="G90" t="n">
-        <v>19</v>
+        <v>-3</v>
       </c>
       <c r="H90" t="n">
-        <v>4.5</v>
+        <v>21.5</v>
       </c>
       <c r="I90" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="J90" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K90" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M90" t="n">
-        <v>5.1</v>
+        <v>15.44</v>
       </c>
       <c r="N90" t="n">
-        <v>61</v>
+        <v>741</v>
       </c>
       <c r="O90" t="n">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Feb, Jul, Aug, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($61 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($741 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Decoy Cabernet Sauvignon 750ml</t>
+          <t>Pacific Rim Sweet Riesling 750ml</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>669576019269</t>
+          <t>899552102276</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5812,22 +5808,22 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>181</v>
+        <v>31</v>
       </c>
       <c r="F91" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="G91" t="n">
-        <v>-7</v>
+        <v>19</v>
       </c>
       <c r="H91" t="n">
-        <v>23.8</v>
+        <v>4.5</v>
       </c>
       <c r="I91" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="J91" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K91" t="n">
         <v>12</v>
@@ -5836,64 +5832,64 @@
         <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>13.52</v>
+        <v>5.1</v>
       </c>
       <c r="N91" t="n">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="O91" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Jan, Feb, Jul, Aug, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($162 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($61 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Colle Corviano Cerasuolo Rose 750ml</t>
+          <t>Decoy Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>181856000892</t>
+          <t>669576019269</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Small Lot MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>114</v>
+        <v>181</v>
       </c>
       <c r="F92" t="n">
         <v>6.5</v>
       </c>
       <c r="G92" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="H92" t="n">
-        <v>11.2</v>
+        <v>23.8</v>
       </c>
       <c r="I92" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="J92" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K92" t="n">
         <v>12</v>
@@ -5902,64 +5898,64 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>6</v>
+        <v>13.52</v>
       </c>
       <c r="N92" t="n">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="O92" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, May, Jun, Jul, Aug) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($72 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($162 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Decoy Sauvignon Blanc 750ml</t>
+          <t>Colle Corviano Cerasuolo Rose 750ml</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>669576019214</t>
+          <t>181856000892</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Small Lot MN</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F93" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="G93" t="n">
-        <v>42</v>
+        <v>-9</v>
       </c>
       <c r="H93" t="n">
-        <v>16.2</v>
+        <v>11.2</v>
       </c>
       <c r="I93" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="J93" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="K93" t="n">
         <v>12</v>
@@ -5968,130 +5964,130 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>10.34</v>
+        <v>6</v>
       </c>
       <c r="N93" t="n">
-        <v>124</v>
+        <v>72</v>
       </c>
       <c r="O93" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Apr, May, Jun, Jul, Aug) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($124 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($72 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Bertrand Cote des Roses Rose 750ml</t>
+          <t>Decoy Sauvignon Blanc 750ml</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>812147020083</t>
+          <t>669576019214</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F94" t="n">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="G94" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="H94" t="n">
-        <v>17.5</v>
+        <v>16.2</v>
       </c>
       <c r="I94" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J94" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="K94" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>12.32</v>
+        <v>10.34</v>
       </c>
       <c r="N94" t="n">
-        <v>296</v>
+        <v>124</v>
       </c>
       <c r="O94" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($296 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($124 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Dark Horse Buttery Chardonnay 750ml</t>
+          <t>Bertrand Cote des Roses Rose 750ml</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>085000031223</t>
+          <t>812147020083</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="F95" t="n">
         <v>7.3</v>
       </c>
       <c r="G95" t="n">
-        <v>-6</v>
+        <v>17</v>
       </c>
       <c r="H95" t="n">
-        <v>6</v>
+        <v>17.5</v>
       </c>
       <c r="I95" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="J95" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="K95" t="n">
         <v>24</v>
@@ -6100,40 +6096,40 @@
         <v>2</v>
       </c>
       <c r="M95" t="n">
-        <v>5.59</v>
+        <v>12.32</v>
       </c>
       <c r="N95" t="n">
-        <v>134</v>
+        <v>296</v>
       </c>
       <c r="O95" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($134 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($296 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Black Box Malbec 3L Box</t>
+          <t>Dark Horse Buttery Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>082100738465</t>
+          <t>085000031223</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Malbec</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6142,37 +6138,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F96" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="G96" t="n">
-        <v>-18</v>
+        <v>-6</v>
       </c>
       <c r="H96" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="I96" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J96" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K96" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M96" t="n">
-        <v>13.89</v>
+        <v>5.59</v>
       </c>
       <c r="N96" t="n">
-        <v>250</v>
+        <v>134</v>
       </c>
       <c r="O96" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr">
@@ -6182,114 +6178,114 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($250 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($134 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Decoy Sonoma Chardonnay 750ml</t>
+          <t>Black Box Malbec 3L Box</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>669576019245</t>
+          <t>082100738465</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Malbec</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="F97" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="G97" t="n">
-        <v>42</v>
+        <v>-18</v>
       </c>
       <c r="H97" t="n">
-        <v>19.2</v>
+        <v>11.5</v>
       </c>
       <c r="I97" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J97" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K97" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M97" t="n">
-        <v>11.28</v>
+        <v>13.89</v>
       </c>
       <c r="N97" t="n">
-        <v>135</v>
+        <v>250</v>
       </c>
       <c r="O97" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($135 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($250 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Dark Horse Cabernet Sauvignon 750ml</t>
+          <t>Decoy Sonoma Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>085000020302</t>
+          <t>669576019245</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="F98" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="G98" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="H98" t="n">
-        <v>6.5</v>
+        <v>19.2</v>
       </c>
       <c r="I98" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K98" t="n">
         <v>12</v>
@@ -6298,40 +6294,40 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>4.85</v>
+        <v>11.28</v>
       </c>
       <c r="N98" t="n">
-        <v>58</v>
+        <v>135</v>
       </c>
       <c r="O98" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($58 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($135 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Dark Horse Sauvignon Blanc 750ml</t>
+          <t>Dark Horse Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>085000022924</t>
+          <t>085000020302</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6340,22 +6336,22 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="F99" t="n">
         <v>7.8</v>
       </c>
       <c r="G99" t="n">
-        <v>-5</v>
+        <v>29</v>
       </c>
       <c r="H99" t="n">
         <v>6.5</v>
       </c>
       <c r="I99" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J99" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K99" t="n">
         <v>12</v>
@@ -6364,13 +6360,13 @@
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>5.6</v>
+        <v>4.85</v>
       </c>
       <c r="N99" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="O99" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
@@ -6380,48 +6376,48 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($67 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($58 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Charles Smith Kung Fu Girl Riesling 750ml</t>
+          <t>Dark Horse Sauvignon Blanc 750ml</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>083120015048</t>
+          <t>085000022924</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="F100" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="G100" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H100" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I100" t="n">
+        <v>9</v>
+      </c>
+      <c r="J100" t="n">
         <v>6</v>
-      </c>
-      <c r="I100" t="n">
-        <v>15</v>
-      </c>
-      <c r="J100" t="n">
-        <v>14</v>
       </c>
       <c r="K100" t="n">
         <v>12</v>
@@ -6430,64 +6426,64 @@
         <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>7.52</v>
+        <v>5.6</v>
       </c>
       <c r="N100" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="O100" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($90 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($67 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Dark Horse Double Down Red Bl 750ml</t>
+          <t>Charles Smith Kung Fu Girl Riesling 750ml</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>085000026106</t>
+          <t>083120015048</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="F101" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="G101" t="n">
-        <v>-25</v>
+        <v>-4</v>
       </c>
       <c r="H101" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K101" t="n">
         <v>12</v>
@@ -6496,40 +6492,40 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>6.03</v>
+        <v>7.52</v>
       </c>
       <c r="N101" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="O101" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($72 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($90 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Clos Du Bois Chardonnay 750ml</t>
+          <t>Dark Horse Double Down Red Bl 750ml</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>087356510124</t>
+          <t>085000026106</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6538,196 +6534,196 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="F102" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="G102" t="n">
-        <v>-12</v>
+        <v>-25</v>
       </c>
       <c r="H102" t="n">
-        <v>14</v>
+        <v>1.8</v>
       </c>
       <c r="I102" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
         <v>12</v>
       </c>
-      <c r="K102" t="n">
-        <v>60</v>
-      </c>
       <c r="L102" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>5.78</v>
+        <v>6.03</v>
       </c>
       <c r="N102" t="n">
-        <v>347</v>
+        <v>72</v>
       </c>
       <c r="O102" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($347 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($72 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Bartenura Moscato 750ml</t>
+          <t>Clos Du Bois Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>087752005644</t>
+          <t>087356510124</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Moscato</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="F103" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G103" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="H103" t="n">
-        <v>12.8</v>
+        <v>14</v>
       </c>
       <c r="I103" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J103" t="n">
+        <v>12</v>
+      </c>
+      <c r="K103" t="n">
+        <v>60</v>
+      </c>
+      <c r="L103" t="n">
         <v>5</v>
       </c>
-      <c r="K103" t="n">
-        <v>48</v>
-      </c>
-      <c r="L103" t="n">
-        <v>4</v>
-      </c>
       <c r="M103" t="n">
-        <v>7.03</v>
+        <v>5.78</v>
       </c>
       <c r="N103" t="n">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="O103" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($338 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($347 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sonoma Cutrer Chardonnay 750ml</t>
+          <t>Bartenura Moscato 750ml</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>769611454441</t>
+          <t>087752005644</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Moscato</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>266</v>
+        <v>133</v>
       </c>
       <c r="F104" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G104" t="n">
-        <v>8</v>
+        <v>-8</v>
       </c>
       <c r="H104" t="n">
-        <v>24.8</v>
+        <v>12.8</v>
       </c>
       <c r="I104" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J104" t="n">
+        <v>5</v>
+      </c>
+      <c r="K104" t="n">
+        <v>48</v>
+      </c>
+      <c r="L104" t="n">
         <v>4</v>
       </c>
-      <c r="K104" t="n">
-        <v>660</v>
-      </c>
-      <c r="L104" t="n">
-        <v>55</v>
-      </c>
       <c r="M104" t="n">
-        <v>14.97</v>
+        <v>7.03</v>
       </c>
       <c r="N104" t="n">
-        <v>9878</v>
+        <v>338</v>
       </c>
       <c r="O104" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>Large buy ($9,878) - confirm; Buy-month stock-up ($9,878 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($338 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Decoy Sonoma Pinot Noir 750ml</t>
+          <t>Sonoma Cutrer Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>669576019221</t>
+          <t>769611454441</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6736,85 +6732,85 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103</v>
+        <v>266</v>
       </c>
       <c r="F105" t="n">
-        <v>12.6</v>
+        <v>10</v>
       </c>
       <c r="G105" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H105" t="n">
-        <v>10.2</v>
+        <v>24.8</v>
       </c>
       <c r="I105" t="n">
+        <v>7</v>
+      </c>
+      <c r="J105" t="n">
         <v>4</v>
       </c>
-      <c r="J105" t="n">
-        <v>0</v>
-      </c>
       <c r="K105" t="n">
-        <v>12</v>
+        <v>660</v>
       </c>
       <c r="L105" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="M105" t="n">
-        <v>13.02</v>
+        <v>14.97</v>
       </c>
       <c r="N105" t="n">
-        <v>156</v>
+        <v>9878</v>
       </c>
       <c r="O105" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($156 to next deal) - confirm</t>
+          <t>Large buy ($9,878) - confirm; Buy-month stock-up ($9,878 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Josh Cellars BB Cab 750ml</t>
+          <t>Decoy Sonoma Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>031259004327</t>
+          <t>669576019221</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>174</v>
+        <v>103</v>
       </c>
       <c r="F106" t="n">
-        <v>14.3</v>
+        <v>12.6</v>
       </c>
       <c r="G106" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H106" t="n">
-        <v>15.2</v>
+        <v>10.2</v>
       </c>
       <c r="I106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -6826,23 +6822,23 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>6.67</v>
+        <v>13.02</v>
       </c>
       <c r="N106" t="n">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="O106" t="n">
-        <v>68</v>
-      </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R106" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+        </is>
+      </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>Overstocked (14 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($156 to next deal) - confirm</t>
         </is>
       </c>
     </row>
@@ -7179,38 +7175,38 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Pacific Sound Carmenere 750ml</t>
+          <t>Bonterra Equinox Red 750ml</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>7801222923626</t>
+          <t>082896003044</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Other Reds</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Bourget Imports, LLC</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="F112" t="n">
-        <v>26.2</v>
+        <v>27.3</v>
       </c>
       <c r="G112" t="n">
-        <v>-5</v>
+        <v>7</v>
       </c>
       <c r="H112" t="n">
-        <v>19.2</v>
+        <v>4.5</v>
       </c>
       <c r="I112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -7222,35 +7218,35 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>4.25</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="N112" t="n">
-        <v>51</v>
+        <v>104</v>
       </c>
       <c r="O112" t="n">
-        <v>72</v>
-      </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R112" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>In buy-month (Mar, Apr, Jul, Sep, Oct, Nov, Dec) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>Overstocked (26 wks on hand) - confirm before buying more; Seasonal - last year ~19/wk vs 7 now, buy ahead?</t>
+          <t>Buy-month stock-up ($104 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Bonterra Equinox Red 750ml</t>
+          <t>Black Box Dolce Semi-Sweet Red Blend 3L Box</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>082896003044</t>
+          <t>085000037669</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7260,68 +7256,72 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>134</v>
+        <v>59</v>
       </c>
       <c r="F113" t="n">
-        <v>27.3</v>
+        <v>28.1</v>
       </c>
       <c r="G113" t="n">
-        <v>7</v>
+        <v>-27</v>
       </c>
       <c r="H113" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>8.710000000000001</v>
+        <v>12.71</v>
       </c>
       <c r="N113" t="n">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="O113" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q113" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Sep, Oct, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($104 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($76 to next deal) - confirm; Seasonal - last year ~5/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Black Box Dolce Semi-Sweet Red Blend 3L Box</t>
+          <t>Clos Du Bois Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>085000037669</t>
+          <t>087356442128</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7330,16 +7330,16 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="F114" t="n">
-        <v>28.1</v>
+        <v>30</v>
       </c>
       <c r="G114" t="n">
-        <v>-27</v>
+        <v>-43</v>
       </c>
       <c r="H114" t="n">
-        <v>4.8</v>
+        <v>0.8</v>
       </c>
       <c r="I114" t="n">
         <v>1</v>
@@ -7348,67 +7348,67 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L114" t="n">
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>12.71</v>
+        <v>6.96</v>
       </c>
       <c r="N114" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="O114" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($76 to next deal) - confirm; Seasonal - last year ~5/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($84 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Clos Du Bois Pinot Noir 750ml</t>
+          <t>Bonterra Pinot Gris 750ml</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>087356442128</t>
+          <t>082896004157</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="F115" t="n">
-        <v>30</v>
+        <v>30.3</v>
       </c>
       <c r="G115" t="n">
-        <v>-43</v>
+        <v>-22</v>
       </c>
       <c r="H115" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -7420,40 +7420,40 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>6.96</v>
+        <v>7.43</v>
       </c>
       <c r="N115" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="O115" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Sep, Oct, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($84 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($89 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Bonterra Pinot Gris 750ml</t>
+          <t>Decoy Zinfandel 750ml</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>082896004157</t>
+          <t>669576019238</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -7462,19 +7462,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="F116" t="n">
-        <v>30.3</v>
+        <v>34.3</v>
       </c>
       <c r="G116" t="n">
-        <v>-22</v>
+        <v>20</v>
       </c>
       <c r="H116" t="n">
         <v>3.2</v>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -7486,40 +7486,40 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>7.43</v>
+        <v>14.1</v>
       </c>
       <c r="N116" t="n">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c r="O116" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Sep, Oct, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($89 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($169 to next deal) - confirm; Seasonal - last year ~3/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Decoy Zinfandel 750ml</t>
+          <t>Harken Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>669576019238</t>
+          <t>847159001812</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7528,19 +7528,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>48</v>
+        <v>238</v>
       </c>
       <c r="F117" t="n">
-        <v>34.3</v>
+        <v>46.4</v>
       </c>
       <c r="G117" t="n">
-        <v>20</v>
+        <v>-11</v>
       </c>
       <c r="H117" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -7552,40 +7552,40 @@
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>14.1</v>
+        <v>5.92</v>
       </c>
       <c r="N117" t="n">
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="O117" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Jan, Mar, Jul, Aug) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($169 to next deal) - confirm; Seasonal - last year ~3/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($71 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Harken Chardonnay 750ml</t>
+          <t>Decoy Merlot 750ml</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>847159001812</t>
+          <t>669576019252</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7594,19 +7594,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>238</v>
+        <v>117</v>
       </c>
       <c r="F118" t="n">
-        <v>46.4</v>
+        <v>50.1</v>
       </c>
       <c r="G118" t="n">
-        <v>-11</v>
+        <v>-46</v>
       </c>
       <c r="H118" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="I118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -7618,87 +7618,21 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>5.92</v>
+        <v>12.72</v>
       </c>
       <c r="N118" t="n">
-        <v>71</v>
+        <v>153</v>
       </c>
       <c r="O118" t="n">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, Jul, Aug) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($71 to next deal) - confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Decoy Merlot 750ml</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>669576019252</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Merlot</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
-        </is>
-      </c>
-      <c r="E119" t="n">
-        <v>117</v>
-      </c>
-      <c r="F119" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="G119" t="n">
-        <v>-46</v>
-      </c>
-      <c r="H119" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I119" t="n">
-        <v>2</v>
-      </c>
-      <c r="J119" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" t="n">
-        <v>12</v>
-      </c>
-      <c r="L119" t="n">
-        <v>1</v>
-      </c>
-      <c r="M119" t="n">
-        <v>12.72</v>
-      </c>
-      <c r="N119" t="n">
-        <v>153</v>
-      </c>
-      <c r="O119" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q119" t="inlineStr"/>
-      <c r="R119" t="inlineStr">
-        <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
-        </is>
-      </c>
-      <c r="S119" t="inlineStr">
         <is>
           <t>Buy-month stock-up ($153 to next deal) - confirm</t>
         </is>
@@ -7715,7 +7649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S52"/>
+  <dimension ref="A1:S50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10231,17 +10165,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Josh Cellars BB Cab 750ml</t>
+          <t>Black Box Vibrant Velvety Red Blend 3L Box</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>031259004327</t>
+          <t>085000034545</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -10250,16 +10184,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>174</v>
+        <v>68</v>
       </c>
       <c r="F39" t="n">
-        <v>14.3</v>
+        <v>15.3</v>
       </c>
       <c r="G39" t="n">
-        <v>12</v>
+        <v>-23</v>
       </c>
       <c r="H39" t="n">
-        <v>15.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I39" t="n">
         <v>3</v>
@@ -10268,133 +10202,133 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L39" t="n">
         <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>6.67</v>
+        <v>13.2</v>
       </c>
       <c r="N39" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O39" t="n">
-        <v>68</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Overstocked (14 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($79 to next deal) - confirm; Seasonal - last year ~9/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Black Box Vibrant Velvety Red Blend 3L Box</t>
+          <t>Bonterra Rose 750ml</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>085000034545</t>
+          <t>082896060412</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="F40" t="n">
-        <v>15.3</v>
+        <v>16.6</v>
       </c>
       <c r="G40" t="n">
-        <v>-23</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L40" t="n">
         <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>13.2</v>
+        <v>7.46</v>
       </c>
       <c r="N40" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="O40" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Sep, Oct, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($79 to next deal) - confirm; Seasonal - last year ~9/wk vs 4 now, buy ahead?</t>
+          <t>Buy-month stock-up ($90 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bonterra Rose 750ml</t>
+          <t>Ecco Domani 90 Calorie Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>082896060412</t>
+          <t>085000040119</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="F41" t="n">
-        <v>16.6</v>
+        <v>18.4</v>
       </c>
       <c r="G41" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
         <v>3</v>
-      </c>
-      <c r="H41" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I41" t="n">
-        <v>5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -10406,35 +10340,35 @@
         <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>7.46</v>
+        <v>8</v>
       </c>
       <c r="N41" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="O41" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Sep, Oct, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, Apr, Jul, Sep, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($90 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($96 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ecco Domani 90 Calorie Pinot Grigio 750ml</t>
+          <t>Black Box Brilliant Pinot Grigio 3L Box</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>085000040119</t>
+          <t>085000034507</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -10448,64 +10382,64 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>159</v>
+        <v>90</v>
       </c>
       <c r="F42" t="n">
         <v>18.4</v>
       </c>
       <c r="G42" t="n">
-        <v>-12</v>
+        <v>-28</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L42" t="n">
         <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>8</v>
+        <v>11.97</v>
       </c>
       <c r="N42" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="O42" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, Apr, Jul, Sep, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($96 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($72 to next deal) - confirm; Seasonal - last year ~10/wk vs 5 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Black Box Brilliant Pinot Grigio 3L Box</t>
+          <t>Dark Horse Merlot 750ml</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>085000034507</t>
+          <t>085000022870</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -10514,37 +10448,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="F43" t="n">
-        <v>18.4</v>
+        <v>21.4</v>
       </c>
       <c r="G43" t="n">
-        <v>-28</v>
+        <v>-36</v>
       </c>
       <c r="H43" t="n">
-        <v>9.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L43" t="n">
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>11.97</v>
+        <v>5.59</v>
       </c>
       <c r="N43" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="O43" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
@@ -10554,42 +10488,42 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($72 to next deal) - confirm; Seasonal - last year ~10/wk vs 5 now, buy ahead?</t>
+          <t>Buy-month stock-up ($67 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dark Horse Merlot 750ml</t>
+          <t>Bonterra Equinox Red 750ml</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>085000022870</t>
+          <t>082896003044</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Merlot</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>15</v>
+        <v>134</v>
       </c>
       <c r="F44" t="n">
-        <v>21.4</v>
+        <v>27.3</v>
       </c>
       <c r="G44" t="n">
-        <v>-36</v>
+        <v>7</v>
       </c>
       <c r="H44" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="I44" t="n">
         <v>2</v>
@@ -10604,127 +10538,131 @@
         <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>5.59</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="O44" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Sep, Oct, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($67 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($104 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Pacific Sound Carmenere 750ml</t>
+          <t>Black Box Dolce Semi-Sweet Red Blend 3L Box</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>7801222923626</t>
+          <t>085000037669</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Other Reds</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Bourget Imports, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>171</v>
+        <v>59</v>
       </c>
       <c r="F45" t="n">
-        <v>26.2</v>
+        <v>28.1</v>
       </c>
       <c r="G45" t="n">
-        <v>-5</v>
+        <v>-27</v>
       </c>
       <c r="H45" t="n">
-        <v>19.2</v>
+        <v>4.8</v>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L45" t="n">
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>4.25</v>
+        <v>12.71</v>
       </c>
       <c r="N45" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="O45" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>ON AD - weekly special (buy to 4.5w)</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Overstocked (26 wks on hand) - confirm before buying more; Seasonal - last year ~19/wk vs 7 now, buy ahead?</t>
+          <t>Buy-month stock-up ($76 to next deal) - confirm; Seasonal - last year ~5/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Bonterra Equinox Red 750ml</t>
+          <t>Clos Du Bois Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>082896003044</t>
+          <t>087356442128</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>134</v>
+        <v>28</v>
       </c>
       <c r="F46" t="n">
-        <v>27.3</v>
+        <v>30</v>
       </c>
       <c r="G46" t="n">
-        <v>7</v>
+        <v>-43</v>
       </c>
       <c r="H46" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -10736,124 +10674,124 @@
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>8.710000000000001</v>
+        <v>6.96</v>
       </c>
       <c r="N46" t="n">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="O46" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Sep, Oct, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($104 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($84 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Black Box Dolce Semi-Sweet Red Blend 3L Box</t>
+          <t>Bonterra Pinot Gris 750ml</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>085000037669</t>
+          <t>082896004157</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="F47" t="n">
-        <v>28.1</v>
+        <v>30.3</v>
       </c>
       <c r="G47" t="n">
-        <v>-27</v>
+        <v>-22</v>
       </c>
       <c r="H47" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>12.71</v>
+        <v>7.43</v>
       </c>
       <c r="N47" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O47" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Sep, Oct, Nov, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($76 to next deal) - confirm; Seasonal - last year ~5/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($89 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Clos Du Bois Pinot Noir 750ml</t>
+          <t>Decoy Zinfandel 750ml</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>087356442128</t>
+          <t>669576019238</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="F48" t="n">
-        <v>30</v>
+        <v>34.3</v>
       </c>
       <c r="G48" t="n">
-        <v>-43</v>
+        <v>20</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="I48" t="n">
         <v>1</v>
@@ -10868,40 +10806,40 @@
         <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>6.96</v>
+        <v>14.1</v>
       </c>
       <c r="N48" t="n">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="O48" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jul, Oct) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($84 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($169 to next deal) - confirm; Seasonal - last year ~3/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Bonterra Pinot Gris 750ml</t>
+          <t>Harken Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>082896004157</t>
+          <t>847159001812</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10910,19 +10848,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>120</v>
+        <v>238</v>
       </c>
       <c r="F49" t="n">
-        <v>30.3</v>
+        <v>46.4</v>
       </c>
       <c r="G49" t="n">
-        <v>-22</v>
+        <v>-11</v>
       </c>
       <c r="H49" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -10934,40 +10872,40 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>7.43</v>
+        <v>5.92</v>
       </c>
       <c r="N49" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O49" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Sep, Oct, Nov, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, Jul, Aug) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($89 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($71 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Decoy Zinfandel 750ml</t>
+          <t>Decoy Merlot 750ml</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>669576019238</t>
+          <t>669576019252</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10976,19 +10914,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="F50" t="n">
-        <v>34.3</v>
+        <v>50.1</v>
       </c>
       <c r="G50" t="n">
-        <v>20</v>
+        <v>-46</v>
       </c>
       <c r="H50" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -11000,13 +10938,13 @@
         <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>14.1</v>
+        <v>12.72</v>
       </c>
       <c r="N50" t="n">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="O50" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
@@ -11015,138 +10953,6 @@
         </is>
       </c>
       <c r="S50" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($169 to next deal) - confirm; Seasonal - last year ~3/wk vs 1 now, buy ahead?</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Harken Chardonnay 750ml</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>847159001812</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Chardonnay</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>238</v>
-      </c>
-      <c r="F51" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="G51" t="n">
-        <v>-11</v>
-      </c>
-      <c r="H51" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I51" t="n">
-        <v>3</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>12</v>
-      </c>
-      <c r="L51" t="n">
-        <v>1</v>
-      </c>
-      <c r="M51" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="N51" t="n">
-        <v>71</v>
-      </c>
-      <c r="O51" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>In buy-month (Jan, Mar, Jul, Aug) - stock up ~4wks to next deal</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($71 to next deal) - confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Decoy Merlot 750ml</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>669576019252</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Merlot</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>117</v>
-      </c>
-      <c r="F52" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="G52" t="n">
-        <v>-46</v>
-      </c>
-      <c r="H52" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I52" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>12</v>
-      </c>
-      <c r="L52" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" t="n">
-        <v>12.72</v>
-      </c>
-      <c r="N52" t="n">
-        <v>153</v>
-      </c>
-      <c r="O52" t="n">
-        <v>47</v>
-      </c>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~4wks to next deal</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
         <is>
           <t>Buy-month stock-up ($153 to next deal) - confirm</t>
         </is>
@@ -12379,7 +12185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12664,106 +12470,102 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J Lohr Cabernet Sauvignon 750ml</t>
+          <t>Pine Ridge Chen Blanc/Viognier 750ml</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>089121288122</t>
+          <t>000579000098</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>White Blends</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="F5" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="G5" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>20.5</v>
+        <v>29.5</v>
       </c>
       <c r="I5" t="n">
-        <v>57</v>
+        <v>111</v>
       </c>
       <c r="J5" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>13.15</v>
+        <v>7.24</v>
       </c>
       <c r="N5" t="n">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="O5" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>ON AD - Sunday special (buy to 4.5w)</t>
-        </is>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Mar, Jun, Sep, Nov, Dec)</t>
+          <t>Wait for buy-month (Feb, May, Aug, Oct, Nov)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Meiomi Cabernet Sauvignon 750ml</t>
+          <t>Santa Margherita Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>086003251274</t>
+          <t>086891022871</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="F6" t="n">
-        <v>12.9</v>
+        <v>8.6</v>
       </c>
       <c r="G6" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>31.8</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K6" t="n">
         <v>12</v>
@@ -12772,13 +12574,13 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>14.33</v>
+        <v>19.19</v>
       </c>
       <c r="N6" t="n">
-        <v>172</v>
+        <v>230</v>
       </c>
       <c r="O6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -12787,24 +12589,24 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Mar, Jun, Sep, Dec)</t>
+          <t>Wait for buy-month (Mar, May, Aug, Sep, Nov, Dec)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pine Ridge Chen Blanc/Viognier 750ml</t>
+          <t>Underwood Bubbles 355ml</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>000579000098</t>
+          <t>856036001098</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>White Blends</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -12813,54 +12615,54 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H7" t="n">
-        <v>29.5</v>
+        <v>54</v>
       </c>
       <c r="I7" t="n">
-        <v>111</v>
+        <v>174</v>
       </c>
       <c r="J7" t="n">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M7" t="n">
-        <v>7.24</v>
+        <v>4.5</v>
       </c>
       <c r="N7" t="n">
-        <v>174</v>
+        <v>649</v>
       </c>
       <c r="O7" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Feb, May, Aug, Oct, Nov)</t>
+          <t>Wait for buy-month (Apr, Jun, Aug, Oct)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Underwood Bubbles 355ml</t>
+          <t>Underwood Rose Bubbles 375ml</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>856036001098</t>
+          <t>856036001197</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -12874,37 +12676,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="G8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>54</v>
+        <v>54.2</v>
       </c>
       <c r="I8" t="n">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="J8" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K8" t="n">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="N8" t="n">
-        <v>649</v>
+        <v>416</v>
       </c>
       <c r="O8" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -12916,120 +12718,59 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Underwood Rose Bubbles 375ml</t>
+          <t>Whitehaven Sauv Blanc 750ml</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>856036001197</t>
+          <t>085000012017</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>136</v>
+        <v>582</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>54.2</v>
+        <v>126.5</v>
       </c>
       <c r="I9" t="n">
-        <v>143</v>
+        <v>339</v>
       </c>
       <c r="J9" t="n">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="K9" t="n">
-        <v>108</v>
+        <v>228</v>
       </c>
       <c r="L9" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="M9" t="n">
-        <v>3.85</v>
+        <v>12.08</v>
       </c>
       <c r="N9" t="n">
-        <v>416</v>
+        <v>2753</v>
       </c>
       <c r="O9" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
-        <is>
-          <t>Wait for buy-month (Apr, Jun, Aug, Oct)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Whitehaven Sauv Blanc 750ml</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>085000012017</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Sauvignon Blanc</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>582</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>126.5</v>
-      </c>
-      <c r="I10" t="n">
-        <v>339</v>
-      </c>
-      <c r="J10" t="n">
-        <v>107</v>
-      </c>
-      <c r="K10" t="n">
-        <v>228</v>
-      </c>
-      <c r="L10" t="n">
-        <v>19</v>
-      </c>
-      <c r="M10" t="n">
-        <v>12.08</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2753</v>
-      </c>
-      <c r="O10" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr">
         <is>
           <t>Wait for buy-month (Feb, May, Aug, Nov)</t>
         </is>

--- a/data/Wine Recommended Order.xlsx
+++ b/data/Wine Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S99"/>
+  <dimension ref="A1:S100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1465,21 +1465,25 @@
         <v>13</v>
       </c>
       <c r="K18" t="n">
-        <v>240</v>
+        <v>288</v>
       </c>
       <c r="L18" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M18" t="n">
         <v>7.92</v>
       </c>
       <c r="N18" t="n">
-        <v>1900</v>
+        <v>2280</v>
       </c>
       <c r="O18" t="n">
         <v>43</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
     </row>
@@ -4771,35 +4775,35 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Black Box Pinot Noir 3L Box</t>
+          <t>Kim Crawford Sauvignon Blanc Non Alc 750ml</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>081434710017</t>
+          <t>689352010327</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221</v>
+        <v>17</v>
       </c>
       <c r="F74" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="G74" t="n">
-        <v>-15</v>
+        <v>26</v>
       </c>
       <c r="H74" t="n">
-        <v>44.5</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
         <v>5</v>
@@ -4808,136 +4812,132 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="L74" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>5.85</v>
+        <v>10.7</v>
       </c>
       <c r="N74" t="n">
-        <v>562</v>
+        <v>128</v>
       </c>
       <c r="O74" t="n">
-        <v>71</v>
-      </c>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($562 to next deal) - confirm</t>
-        </is>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Pacific Rim Sweet Riesling 750ml</t>
+          <t>Black Box Pinot Noir 3L Box</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>899552102276</t>
+          <t>081434710017</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>31</v>
+        <v>221</v>
       </c>
       <c r="F75" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="G75" t="n">
-        <v>19</v>
+        <v>-15</v>
       </c>
       <c r="H75" t="n">
-        <v>4.5</v>
+        <v>44.5</v>
       </c>
       <c r="I75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="M75" t="n">
-        <v>5.1</v>
+        <v>5.85</v>
       </c>
       <c r="N75" t="n">
-        <v>61</v>
+        <v>562</v>
       </c>
       <c r="O75" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Feb, Jul, Aug, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($61 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($562 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Colle Corviano Cerasuolo Rose 750ml</t>
+          <t>Pacific Rim Sweet Riesling 750ml</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>181856000892</t>
+          <t>899552102276</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Small Lot MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>112</v>
+        <v>31</v>
       </c>
       <c r="F76" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="G76" t="n">
-        <v>-10</v>
+        <v>19</v>
       </c>
       <c r="H76" t="n">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="I76" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="J76" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="K76" t="n">
         <v>12</v>
@@ -4946,153 +4946,157 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="N76" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="O76" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, May, Jun, Jul, Aug) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Jan, Feb, Jul, Aug, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($72 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($61 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Black Box Red Elegance 3L Box</t>
+          <t>Colle Corviano Cerasuolo Rose 750ml</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>081434700193</t>
+          <t>181856000892</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Small Lot MN</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F77" t="n">
         <v>6.5</v>
       </c>
       <c r="G77" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="H77" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="I77" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="J77" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="K77" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="L77" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" t="n">
         <v>6</v>
       </c>
-      <c r="M77" t="n">
-        <v>15.28</v>
-      </c>
       <c r="N77" t="n">
-        <v>550</v>
+        <v>72</v>
       </c>
       <c r="O77" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, May, Jun, Jul, Aug) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($550 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($72 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Raza Vinho Verde 750ml</t>
+          <t>Black Box Red Elegance 3L Box</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5600379041236</t>
+          <t>081434700193</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>The Wine Company</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>185</v>
+        <v>108</v>
       </c>
       <c r="F78" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="G78" t="n">
-        <v>77</v>
+        <v>-2</v>
       </c>
       <c r="H78" t="n">
-        <v>14.8</v>
+        <v>21</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J78" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K78" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M78" t="n">
-        <v>5.88</v>
+        <v>15.28</v>
       </c>
       <c r="N78" t="n">
-        <v>71</v>
+        <v>550</v>
       </c>
       <c r="O78" t="n">
-        <v>55</v>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Buy-month stock-up ($550 to next deal) - confirm</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6336,11 +6340,7 @@
       <c r="O97" t="n">
         <v>36</v>
       </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
+      <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr">
         <is>
           <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
@@ -6421,64 +6421,130 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Barkan Cabernet Sauvignon 750ml</t>
+          <t>90+ Cellars Prosecco Rose (3pk) 187ml</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>087752006108</t>
+          <t>810879023655</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>63</v>
+        <v>139.66</v>
       </c>
       <c r="F99" t="n">
-        <v>90</v>
+        <v>39.9</v>
       </c>
       <c r="G99" t="n">
-        <v>-10</v>
+        <v>-17</v>
       </c>
       <c r="H99" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L99" t="n">
         <v>1</v>
       </c>
       <c r="M99" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="N99" t="n">
+        <v>74</v>
+      </c>
+      <c r="O99" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Overstocked (40 wks on hand) - confirm before buying more; Seasonal - last year ~6/wk vs 4 now, buy ahead?</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Barkan Cabernet Sauvignon 750ml</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>087752006108</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Cabernet</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>63</v>
+      </c>
+      <c r="F100" t="n">
+        <v>90</v>
+      </c>
+      <c r="G100" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I100" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>12</v>
+      </c>
+      <c r="L100" t="n">
+        <v>1</v>
+      </c>
+      <c r="M100" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="N99" t="n">
+      <c r="N100" t="n">
         <v>118</v>
       </c>
-      <c r="O99" t="n">
+      <c r="O100" t="n">
         <v>38</v>
       </c>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr">
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr">
         <is>
           <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
+      <c r="S100" t="inlineStr">
         <is>
           <t>Buy-month stock-up ($118 to next deal) - confirm</t>
         </is>
@@ -6495,7 +6561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9260,11 +9326,7 @@
       <c r="O42" t="n">
         <v>36</v>
       </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
           <t>In buy-month (Jan, Mar, May, Jul, Sep, Nov) - stock up ~9wks to next deal</t>
@@ -9345,64 +9407,130 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Barkan Cabernet Sauvignon 750ml</t>
+          <t>90+ Cellars Prosecco Rose (3pk) 187ml</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>087752006108</t>
+          <t>810879023655</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>63</v>
+        <v>139.66</v>
       </c>
       <c r="F44" t="n">
-        <v>90</v>
+        <v>39.9</v>
       </c>
       <c r="G44" t="n">
-        <v>-10</v>
+        <v>-17</v>
       </c>
       <c r="H44" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
       </c>
       <c r="M44" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="N44" t="n">
+        <v>74</v>
+      </c>
+      <c r="O44" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Overstocked (40 wks on hand) - confirm before buying more; Seasonal - last year ~6/wk vs 4 now, buy ahead?</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Barkan Cabernet Sauvignon 750ml</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>087752006108</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Cabernet</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Phillips Wine &amp; Spirits - St. Paul</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>63</v>
+      </c>
+      <c r="F45" t="n">
+        <v>90</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>12</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
         <v>9.859999999999999</v>
       </c>
-      <c r="N44" t="n">
+      <c r="N45" t="n">
         <v>118</v>
       </c>
-      <c r="O44" t="n">
+      <c r="O45" t="n">
         <v>38</v>
       </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr">
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
         <is>
           <t>In buy-month (Feb, Apr, Jul, Oct, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>Buy-month stock-up ($118 to next deal) - confirm</t>
         </is>
@@ -10621,35 +10749,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19 Crimes Cali Red 750ml</t>
+          <t>Apothic Cabernet Sauv 750ml</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>012354004290</t>
+          <t>085000030967</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>242</v>
+        <v>131</v>
       </c>
       <c r="F2" t="n">
-        <v>9.1</v>
+        <v>18.1</v>
       </c>
       <c r="G2" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="H2" t="n">
-        <v>20.2</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
         <v>3</v>
@@ -10664,13 +10792,13 @@
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>7.91</v>
+        <v>7.33</v>
       </c>
       <c r="N2" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="O2" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -10679,7 +10807,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Wait for buy-month (Mar, May, Jun, Sep, Nov, Dec)</t>
+          <t>Wait for buy-month (Feb, May, Aug, Oct, Dec)</t>
         </is>
       </c>
     </row>

--- a/data/Wine Recommended Order.xlsx
+++ b/data/Wine Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S115"/>
+  <dimension ref="A1:S121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4335,342 +4335,338 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Barefoot Apple Moscato 750ml</t>
+          <t>Summit Chardonnay 3L Box</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>085000029022</t>
+          <t>083120015420</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F66" t="n">
         <v>8</v>
       </c>
       <c r="G66" t="n">
-        <v>-23</v>
+        <v>31</v>
       </c>
       <c r="H66" t="n">
-        <v>8.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K66" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="L66" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>4.36</v>
+        <v>11.19</v>
       </c>
       <c r="N66" t="n">
-        <v>367</v>
+        <v>67</v>
       </c>
       <c r="O66" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($367 to next deal) - confirm</t>
+          <t>Seasonal - last year ~10/wk vs 7 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Barefoot Moscato 750ml</t>
+          <t>Summit Pinot Noir 3L Box</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>085000016688</t>
+          <t>083120016397</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Moscato</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="F67" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="G67" t="n">
-        <v>-22</v>
+        <v>17</v>
       </c>
       <c r="H67" t="n">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>240</v>
+        <v>6</v>
       </c>
       <c r="L67" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>4.37</v>
+        <v>11.19</v>
       </c>
       <c r="N67" t="n">
-        <v>1049</v>
+        <v>67</v>
       </c>
       <c r="O67" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($1,049 to next deal) - confirm</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Underwood Pinot Gris 375ml</t>
+          <t>Barefoot Apple Moscato 750ml</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>856036001067</t>
+          <t>085000029022</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="F68" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="G68" t="n">
-        <v>39</v>
+        <v>-23</v>
       </c>
       <c r="H68" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M68" t="n">
-        <v>4.18</v>
+        <v>4.36</v>
       </c>
       <c r="N68" t="n">
-        <v>50</v>
+        <v>367</v>
       </c>
       <c r="O68" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($50 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($367 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Quilt Reserve Cabernet Sauvignon 750ml</t>
+          <t>Barefoot Moscato 750ml</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>859889006111</t>
+          <t>085000016688</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Moscato</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>140</v>
       </c>
       <c r="F69" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>50</v>
+        <v>-22</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K69" t="n">
-        <v>12</v>
+        <v>240</v>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="M69" t="n">
-        <v>71.92</v>
+        <v>4.37</v>
       </c>
       <c r="N69" t="n">
-        <v>863</v>
+        <v>1049</v>
       </c>
       <c r="O69" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($863 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,049 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Barefoot Pink Moscato 750ml</t>
+          <t>Underwood Pinot Gris 375ml</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>085000020456</t>
+          <t>856036001067</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="F70" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="G70" t="n">
-        <v>-14</v>
+        <v>39</v>
       </c>
       <c r="H70" t="n">
-        <v>26.2</v>
+        <v>7.8</v>
       </c>
       <c r="I70" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="K70" t="n">
-        <v>252</v>
+        <v>12</v>
       </c>
       <c r="L70" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>4.32</v>
+        <v>4.18</v>
       </c>
       <c r="N70" t="n">
-        <v>1089</v>
+        <v>50</v>
       </c>
       <c r="O70" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,089 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($50 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Quilt Napa Cabernet Sauvignon 750ml</t>
+          <t>Quilt Reserve Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>859889006005</t>
+          <t>859889006111</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4684,37 +4680,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="G71" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H71" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>216</v>
+        <v>12</v>
       </c>
       <c r="L71" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="M71" t="n">
-        <v>33.39</v>
+        <v>71.92</v>
       </c>
       <c r="N71" t="n">
-        <v>7213</v>
+        <v>863</v>
       </c>
       <c r="O71" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
@@ -4724,217 +4720,217 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Large buy ($7,213) - confirm; Buy-month stock-up ($7,213 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($863 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Robert Mondavi PS Cab Sauv BB 750ml</t>
+          <t>Barefoot Pink Moscato 750ml</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>086003780217</t>
+          <t>085000020456</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="F72" t="n">
-        <v>9.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="G72" t="n">
-        <v>-7</v>
+        <v>-14</v>
       </c>
       <c r="H72" t="n">
-        <v>12.2</v>
+        <v>26.2</v>
       </c>
       <c r="I72" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J72" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K72" t="n">
-        <v>48</v>
+        <v>252</v>
       </c>
       <c r="L72" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="M72" t="n">
-        <v>8.699999999999999</v>
+        <v>4.32</v>
       </c>
       <c r="N72" t="n">
-        <v>417</v>
+        <v>1089</v>
       </c>
       <c r="O72" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($417 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,089 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Barefoot Sauv Blanc 750ml</t>
+          <t>Summit Pinot Grigio 3L Box</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>018341751024</t>
+          <t>083120015444</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="F73" t="n">
-        <v>9.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="G73" t="n">
-        <v>19</v>
+        <v>-1</v>
       </c>
       <c r="H73" t="n">
-        <v>3.8</v>
+        <v>11.2</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J73" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K73" t="n">
-        <v>132</v>
+        <v>6</v>
       </c>
       <c r="L73" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>4.34</v>
+        <v>11.19</v>
       </c>
       <c r="N73" t="n">
-        <v>573</v>
+        <v>67</v>
       </c>
       <c r="O73" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr"/>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($573 to next deal) - confirm</t>
+          <t>Overstocked (9 wks on hand) - confirm before buying more; Seasonal - last year ~11/wk vs 6 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Four Graces Pinot Noir 750ml</t>
+          <t>Quilt Napa Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>185977000076</t>
+          <t>859889006005</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="F74" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>12</v>
+        <v>216</v>
       </c>
       <c r="L74" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="M74" t="n">
-        <v>16.67</v>
+        <v>33.39</v>
       </c>
       <c r="N74" t="n">
-        <v>200</v>
+        <v>7213</v>
       </c>
       <c r="O74" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, May, Aug, Sep, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($200 to next deal) - confirm</t>
+          <t>Large buy ($7,213) - confirm; Buy-month stock-up ($7,213 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Frank Family Cabernet 750ml</t>
+          <t>Robert Mondavi PS Cab Sauv BB 750ml</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>894910000409</t>
+          <t>086003780217</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4944,158 +4940,158 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="F75" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>45</v>
+        <v>-7</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="I75" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J75" t="n">
         <v>6</v>
       </c>
       <c r="K75" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M75" t="n">
-        <v>38</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N75" t="n">
-        <v>456</v>
+        <v>417</v>
       </c>
       <c r="O75" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($456 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($417 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Underwood Rose 375ml</t>
+          <t>Barefoot Sauv Blanc 750ml</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>856036001074</t>
+          <t>018341751024</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="F76" t="n">
-        <v>10.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H76" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="I76" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K76" t="n">
-        <v>12</v>
+        <v>132</v>
       </c>
       <c r="L76" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M76" t="n">
-        <v>4.17</v>
+        <v>4.34</v>
       </c>
       <c r="N76" t="n">
-        <v>50</v>
+        <v>573</v>
       </c>
       <c r="O76" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($50 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($573 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Apothic White 750ml</t>
+          <t>Four Graces Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>085000019733</t>
+          <t>185977000076</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>White Blends</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="F77" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G77" t="n">
-        <v>-17</v>
+        <v>17</v>
       </c>
       <c r="H77" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J77" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
         <v>12</v>
@@ -5104,190 +5100,190 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>7.32</v>
+        <v>16.67</v>
       </c>
       <c r="N77" t="n">
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="O77" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, May, Aug, Sep, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($200 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Barefoot Peach Moscato 750ml</t>
+          <t>Frank Family Cabernet 750ml</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>085000029008</t>
+          <t>894910000409</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>157</v>
+        <v>33</v>
       </c>
       <c r="F78" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="G78" t="n">
-        <v>-9</v>
+        <v>45</v>
       </c>
       <c r="H78" t="n">
-        <v>26.2</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J78" t="n">
         <v>6</v>
       </c>
       <c r="K78" t="n">
-        <v>168</v>
+        <v>12</v>
       </c>
       <c r="L78" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>2.88</v>
+        <v>38</v>
       </c>
       <c r="N78" t="n">
-        <v>484</v>
+        <v>456</v>
       </c>
       <c r="O78" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($484 to next deal) - confirm; Seasonal - last year ~26/wk vs 15 now, buy ahead?</t>
+          <t>Buy-month stock-up ($456 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Barefoot Chardonnay 750ml</t>
+          <t>Underwood Rose 375ml</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>018341751055</t>
+          <t>856036001074</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="F79" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="G79" t="n">
+        <v>23</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I79" t="n">
+        <v>9</v>
+      </c>
+      <c r="J79" t="n">
         <v>4</v>
       </c>
-      <c r="H79" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="I79" t="n">
-        <v>22</v>
-      </c>
-      <c r="J79" t="n">
-        <v>14</v>
-      </c>
       <c r="K79" t="n">
-        <v>108</v>
+        <v>12</v>
       </c>
       <c r="L79" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>4.47</v>
+        <v>4.17</v>
       </c>
       <c r="N79" t="n">
-        <v>483</v>
+        <v>50</v>
       </c>
       <c r="O79" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($483 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($50 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Charles Smith Kung Fu Girl Riesling 750ml</t>
+          <t>Apothic White 750ml</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>083120015048</t>
+          <t>085000019733</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>White Blends</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F80" t="n">
-        <v>11.6</v>
+        <v>10.3</v>
       </c>
       <c r="G80" t="n">
-        <v>-8</v>
+        <v>-17</v>
       </c>
       <c r="H80" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="I80" t="n">
         <v>12</v>
@@ -5302,106 +5298,106 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>7.49</v>
+        <v>7.32</v>
       </c>
       <c r="N80" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O80" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($90 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Decoy Sonoma Chardonnay 750ml</t>
+          <t>Barefoot Peach Moscato 750ml</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>669576019245</t>
+          <t>085000029008</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="F81" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="G81" t="n">
-        <v>27</v>
+        <v>-9</v>
       </c>
       <c r="H81" t="n">
-        <v>16.8</v>
+        <v>26.2</v>
       </c>
       <c r="I81" t="n">
+        <v>7</v>
+      </c>
+      <c r="J81" t="n">
         <v>6</v>
       </c>
-      <c r="J81" t="n">
-        <v>5</v>
-      </c>
       <c r="K81" t="n">
-        <v>12</v>
+        <v>168</v>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M81" t="n">
-        <v>11.52</v>
+        <v>2.88</v>
       </c>
       <c r="N81" t="n">
-        <v>138</v>
+        <v>484</v>
       </c>
       <c r="O81" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($138 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($484 to next deal) - confirm; Seasonal - last year ~26/wk vs 15 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>LaMarca Prosecco Demi Sec 750ml</t>
+          <t>Barefoot Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>085000040669</t>
+          <t>018341751055</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5410,196 +5406,196 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="F82" t="n">
-        <v>13.2</v>
+        <v>10.9</v>
       </c>
       <c r="G82" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="I82" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K82" t="n">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="L82" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M82" t="n">
-        <v>12.47</v>
+        <v>4.47</v>
       </c>
       <c r="N82" t="n">
-        <v>1796</v>
+        <v>483</v>
       </c>
       <c r="O82" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,796 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($483 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>LaMarca Prosecco Rose 750ml</t>
+          <t>Charles Smith Kung Fu Girl Riesling 750ml</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>085000032442</t>
+          <t>083120015048</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>147</v>
+        <v>92</v>
       </c>
       <c r="F83" t="n">
-        <v>13.7</v>
+        <v>11.6</v>
       </c>
       <c r="G83" t="n">
+        <v>-8</v>
+      </c>
+      <c r="H83" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I83" t="n">
+        <v>12</v>
+      </c>
+      <c r="J83" t="n">
         <v>9</v>
       </c>
-      <c r="H83" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="I83" t="n">
-        <v>8</v>
-      </c>
-      <c r="J83" t="n">
-        <v>8</v>
-      </c>
       <c r="K83" t="n">
-        <v>144</v>
+        <v>12</v>
       </c>
       <c r="L83" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>12.19</v>
+        <v>7.49</v>
       </c>
       <c r="N83" t="n">
-        <v>1755</v>
+        <v>90</v>
       </c>
       <c r="O83" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,755 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($90 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Belle Glos Clark &amp; Telephone 750ml</t>
+          <t>Decoy Sonoma Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>855622000118</t>
+          <t>669576019245</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>29</v>
+        <v>191</v>
       </c>
       <c r="F84" t="n">
-        <v>13.8</v>
+        <v>13</v>
       </c>
       <c r="G84" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="H84" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="I84" t="n">
+        <v>6</v>
+      </c>
+      <c r="J84" t="n">
+        <v>5</v>
+      </c>
+      <c r="K84" t="n">
+        <v>12</v>
+      </c>
+      <c r="L84" t="n">
         <v>1</v>
       </c>
-      <c r="I84" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>48</v>
-      </c>
-      <c r="L84" t="n">
-        <v>4</v>
-      </c>
       <c r="M84" t="n">
-        <v>32.89</v>
+        <v>11.52</v>
       </c>
       <c r="N84" t="n">
-        <v>1579</v>
+        <v>138</v>
       </c>
       <c r="O84" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,579 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($138 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Barefoot Pineapple Moscato 750ml</t>
+          <t>LaMarca Prosecco Demi Sec 750ml</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>085000033319</t>
+          <t>085000040669</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5608,64 +5604,64 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="F85" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="G85" t="n">
-        <v>-23</v>
+        <v>-1</v>
       </c>
       <c r="H85" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="L85" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M85" t="n">
-        <v>4.36</v>
+        <v>12.47</v>
       </c>
       <c r="N85" t="n">
-        <v>105</v>
+        <v>1796</v>
       </c>
       <c r="O85" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($105 to next deal) - confirm; Seasonal - last year ~5/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($1,796 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Barefoot Rose 750ml</t>
+          <t>LaMarca Prosecco Rose 750ml</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>085000025871</t>
+          <t>085000032442</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5674,125 +5670,125 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="F86" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="G86" t="n">
-        <v>-3</v>
+        <v>9</v>
       </c>
       <c r="H86" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="I86" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J86" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K86" t="n">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="L86" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M86" t="n">
-        <v>4.4</v>
+        <v>12.19</v>
       </c>
       <c r="N86" t="n">
-        <v>264</v>
+        <v>1755</v>
       </c>
       <c r="O86" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($264 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,755 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Barefoot Watermelon Moscato 750ml</t>
+          <t>Belle Glos Clark &amp; Telephone 750ml</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>085000029923</t>
+          <t>855622000118</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F87" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H87" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M87" t="n">
-        <v>4.31</v>
+        <v>32.89</v>
       </c>
       <c r="N87" t="n">
-        <v>52</v>
+        <v>1579</v>
       </c>
       <c r="O87" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($1,579 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Barefoot Mango Moscato 750ml</t>
+          <t>Barefoot Pineapple Moscato 750ml</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>085000032176</t>
+          <t>085000033319</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5806,19 +5802,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F88" t="n">
-        <v>14.8</v>
+        <v>13.9</v>
       </c>
       <c r="G88" t="n">
-        <v>-25</v>
+        <v>-23</v>
       </c>
       <c r="H88" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -5830,13 +5826,13 @@
         <v>2</v>
       </c>
       <c r="M88" t="n">
-        <v>4.32</v>
+        <v>4.36</v>
       </c>
       <c r="N88" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O88" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
@@ -5846,24 +5842,24 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($104 to next deal) - confirm; Seasonal - last year ~7/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($105 to next deal) - confirm; Seasonal - last year ~5/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Barefoot Riesling 750ml</t>
+          <t>Barefoot Rose 750ml</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>085000015810</t>
+          <t>085000025871</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5872,22 +5868,22 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="F89" t="n">
-        <v>15.1</v>
+        <v>14</v>
       </c>
       <c r="G89" t="n">
-        <v>14</v>
+        <v>-3</v>
       </c>
       <c r="H89" t="n">
         <v>10.5</v>
       </c>
       <c r="I89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K89" t="n">
         <v>60</v>
@@ -5896,13 +5892,13 @@
         <v>5</v>
       </c>
       <c r="M89" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="N89" t="n">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="O89" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
@@ -5912,24 +5908,24 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($260 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($264 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Apothic Rose 750ml</t>
+          <t>Barefoot Watermelon Moscato 750ml</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>085000021545</t>
+          <t>085000029923</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5938,19 +5934,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="F90" t="n">
-        <v>15.2</v>
+        <v>14.3</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -5962,101 +5958,101 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>7.1</v>
+        <v>4.31</v>
       </c>
       <c r="N90" t="n">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="O90" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($85 to next deal) - confirm; Seasonal - last year ~5/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Barefoot Pear Moscato 750ml</t>
+          <t>Summit Red Blend 3L Box</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>085000037607</t>
+          <t>083120015437</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F91" t="n">
-        <v>15.2</v>
+        <v>14.5</v>
       </c>
       <c r="G91" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="H91" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I91" t="n">
+        <v>3</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
         <v>6</v>
       </c>
-      <c r="J91" t="n">
-        <v>6</v>
-      </c>
-      <c r="K91" t="n">
-        <v>24</v>
-      </c>
       <c r="L91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>4.32</v>
+        <v>11.19</v>
       </c>
       <c r="N91" t="n">
-        <v>104</v>
+        <v>67</v>
       </c>
       <c r="O91" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($104 to next deal) - confirm; Seasonal - last year ~5/wk vs 3 now, buy ahead?</t>
+          <t>Overstocked (14 wks on hand) - confirm before buying more; Seasonal - last year ~9/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Barefoot Red Moscato 750ml</t>
+          <t>Barefoot Mango Moscato 750ml</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>085000019894</t>
+          <t>085000032176</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6070,37 +6066,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>116</v>
+        <v>45</v>
       </c>
       <c r="F92" t="n">
-        <v>15.5</v>
+        <v>14.8</v>
       </c>
       <c r="G92" t="n">
-        <v>-7</v>
+        <v>-25</v>
       </c>
       <c r="H92" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="L92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M92" t="n">
-        <v>4.38</v>
+        <v>4.32</v>
       </c>
       <c r="N92" t="n">
-        <v>210</v>
+        <v>104</v>
       </c>
       <c r="O92" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr">
@@ -6110,90 +6106,90 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($210 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($104 to next deal) - confirm; Seasonal - last year ~7/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Stags' Leap Cabernet Sauvignon Napa 750ml</t>
+          <t>Barefoot Riesling 750ml</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>089819042401</t>
+          <t>085000015810</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="F93" t="n">
-        <v>16.2</v>
+        <v>15.1</v>
       </c>
       <c r="G93" t="n">
+        <v>14</v>
+      </c>
+      <c r="H93" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I93" t="n">
         <v>10</v>
       </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>1</v>
-      </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K93" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="L93" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M93" t="n">
-        <v>39.9</v>
+        <v>4.33</v>
       </c>
       <c r="N93" t="n">
-        <v>479</v>
+        <v>260</v>
       </c>
       <c r="O93" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($479 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($260 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Barefoot White Zin 750ml</t>
+          <t>Apothic Rose 750ml</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>018341751062</t>
+          <t>085000021545</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6202,59 +6198,59 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="F94" t="n">
-        <v>17</v>
+        <v>15.2</v>
       </c>
       <c r="G94" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="I94" t="n">
+        <v>2</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
         <v>12</v>
       </c>
-      <c r="J94" t="n">
-        <v>11</v>
-      </c>
-      <c r="K94" t="n">
-        <v>36</v>
-      </c>
       <c r="L94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>4.38</v>
+        <v>7.1</v>
       </c>
       <c r="N94" t="n">
-        <v>158</v>
+        <v>85</v>
       </c>
       <c r="O94" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($158 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($85 to next deal) - confirm; Seasonal - last year ~5/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Barefoot Strawberry Moscato 750ml</t>
+          <t>Barefoot Pear Moscato 750ml</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>085000029015</t>
+          <t>085000037607</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6268,37 +6264,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>149</v>
+        <v>46</v>
       </c>
       <c r="F95" t="n">
-        <v>17.3</v>
+        <v>15.2</v>
       </c>
       <c r="G95" t="n">
-        <v>-22</v>
+        <v>44</v>
       </c>
       <c r="H95" t="n">
-        <v>12.2</v>
+        <v>5</v>
       </c>
       <c r="I95" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J95" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K95" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="L95" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M95" t="n">
-        <v>4.36</v>
+        <v>4.32</v>
       </c>
       <c r="N95" t="n">
-        <v>209</v>
+        <v>104</v>
       </c>
       <c r="O95" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
@@ -6308,114 +6304,114 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($209 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($104 to next deal) - confirm; Seasonal - last year ~5/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Quilt Threadcount Red Blend 750ml</t>
+          <t>Barefoot Red Moscato 750ml</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>860009046009</t>
+          <t>085000019894</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="F96" t="n">
-        <v>17.7</v>
+        <v>15.5</v>
       </c>
       <c r="G96" t="n">
-        <v>9</v>
+        <v>-7</v>
       </c>
       <c r="H96" t="n">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="I96" t="n">
+        <v>5</v>
+      </c>
+      <c r="J96" t="n">
+        <v>5</v>
+      </c>
+      <c r="K96" t="n">
+        <v>48</v>
+      </c>
+      <c r="L96" t="n">
         <v>4</v>
       </c>
-      <c r="J96" t="n">
-        <v>4</v>
-      </c>
-      <c r="K96" t="n">
-        <v>36</v>
-      </c>
-      <c r="L96" t="n">
-        <v>3</v>
-      </c>
       <c r="M96" t="n">
-        <v>13.45</v>
+        <v>4.38</v>
       </c>
       <c r="N96" t="n">
-        <v>484</v>
+        <v>210</v>
       </c>
       <c r="O96" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($484 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($210 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cooks Brut 750ml</t>
+          <t>Stags' Leap Cabernet Sauvignon Napa 750ml</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>083804047211</t>
+          <t>089819042401</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="F97" t="n">
-        <v>17.8</v>
+        <v>16.2</v>
       </c>
       <c r="G97" t="n">
-        <v>-36</v>
+        <v>10</v>
       </c>
       <c r="H97" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
         <v>12</v>
@@ -6424,40 +6420,40 @@
         <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>6</v>
+        <v>39.9</v>
       </c>
       <c r="N97" t="n">
-        <v>72</v>
+        <v>479</v>
       </c>
       <c r="O97" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($72 to next deal) - confirm; Seasonal - last year ~16/wk vs 10 now, buy ahead?</t>
+          <t>Buy-month stock-up ($479 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Apothic Crush 750ml</t>
+          <t>Barefoot White Zin 750ml</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>085000023488</t>
+          <t>018341751062</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6466,64 +6462,64 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>181</v>
+        <v>115</v>
       </c>
       <c r="F98" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G98" t="n">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="H98" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K98" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="L98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M98" t="n">
-        <v>6.16</v>
+        <v>4.38</v>
       </c>
       <c r="N98" t="n">
-        <v>74</v>
+        <v>158</v>
       </c>
       <c r="O98" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($74 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($158 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Apothic Cabernet Sauv 750ml</t>
+          <t>Barefoot Strawberry Moscato 750ml</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>085000030967</t>
+          <t>085000029015</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6532,68 +6528,64 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="F99" t="n">
-        <v>18.3</v>
+        <v>17.3</v>
       </c>
       <c r="G99" t="n">
-        <v>-8</v>
+        <v>-22</v>
       </c>
       <c r="H99" t="n">
-        <v>6.5</v>
+        <v>12.2</v>
       </c>
       <c r="I99" t="n">
         <v>4</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K99" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="L99" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M99" t="n">
-        <v>7.33</v>
+        <v>4.36</v>
       </c>
       <c r="N99" t="n">
-        <v>88</v>
+        <v>209</v>
       </c>
       <c r="O99" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($209 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Underwood Pinot Noir 355ml</t>
+          <t>Quilt Threadcount Red Blend 750ml</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>856036001043</t>
+          <t>860009046009</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6602,64 +6594,64 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="F100" t="n">
-        <v>18.6</v>
+        <v>17.7</v>
       </c>
       <c r="G100" t="n">
         <v>9</v>
       </c>
       <c r="H100" t="n">
-        <v>5.2</v>
+        <v>1.2</v>
       </c>
       <c r="I100" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J100" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K100" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="L100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M100" t="n">
-        <v>4.33</v>
+        <v>13.45</v>
       </c>
       <c r="N100" t="n">
-        <v>52</v>
+        <v>484</v>
       </c>
       <c r="O100" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($484 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Acrobat Rose 750ml</t>
+          <t>Cooks Brut 750ml</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>768675116029</t>
+          <t>083804047211</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6668,22 +6660,22 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>54</v>
+        <v>174</v>
       </c>
       <c r="F101" t="n">
-        <v>19.3</v>
+        <v>17.8</v>
       </c>
       <c r="G101" t="n">
-        <v>9</v>
+        <v>-36</v>
       </c>
       <c r="H101" t="n">
-        <v>4</v>
+        <v>15.8</v>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K101" t="n">
         <v>12</v>
@@ -6692,64 +6684,64 @@
         <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>9.17</v>
+        <v>6</v>
       </c>
       <c r="N101" t="n">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="O101" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, May, Aug, Sep, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($110 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($72 to next deal) - confirm; Seasonal - last year ~16/wk vs 10 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Ferrari Carano Fume Blanc 750ml</t>
+          <t>Apothic Crush 750ml</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>742651123102</t>
+          <t>085000023488</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>208</v>
+        <v>181</v>
       </c>
       <c r="F102" t="n">
-        <v>20.7</v>
+        <v>18</v>
       </c>
       <c r="G102" t="n">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="H102" t="n">
-        <v>11.8</v>
+        <v>6.8</v>
       </c>
       <c r="I102" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
         <v>12</v>
@@ -6758,40 +6750,40 @@
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>9.99</v>
+        <v>6.16</v>
       </c>
       <c r="N102" t="n">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="O102" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($120 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($74 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Barefoot Bright &amp; Breezy Pinot Grigio 750ml</t>
+          <t>Apothic Cabernet Sauv 750ml</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>085000032879</t>
+          <t>085000030967</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6800,19 +6792,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>45</v>
+        <v>128</v>
       </c>
       <c r="F103" t="n">
-        <v>21.4</v>
+        <v>18.3</v>
       </c>
       <c r="G103" t="n">
-        <v>108</v>
+        <v>-8</v>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="I103" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -6824,64 +6816,68 @@
         <v>1</v>
       </c>
       <c r="M103" t="n">
-        <v>4.47</v>
+        <v>7.33</v>
       </c>
       <c r="N103" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="O103" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q103" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($54 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Barefoot Sweet Red 750ml</t>
+          <t>Underwood Pinot Noir 355ml</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>085000018491</t>
+          <t>856036001043</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="F104" t="n">
-        <v>21.4</v>
+        <v>18.6</v>
       </c>
       <c r="G104" t="n">
-        <v>-36</v>
+        <v>9</v>
       </c>
       <c r="H104" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K104" t="n">
         <v>12</v>
@@ -6890,58 +6886,58 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>4.26</v>
+        <v>4.33</v>
       </c>
       <c r="N104" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O104" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($51 to next deal) - confirm; Seasonal - last year ~6/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Barefoot Merlot 750ml</t>
+          <t>Acrobat Rose 750ml</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>018341751109</t>
+          <t>768675116029</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Merlot</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="F105" t="n">
-        <v>24.6</v>
+        <v>19.3</v>
       </c>
       <c r="G105" t="n">
-        <v>-10</v>
+        <v>9</v>
       </c>
       <c r="H105" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="I105" t="n">
         <v>1</v>
@@ -6956,64 +6952,64 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>4.4</v>
+        <v>9.17</v>
       </c>
       <c r="N105" t="n">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="O105" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, Apr, May, Aug, Sep, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($53 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($110 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Boen Tri Appellation Chardonnay 750ml</t>
+          <t>Ferrari Carano Fume Blanc 750ml</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>856184006310</t>
+          <t>742651123102</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>23</v>
+        <v>208</v>
       </c>
       <c r="F106" t="n">
-        <v>24.6</v>
+        <v>20.7</v>
       </c>
       <c r="G106" t="n">
-        <v>140</v>
+        <v>-11</v>
       </c>
       <c r="H106" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="I106" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K106" t="n">
         <v>12</v>
@@ -7022,40 +7018,40 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>11.92</v>
+        <v>9.99</v>
       </c>
       <c r="N106" t="n">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="O106" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($143 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($120 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Belle Glos Dairyman Pinot Noir 750ml</t>
+          <t>Conundrum Red 750ml</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>855622000811</t>
+          <t>017224760122</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -7064,85 +7060,85 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>47</v>
+        <v>479</v>
       </c>
       <c r="F107" t="n">
-        <v>25.2</v>
+        <v>21.2</v>
       </c>
       <c r="G107" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="H107" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I107" t="n">
+        <v>2</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>12</v>
+      </c>
+      <c r="L107" t="n">
         <v>1</v>
       </c>
-      <c r="I107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" t="n">
-        <v>24</v>
-      </c>
-      <c r="L107" t="n">
-        <v>2</v>
-      </c>
       <c r="M107" t="n">
-        <v>31.77</v>
+        <v>6.59</v>
       </c>
       <c r="N107" t="n">
-        <v>763</v>
+        <v>79</v>
       </c>
       <c r="O107" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q107" t="inlineStr"/>
-      <c r="R107" t="inlineStr">
-        <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
-        </is>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($763 to next deal) - confirm</t>
+          <t>Overstocked (21 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Saldo Zinfandel 750ml</t>
+          <t>Barefoot Bright &amp; Breezy Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>086003258006</t>
+          <t>085000032879</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>96</v>
+        <v>45</v>
       </c>
       <c r="F108" t="n">
-        <v>27.4</v>
+        <v>21.4</v>
       </c>
       <c r="G108" t="n">
-        <v>-12</v>
+        <v>108</v>
       </c>
       <c r="H108" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -7154,40 +7150,40 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>20.35</v>
+        <v>4.47</v>
       </c>
       <c r="N108" t="n">
-        <v>244</v>
+        <v>54</v>
       </c>
       <c r="O108" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($244 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($54 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>LaMarca Prosecco Rose 187ml</t>
+          <t>Barefoot Sweet Red 750ml</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>085000034705</t>
+          <t>085000018491</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7196,154 +7192,154 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F109" t="n">
-        <v>28.9</v>
+        <v>21.4</v>
       </c>
       <c r="G109" t="n">
-        <v>-54</v>
+        <v>-36</v>
       </c>
       <c r="H109" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
       </c>
       <c r="K109" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L109" t="n">
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>4.53</v>
+        <v>4.26</v>
       </c>
       <c r="N109" t="n">
-        <v>109</v>
+        <v>51</v>
       </c>
       <c r="O109" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($109 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($51 to next deal) - confirm; Seasonal - last year ~6/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Risata Moscato d'Asti 1.5L</t>
+          <t>Barefoot Merlot 750ml</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>084279989266</t>
+          <t>018341751109</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Moscato</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="F110" t="n">
-        <v>32.9</v>
+        <v>24.6</v>
       </c>
       <c r="G110" t="n">
-        <v>-31</v>
+        <v>-10</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L110" t="n">
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>19.32</v>
+        <v>4.4</v>
       </c>
       <c r="N110" t="n">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="O110" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+        </is>
+      </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>Overstocked (33 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($53 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Apothic Merlot 750ml</t>
+          <t>Boen Tri Appellation Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>085000032145</t>
+          <t>856184006310</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Merlot</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="F111" t="n">
-        <v>35</v>
+        <v>24.6</v>
       </c>
       <c r="G111" t="n">
-        <v>6</v>
+        <v>140</v>
       </c>
       <c r="H111" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="I111" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J111" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K111" t="n">
         <v>12</v>
@@ -7352,172 +7348,172 @@
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>7.37</v>
+        <v>11.92</v>
       </c>
       <c r="N111" t="n">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="O111" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($143 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Kim Crawford Pinot Grigio 750ml</t>
+          <t>Belle Glos Dairyman Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>689352010310</t>
+          <t>855622000811</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="F112" t="n">
-        <v>37.1</v>
+        <v>25.2</v>
       </c>
       <c r="G112" t="n">
-        <v>18</v>
+        <v>-8</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M112" t="n">
-        <v>10.7</v>
+        <v>31.77</v>
       </c>
       <c r="N112" t="n">
-        <v>128</v>
+        <v>763</v>
       </c>
       <c r="O112" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($128 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($763 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>90+ Cellars Prosecco Rose (3pk) 187ml</t>
+          <t>Saldo Zinfandel 750ml</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>810879023655</t>
+          <t>086003258006</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>136.66</v>
+        <v>96</v>
       </c>
       <c r="F113" t="n">
-        <v>41.8</v>
+        <v>27.4</v>
       </c>
       <c r="G113" t="n">
-        <v>-25</v>
+        <v>-12</v>
       </c>
       <c r="H113" t="n">
-        <v>6.2</v>
+        <v>1.5</v>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>9.25</v>
+        <v>20.35</v>
       </c>
       <c r="N113" t="n">
-        <v>74</v>
+        <v>244</v>
       </c>
       <c r="O113" t="n">
-        <v>58</v>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+        </is>
+      </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>Overstocked (42 wks on hand) - confirm before buying more; Seasonal - last year ~6/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($244 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Apothic Inferno 750ml</t>
+          <t>LaMarca Prosecco Rose 187ml</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>085000024904</t>
+          <t>085000034705</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7526,111 +7522,507 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>217</v>
+        <v>27</v>
       </c>
       <c r="F114" t="n">
-        <v>46.5</v>
+        <v>28.9</v>
       </c>
       <c r="G114" t="n">
-        <v>-37</v>
+        <v>-54</v>
       </c>
       <c r="H114" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L114" t="n">
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>8.59</v>
+        <v>4.53</v>
       </c>
       <c r="N114" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="O114" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($103 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($109 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Harken Chardonnay 750ml</t>
+          <t>Risata Moscato d'Asti 1.5L</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>847159001812</t>
+          <t>084279989266</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Moscato</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>236</v>
+        <v>69</v>
       </c>
       <c r="F115" t="n">
-        <v>50.6</v>
+        <v>32.9</v>
       </c>
       <c r="G115" t="n">
-        <v>-14</v>
+        <v>-31</v>
       </c>
       <c r="H115" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L115" t="n">
         <v>1</v>
       </c>
       <c r="M115" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="N115" t="n">
+        <v>116</v>
+      </c>
+      <c r="O115" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Overstocked (33 wks on hand) - confirm before buying more</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Apothic Merlot 750ml</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>085000032145</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Merlot</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>147</v>
+      </c>
+      <c r="F116" t="n">
+        <v>35</v>
+      </c>
+      <c r="G116" t="n">
+        <v>6</v>
+      </c>
+      <c r="H116" t="n">
+        <v>4</v>
+      </c>
+      <c r="I116" t="n">
+        <v>7</v>
+      </c>
+      <c r="J116" t="n">
+        <v>5</v>
+      </c>
+      <c r="K116" t="n">
+        <v>12</v>
+      </c>
+      <c r="L116" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="N116" t="n">
+        <v>88</v>
+      </c>
+      <c r="O116" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Kim Crawford Pinot Grigio 750ml</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>689352010310</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Pinot Grigio/Gris</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>130</v>
+      </c>
+      <c r="F117" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="G117" t="n">
+        <v>18</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>12</v>
+      </c>
+      <c r="L117" t="n">
+        <v>1</v>
+      </c>
+      <c r="M117" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="N117" t="n">
+        <v>128</v>
+      </c>
+      <c r="O117" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>Buy-month stock-up ($128 to next deal) - confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>90+ Cellars Prosecco Rose (3pk) 187ml</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>810879023655</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Sparkling</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Bellboy Corporation</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>136.66</v>
+      </c>
+      <c r="F118" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>-25</v>
+      </c>
+      <c r="H118" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>8</v>
+      </c>
+      <c r="L118" t="n">
+        <v>1</v>
+      </c>
+      <c r="M118" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="N118" t="n">
+        <v>74</v>
+      </c>
+      <c r="O118" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>Overstocked (42 wks on hand) - confirm before buying more; Seasonal - last year ~6/wk vs 3 now, buy ahead?</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Summit Sauvignon Blanc 3L Box</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>083120016403</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Sauvignon Blanc</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>32</v>
+      </c>
+      <c r="F119" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="G119" t="n">
+        <v>-77</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>2</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>6</v>
+      </c>
+      <c r="L119" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="N119" t="n">
+        <v>67</v>
+      </c>
+      <c r="O119" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>Overstocked (46 wks on hand) - confirm before buying more</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Apothic Inferno 750ml</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>085000024904</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Red Blends</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>217</v>
+      </c>
+      <c r="F120" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="G120" t="n">
+        <v>-37</v>
+      </c>
+      <c r="H120" t="n">
+        <v>5</v>
+      </c>
+      <c r="I120" t="n">
+        <v>2</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>12</v>
+      </c>
+      <c r="L120" t="n">
+        <v>1</v>
+      </c>
+      <c r="M120" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="N120" t="n">
+        <v>103</v>
+      </c>
+      <c r="O120" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>Buy-month stock-up ($103 to next deal) - confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Harken Chardonnay 750ml</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>847159001812</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Chardonnay</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>236</v>
+      </c>
+      <c r="F121" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="G121" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H121" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I121" t="n">
+        <v>3</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>12</v>
+      </c>
+      <c r="L121" t="n">
+        <v>1</v>
+      </c>
+      <c r="M121" t="n">
         <v>5.93</v>
       </c>
-      <c r="N115" t="n">
+      <c r="N121" t="n">
         <v>71</v>
       </c>
-      <c r="O115" t="n">
+      <c r="O121" t="n">
         <v>67</v>
       </c>
-      <c r="Q115" t="inlineStr"/>
-      <c r="R115" t="inlineStr">
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr">
         <is>
           <t>In buy-month (Jan, Mar, Jul, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr">
+      <c r="S121" t="inlineStr">
         <is>
           <t>Buy-month stock-up ($71 to next deal) - confirm</t>
         </is>
@@ -7647,7 +8039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S71"/>
+  <dimension ref="A1:S76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9045,83 +9437,83 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Barefoot Apple Moscato 750ml</t>
+          <t>Summit Chardonnay 3L Box</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>085000029022</t>
+          <t>083120015420</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F22" t="n">
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>-23</v>
+        <v>31</v>
       </c>
       <c r="H22" t="n">
-        <v>8.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K22" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>4.36</v>
+        <v>11.19</v>
       </c>
       <c r="N22" t="n">
-        <v>367</v>
+        <v>67</v>
       </c>
       <c r="O22" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($367 to next deal) - confirm</t>
+          <t>Seasonal - last year ~10/wk vs 7 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Barefoot Moscato 750ml</t>
+          <t>Barefoot Apple Moscato 750ml</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>085000016688</t>
+          <t>085000029022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Moscato</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -9130,34 +9522,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="F23" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-23</v>
+      </c>
+      <c r="H23" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G23" t="n">
-        <v>-22</v>
-      </c>
-      <c r="H23" t="n">
-        <v>20.5</v>
-      </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>240</v>
+        <v>84</v>
       </c>
       <c r="L23" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="M23" t="n">
-        <v>4.37</v>
+        <v>4.36</v>
       </c>
       <c r="N23" t="n">
-        <v>1049</v>
+        <v>367</v>
       </c>
       <c r="O23" t="n">
         <v>45</v>
@@ -9170,90 +9562,90 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,049 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($367 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Underwood Pinot Gris 375ml</t>
+          <t>Barefoot Moscato 750ml</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>856036001067</t>
+          <t>085000016688</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Moscato</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="F24" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>39</v>
+        <v>-22</v>
       </c>
       <c r="H24" t="n">
-        <v>7.8</v>
+        <v>20.5</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
         <v>24</v>
       </c>
       <c r="K24" t="n">
-        <v>12</v>
+        <v>240</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M24" t="n">
-        <v>4.18</v>
+        <v>4.37</v>
       </c>
       <c r="N24" t="n">
-        <v>50</v>
+        <v>1049</v>
       </c>
       <c r="O24" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($50 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,049 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quilt Reserve Cabernet Sauvignon 750ml</t>
+          <t>Underwood Pinot Gris 375ml</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>859889006111</t>
+          <t>856036001067</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -9262,196 +9654,196 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="F25" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="G25" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="K25" t="n">
         <v>12</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>71.92</v>
+        <v>4.18</v>
       </c>
       <c r="N25" t="n">
-        <v>863</v>
+        <v>50</v>
       </c>
       <c r="O25" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($863 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($50 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Barefoot Pink Moscato 750ml</t>
+          <t>Quilt Reserve Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>085000020456</t>
+          <t>859889006111</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>174</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="G26" t="n">
-        <v>-14</v>
+        <v>50</v>
       </c>
       <c r="H26" t="n">
-        <v>26.2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>252</v>
+        <v>12</v>
       </c>
       <c r="L26" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>4.32</v>
+        <v>71.92</v>
       </c>
       <c r="N26" t="n">
-        <v>1089</v>
+        <v>863</v>
       </c>
       <c r="O26" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,089 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($863 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quilt Napa Cabernet Sauvignon 750ml</t>
+          <t>Barefoot Pink Moscato 750ml</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>859889006005</t>
+          <t>085000020456</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="F27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="G27" t="n">
-        <v>30</v>
+        <v>-14</v>
       </c>
       <c r="H27" t="n">
-        <v>1.5</v>
+        <v>26.2</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K27" t="n">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="L27" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M27" t="n">
-        <v>33.39</v>
+        <v>4.32</v>
       </c>
       <c r="N27" t="n">
-        <v>7213</v>
+        <v>1089</v>
       </c>
       <c r="O27" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Large buy ($7,213) - confirm; Buy-month stock-up ($7,213 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,089 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Robert Mondavi PS Cab Sauv BB 750ml</t>
+          <t>Summit Pinot Grigio 3L Box</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>086003780217</t>
+          <t>083120015444</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -9460,130 +9852,130 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="F28" t="n">
-        <v>9.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="H28" t="n">
-        <v>12.2</v>
+        <v>11.2</v>
       </c>
       <c r="I28" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J28" t="n">
         <v>6</v>
       </c>
       <c r="K28" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="L28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>8.699999999999999</v>
+        <v>11.19</v>
       </c>
       <c r="N28" t="n">
-        <v>417</v>
+        <v>67</v>
       </c>
       <c r="O28" t="n">
-        <v>42</v>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>In buy-month (Feb, May, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($417 to next deal) - confirm</t>
+          <t>Overstocked (9 wks on hand) - confirm before buying more; Seasonal - last year ~11/wk vs 6 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Barefoot Sauv Blanc 750ml</t>
+          <t>Quilt Napa Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>018341751024</t>
+          <t>859889006005</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="F29" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H29" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J29" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>132</v>
+        <v>216</v>
       </c>
       <c r="L29" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M29" t="n">
-        <v>4.34</v>
+        <v>33.39</v>
       </c>
       <c r="N29" t="n">
-        <v>573</v>
+        <v>7213</v>
       </c>
       <c r="O29" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($573 to next deal) - confirm</t>
+          <t>Large buy ($7,213) - confirm; Buy-month stock-up ($7,213 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Four Graces Pinot Noir 750ml</t>
+          <t>Robert Mondavi PS Cab Sauv BB 750ml</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>185977000076</t>
+          <t>086003780217</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -9592,154 +9984,154 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>17</v>
+        <v>-7</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K30" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M30" t="n">
-        <v>16.67</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>200</v>
+        <v>417</v>
       </c>
       <c r="O30" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, May, Aug, Sep, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($200 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($417 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Frank Family Cabernet 750ml</t>
+          <t>Barefoot Sauv Blanc 750ml</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>894910000409</t>
+          <t>018341751024</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="F31" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="I31" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K31" t="n">
-        <v>12</v>
+        <v>132</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M31" t="n">
-        <v>38</v>
+        <v>4.34</v>
       </c>
       <c r="N31" t="n">
-        <v>456</v>
+        <v>573</v>
       </c>
       <c r="O31" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($456 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($573 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Underwood Rose 375ml</t>
+          <t>Four Graces Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>856036001074</t>
+          <t>185977000076</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="F32" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>12</v>
@@ -9748,64 +10140,64 @@
         <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>4.17</v>
+        <v>16.67</v>
       </c>
       <c r="N32" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="O32" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, May, Aug, Sep, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($50 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($200 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Apothic White 750ml</t>
+          <t>Frank Family Cabernet 750ml</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>085000019733</t>
+          <t>894910000409</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>White Blends</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="F33" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="G33" t="n">
-        <v>-17</v>
+        <v>45</v>
       </c>
       <c r="H33" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J33" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K33" t="n">
         <v>12</v>
@@ -9814,106 +10206,106 @@
         <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>7.32</v>
+        <v>38</v>
       </c>
       <c r="N33" t="n">
-        <v>88</v>
+        <v>456</v>
       </c>
       <c r="O33" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($456 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Barefoot Peach Moscato 750ml</t>
+          <t>Underwood Rose 375ml</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>085000029008</t>
+          <t>856036001074</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>157</v>
+        <v>76</v>
       </c>
       <c r="F34" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="G34" t="n">
-        <v>-9</v>
+        <v>23</v>
       </c>
       <c r="H34" t="n">
-        <v>26.2</v>
+        <v>2.2</v>
       </c>
       <c r="I34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K34" t="n">
-        <v>168</v>
+        <v>12</v>
       </c>
       <c r="L34" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>2.88</v>
+        <v>4.17</v>
       </c>
       <c r="N34" t="n">
-        <v>484</v>
+        <v>50</v>
       </c>
       <c r="O34" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($484 to next deal) - confirm; Seasonal - last year ~26/wk vs 15 now, buy ahead?</t>
+          <t>Buy-month stock-up ($50 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Barefoot Chardonnay 750ml</t>
+          <t>Apothic White 750ml</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>018341751055</t>
+          <t>085000019733</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>White Blends</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -9922,125 +10314,125 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="F35" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="G35" t="n">
-        <v>4</v>
+        <v>-17</v>
       </c>
       <c r="H35" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J35" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K35" t="n">
-        <v>108</v>
+        <v>12</v>
       </c>
       <c r="L35" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>4.47</v>
+        <v>7.32</v>
       </c>
       <c r="N35" t="n">
-        <v>483</v>
+        <v>88</v>
       </c>
       <c r="O35" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($483 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Charles Smith Kung Fu Girl Riesling 750ml</t>
+          <t>Barefoot Peach Moscato 750ml</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>083120015048</t>
+          <t>085000029008</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>92</v>
+        <v>157</v>
       </c>
       <c r="F36" t="n">
-        <v>11.6</v>
+        <v>10.5</v>
       </c>
       <c r="G36" t="n">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H36" t="n">
-        <v>5.8</v>
+        <v>26.2</v>
       </c>
       <c r="I36" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K36" t="n">
-        <v>12</v>
+        <v>168</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M36" t="n">
-        <v>7.49</v>
+        <v>2.88</v>
       </c>
       <c r="N36" t="n">
-        <v>90</v>
+        <v>484</v>
       </c>
       <c r="O36" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($90 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($484 to next deal) - confirm; Seasonal - last year ~26/wk vs 15 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Decoy Sonoma Chardonnay 750ml</t>
+          <t>Barefoot Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>669576019245</t>
+          <t>018341751055</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -10050,266 +10442,266 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>191</v>
+        <v>104</v>
       </c>
       <c r="F37" t="n">
-        <v>13</v>
+        <v>10.9</v>
       </c>
       <c r="G37" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
-        <v>16.8</v>
+        <v>5.8</v>
       </c>
       <c r="I37" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K37" t="n">
-        <v>12</v>
+        <v>108</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M37" t="n">
-        <v>11.52</v>
+        <v>4.47</v>
       </c>
       <c r="N37" t="n">
-        <v>138</v>
+        <v>483</v>
       </c>
       <c r="O37" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($138 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($483 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LaMarca Prosecco Demi Sec 750ml</t>
+          <t>Charles Smith Kung Fu Girl Riesling 750ml</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>085000040669</t>
+          <t>083120015048</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="F38" t="n">
-        <v>13.2</v>
+        <v>11.6</v>
       </c>
       <c r="G38" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K38" t="n">
-        <v>144</v>
+        <v>12</v>
       </c>
       <c r="L38" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>12.47</v>
+        <v>7.49</v>
       </c>
       <c r="N38" t="n">
-        <v>1796</v>
+        <v>90</v>
       </c>
       <c r="O38" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,796 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($90 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LaMarca Prosecco Rose 750ml</t>
+          <t>Decoy Sonoma Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>085000032442</t>
+          <t>669576019245</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>147</v>
+        <v>191</v>
       </c>
       <c r="F39" t="n">
-        <v>13.7</v>
+        <v>13</v>
       </c>
       <c r="G39" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="H39" t="n">
-        <v>7.8</v>
+        <v>16.8</v>
       </c>
       <c r="I39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>144</v>
+        <v>12</v>
       </c>
       <c r="L39" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>12.19</v>
+        <v>11.52</v>
       </c>
       <c r="N39" t="n">
-        <v>1755</v>
+        <v>138</v>
       </c>
       <c r="O39" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,755 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($138 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Belle Glos Clark &amp; Telephone 750ml</t>
+          <t>LaMarca Prosecco Demi Sec 750ml</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>855622000118</t>
+          <t>085000040669</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>29</v>
+        <v>139</v>
       </c>
       <c r="F40" t="n">
-        <v>13.8</v>
+        <v>13.2</v>
       </c>
       <c r="G40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
         <v>4</v>
       </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1</v>
-      </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>48</v>
+        <v>144</v>
       </c>
       <c r="L40" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M40" t="n">
-        <v>32.89</v>
+        <v>12.47</v>
       </c>
       <c r="N40" t="n">
-        <v>1579</v>
+        <v>1796</v>
       </c>
       <c r="O40" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,579 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,796 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Barefoot Pineapple Moscato 750ml</t>
+          <t>LaMarca Prosecco Rose 750ml</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>085000033319</t>
+          <t>085000032442</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -10318,125 +10710,125 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>39</v>
+        <v>147</v>
       </c>
       <c r="F41" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="G41" t="n">
-        <v>-23</v>
+        <v>9</v>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K41" t="n">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M41" t="n">
-        <v>4.36</v>
+        <v>12.19</v>
       </c>
       <c r="N41" t="n">
-        <v>105</v>
+        <v>1755</v>
       </c>
       <c r="O41" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($105 to next deal) - confirm; Seasonal - last year ~5/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($1,755 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Barefoot Rose 750ml</t>
+          <t>Belle Glos Clark &amp; Telephone 750ml</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>085000025871</t>
+          <t>855622000118</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="F42" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="G42" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>10.5</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>48</v>
+      </c>
+      <c r="L42" t="n">
+        <v>4</v>
+      </c>
+      <c r="M42" t="n">
+        <v>32.89</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1579</v>
+      </c>
+      <c r="O42" t="n">
         <v>11</v>
-      </c>
-      <c r="J42" t="n">
-        <v>11</v>
-      </c>
-      <c r="K42" t="n">
-        <v>60</v>
-      </c>
-      <c r="L42" t="n">
-        <v>5</v>
-      </c>
-      <c r="M42" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N42" t="n">
-        <v>264</v>
-      </c>
-      <c r="O42" t="n">
-        <v>45</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($264 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,579 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Barefoot Watermelon Moscato 750ml</t>
+          <t>Barefoot Pineapple Moscato 750ml</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>085000029923</t>
+          <t>085000033319</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -10450,37 +10842,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F43" t="n">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="H43" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>4.31</v>
+        <v>4.36</v>
       </c>
       <c r="N43" t="n">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="O43" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
@@ -10490,24 +10882,24 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($105 to next deal) - confirm; Seasonal - last year ~5/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Barefoot Mango Moscato 750ml</t>
+          <t>Barefoot Rose 750ml</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>085000032176</t>
+          <t>085000025871</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -10516,37 +10908,37 @@
         </is>
       </c>
       <c r="E44" t="n">
+        <v>108</v>
+      </c>
+      <c r="F44" t="n">
+        <v>14</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H44" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I44" t="n">
+        <v>11</v>
+      </c>
+      <c r="J44" t="n">
+        <v>11</v>
+      </c>
+      <c r="K44" t="n">
+        <v>60</v>
+      </c>
+      <c r="L44" t="n">
+        <v>5</v>
+      </c>
+      <c r="M44" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N44" t="n">
+        <v>264</v>
+      </c>
+      <c r="O44" t="n">
         <v>45</v>
-      </c>
-      <c r="F44" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="G44" t="n">
-        <v>-25</v>
-      </c>
-      <c r="H44" t="n">
-        <v>7</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>24</v>
-      </c>
-      <c r="L44" t="n">
-        <v>2</v>
-      </c>
-      <c r="M44" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="N44" t="n">
-        <v>104</v>
-      </c>
-      <c r="O44" t="n">
-        <v>46</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
@@ -10556,24 +10948,24 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($104 to next deal) - confirm; Seasonal - last year ~7/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($264 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Barefoot Riesling 750ml</t>
+          <t>Barefoot Watermelon Moscato 750ml</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>085000015810</t>
+          <t>085000029923</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -10582,34 +10974,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>127</v>
+        <v>10</v>
       </c>
       <c r="F45" t="n">
-        <v>15.1</v>
+        <v>14.3</v>
       </c>
       <c r="G45" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="I45" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="L45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="N45" t="n">
-        <v>260</v>
+        <v>52</v>
       </c>
       <c r="O45" t="n">
         <v>46</v>
@@ -10622,85 +11014,85 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($260 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Apothic Rose 750ml</t>
+          <t>Summit Red Blend 3L Box</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>085000021545</t>
+          <t>083120015437</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="F46" t="n">
-        <v>15.2</v>
+        <v>14.5</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="H46" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L46" t="n">
         <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>7.1</v>
+        <v>11.19</v>
       </c>
       <c r="N46" t="n">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="O46" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($85 to next deal) - confirm; Seasonal - last year ~5/wk vs 2 now, buy ahead?</t>
+          <t>Overstocked (14 wks on hand) - confirm before buying more; Seasonal - last year ~9/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Barefoot Pear Moscato 750ml</t>
+          <t>Barefoot Mango Moscato 750ml</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>085000037607</t>
+          <t>085000032176</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -10714,22 +11106,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F47" t="n">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="G47" t="n">
-        <v>44</v>
+        <v>-25</v>
       </c>
       <c r="H47" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I47" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>24</v>
@@ -10754,24 +11146,24 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($104 to next deal) - confirm; Seasonal - last year ~5/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($104 to next deal) - confirm; Seasonal - last year ~7/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Barefoot Red Moscato 750ml</t>
+          <t>Barefoot Riesling 750ml</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>085000019894</t>
+          <t>085000015810</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -10780,37 +11172,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="F48" t="n">
-        <v>15.5</v>
+        <v>15.1</v>
       </c>
       <c r="G48" t="n">
-        <v>-7</v>
+        <v>14</v>
       </c>
       <c r="H48" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I48" t="n">
+        <v>10</v>
+      </c>
+      <c r="J48" t="n">
+        <v>10</v>
+      </c>
+      <c r="K48" t="n">
+        <v>60</v>
+      </c>
+      <c r="L48" t="n">
         <v>5</v>
       </c>
-      <c r="I48" t="n">
-        <v>5</v>
-      </c>
-      <c r="J48" t="n">
-        <v>5</v>
-      </c>
-      <c r="K48" t="n">
-        <v>48</v>
-      </c>
-      <c r="L48" t="n">
-        <v>4</v>
-      </c>
       <c r="M48" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="N48" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="O48" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
@@ -10820,45 +11212,45 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($210 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($260 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Stags' Leap Cabernet Sauvignon Napa 750ml</t>
+          <t>Apothic Rose 750ml</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>089819042401</t>
+          <t>085000021545</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="F49" t="n">
-        <v>16.2</v>
+        <v>15.2</v>
       </c>
       <c r="G49" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -10870,40 +11262,40 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>39.9</v>
+        <v>7.1</v>
       </c>
       <c r="N49" t="n">
-        <v>479</v>
+        <v>85</v>
       </c>
       <c r="O49" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($479 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($85 to next deal) - confirm; Seasonal - last year ~5/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Barefoot White Zin 750ml</t>
+          <t>Barefoot Pear Moscato 750ml</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>018341751062</t>
+          <t>085000037607</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10912,37 +11304,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="F50" t="n">
-        <v>17</v>
+        <v>15.2</v>
       </c>
       <c r="G50" t="n">
-        <v>-11</v>
+        <v>44</v>
       </c>
       <c r="H50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I50" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J50" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K50" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>4.38</v>
+        <v>4.32</v>
       </c>
       <c r="N50" t="n">
-        <v>158</v>
+        <v>104</v>
       </c>
       <c r="O50" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
@@ -10952,19 +11344,19 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($158 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($104 to next deal) - confirm; Seasonal - last year ~5/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Barefoot Strawberry Moscato 750ml</t>
+          <t>Barefoot Red Moscato 750ml</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>085000029015</t>
+          <t>085000019894</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -10978,22 +11370,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="F51" t="n">
-        <v>17.3</v>
+        <v>15.5</v>
       </c>
       <c r="G51" t="n">
-        <v>-22</v>
+        <v>-7</v>
       </c>
       <c r="H51" t="n">
-        <v>12.2</v>
+        <v>5</v>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K51" t="n">
         <v>48</v>
@@ -11002,10 +11394,10 @@
         <v>4</v>
       </c>
       <c r="M51" t="n">
-        <v>4.36</v>
+        <v>4.38</v>
       </c>
       <c r="N51" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O51" t="n">
         <v>45</v>
@@ -11018,156 +11410,156 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($209 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($210 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Quilt Threadcount Red Blend 750ml</t>
+          <t>Stags' Leap Cabernet Sauvignon Napa 750ml</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>860009046009</t>
+          <t>089819042401</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="F52" t="n">
-        <v>17.7</v>
+        <v>16.2</v>
       </c>
       <c r="G52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H52" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="L52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>13.45</v>
+        <v>39.9</v>
       </c>
       <c r="N52" t="n">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="O52" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($484 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($479 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cooks Brut 750ml</t>
+          <t>Barefoot White Zin 750ml</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>083804047211</t>
+          <t>018341751062</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>174</v>
+        <v>115</v>
       </c>
       <c r="F53" t="n">
-        <v>17.8</v>
+        <v>17</v>
       </c>
       <c r="G53" t="n">
-        <v>-36</v>
+        <v>-11</v>
       </c>
       <c r="H53" t="n">
-        <v>15.8</v>
+        <v>4</v>
       </c>
       <c r="I53" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J53" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K53" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M53" t="n">
-        <v>6</v>
+        <v>4.38</v>
       </c>
       <c r="N53" t="n">
-        <v>72</v>
+        <v>158</v>
       </c>
       <c r="O53" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($72 to next deal) - confirm; Seasonal - last year ~16/wk vs 10 now, buy ahead?</t>
+          <t>Buy-month stock-up ($158 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Apothic Crush 750ml</t>
+          <t>Barefoot Strawberry Moscato 750ml</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>085000023488</t>
+          <t>085000029015</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11176,158 +11568,154 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="F54" t="n">
-        <v>18</v>
+        <v>17.3</v>
       </c>
       <c r="G54" t="n">
-        <v>-4</v>
+        <v>-22</v>
       </c>
       <c r="H54" t="n">
-        <v>6.8</v>
+        <v>12.2</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K54" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M54" t="n">
-        <v>6.16</v>
+        <v>4.36</v>
       </c>
       <c r="N54" t="n">
-        <v>74</v>
+        <v>209</v>
       </c>
       <c r="O54" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($74 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($209 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Apothic Cabernet Sauv 750ml</t>
+          <t>Quilt Threadcount Red Blend 750ml</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>085000030967</t>
+          <t>860009046009</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>128</v>
+        <v>33</v>
       </c>
       <c r="F55" t="n">
-        <v>18.3</v>
+        <v>17.7</v>
       </c>
       <c r="G55" t="n">
-        <v>-8</v>
+        <v>9</v>
       </c>
       <c r="H55" t="n">
-        <v>6.5</v>
+        <v>1.2</v>
       </c>
       <c r="I55" t="n">
         <v>4</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K55" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M55" t="n">
-        <v>7.33</v>
+        <v>13.45</v>
       </c>
       <c r="N55" t="n">
-        <v>88</v>
+        <v>484</v>
       </c>
       <c r="O55" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($484 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Underwood Pinot Noir 355ml</t>
+          <t>Cooks Brut 750ml</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>856036001043</t>
+          <t>083804047211</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>87</v>
+        <v>174</v>
       </c>
       <c r="F56" t="n">
-        <v>18.6</v>
+        <v>17.8</v>
       </c>
       <c r="G56" t="n">
-        <v>9</v>
+        <v>-36</v>
       </c>
       <c r="H56" t="n">
-        <v>5.2</v>
+        <v>15.8</v>
       </c>
       <c r="I56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K56" t="n">
         <v>12</v>
@@ -11336,58 +11724,58 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="N56" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="O56" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($72 to next deal) - confirm; Seasonal - last year ~16/wk vs 10 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Acrobat Rose 750ml</t>
+          <t>Apothic Crush 750ml</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>768675116029</t>
+          <t>085000023488</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>54</v>
+        <v>181</v>
       </c>
       <c r="F57" t="n">
-        <v>19.3</v>
+        <v>18</v>
       </c>
       <c r="G57" t="n">
-        <v>9</v>
+        <v>-4</v>
       </c>
       <c r="H57" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="I57" t="n">
         <v>1</v>
@@ -11402,64 +11790,64 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>9.17</v>
+        <v>6.16</v>
       </c>
       <c r="N57" t="n">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="O57" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, May, Aug, Sep, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($110 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($74 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ferrari Carano Fume Blanc 750ml</t>
+          <t>Apothic Cabernet Sauv 750ml</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>742651123102</t>
+          <t>085000030967</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>208</v>
+        <v>128</v>
       </c>
       <c r="F58" t="n">
-        <v>20.7</v>
+        <v>18.3</v>
       </c>
       <c r="G58" t="n">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="H58" t="n">
-        <v>11.8</v>
+        <v>6.5</v>
       </c>
       <c r="I58" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
         <v>12</v>
@@ -11468,64 +11856,68 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>9.99</v>
+        <v>7.33</v>
       </c>
       <c r="N58" t="n">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="O58" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q58" t="inlineStr"/>
+        <v>39</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($120 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Barefoot Bright &amp; Breezy Pinot Grigio 750ml</t>
+          <t>Underwood Pinot Noir 355ml</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>085000032879</t>
+          <t>856036001043</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="F59" t="n">
-        <v>21.4</v>
+        <v>18.6</v>
       </c>
       <c r="G59" t="n">
-        <v>108</v>
+        <v>9</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="I59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K59" t="n">
         <v>12</v>
@@ -11534,61 +11926,61 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>4.47</v>
+        <v>4.33</v>
       </c>
       <c r="N59" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="O59" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($54 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Barefoot Sweet Red 750ml</t>
+          <t>Acrobat Rose 750ml</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>085000018491</t>
+          <t>768675116029</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="F60" t="n">
-        <v>21.4</v>
+        <v>19.3</v>
       </c>
       <c r="G60" t="n">
-        <v>-36</v>
+        <v>9</v>
       </c>
       <c r="H60" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -11600,64 +11992,64 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>4.26</v>
+        <v>9.17</v>
       </c>
       <c r="N60" t="n">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="O60" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, Apr, May, Aug, Sep, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($51 to next deal) - confirm; Seasonal - last year ~6/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($110 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Barefoot Merlot 750ml</t>
+          <t>Ferrari Carano Fume Blanc 750ml</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>018341751109</t>
+          <t>742651123102</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Merlot</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>86</v>
+        <v>208</v>
       </c>
       <c r="F61" t="n">
-        <v>24.6</v>
+        <v>20.7</v>
       </c>
       <c r="G61" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="H61" t="n">
-        <v>2.5</v>
+        <v>11.8</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K61" t="n">
         <v>12</v>
@@ -11666,40 +12058,40 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>4.4</v>
+        <v>9.99</v>
       </c>
       <c r="N61" t="n">
-        <v>53</v>
+        <v>120</v>
       </c>
       <c r="O61" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($53 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($120 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Boen Tri Appellation Chardonnay 750ml</t>
+          <t>Conundrum Red 750ml</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>856184006310</t>
+          <t>017224760122</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -11708,19 +12100,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>23</v>
+        <v>479</v>
       </c>
       <c r="F62" t="n">
-        <v>24.6</v>
+        <v>21.2</v>
       </c>
       <c r="G62" t="n">
-        <v>140</v>
+        <v>-1</v>
       </c>
       <c r="H62" t="n">
-        <v>1.8</v>
+        <v>24.2</v>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -11732,127 +12124,127 @@
         <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>11.92</v>
+        <v>6.59</v>
       </c>
       <c r="N62" t="n">
-        <v>143</v>
+        <v>79</v>
       </c>
       <c r="O62" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($143 to next deal) - confirm</t>
+          <t>Overstocked (21 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Belle Glos Dairyman Pinot Noir 750ml</t>
+          <t>Barefoot Bright &amp; Breezy Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>855622000811</t>
+          <t>085000032879</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F63" t="n">
-        <v>25.2</v>
+        <v>21.4</v>
       </c>
       <c r="G63" t="n">
-        <v>-8</v>
+        <v>108</v>
       </c>
       <c r="H63" t="n">
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>31.77</v>
+        <v>4.47</v>
       </c>
       <c r="N63" t="n">
-        <v>763</v>
+        <v>54</v>
       </c>
       <c r="O63" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($763 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($54 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Saldo Zinfandel 750ml</t>
+          <t>Barefoot Sweet Red 750ml</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>086003258006</t>
+          <t>085000018491</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="F64" t="n">
-        <v>27.4</v>
+        <v>21.4</v>
       </c>
       <c r="G64" t="n">
-        <v>-12</v>
+        <v>-36</v>
       </c>
       <c r="H64" t="n">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -11864,40 +12256,40 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>20.35</v>
+        <v>4.26</v>
       </c>
       <c r="N64" t="n">
-        <v>244</v>
+        <v>51</v>
       </c>
       <c r="O64" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($244 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($51 to next deal) - confirm; Seasonal - last year ~6/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LaMarca Prosecco Rose 187ml</t>
+          <t>Barefoot Merlot 750ml</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>085000034705</t>
+          <t>018341751109</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -11906,16 +12298,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="F65" t="n">
-        <v>28.9</v>
+        <v>24.6</v>
       </c>
       <c r="G65" t="n">
-        <v>-54</v>
+        <v>-10</v>
       </c>
       <c r="H65" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="I65" t="n">
         <v>1</v>
@@ -11924,46 +12316,46 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>4.53</v>
+        <v>4.4</v>
       </c>
       <c r="N65" t="n">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="O65" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($109 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($53 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Risata Moscato d'Asti 1.5L</t>
+          <t>Boen Tri Appellation Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>084279989266</t>
+          <t>856184006310</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Moscato</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11972,130 +12364,130 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="F66" t="n">
-        <v>32.9</v>
+        <v>24.6</v>
       </c>
       <c r="G66" t="n">
-        <v>-31</v>
+        <v>140</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L66" t="n">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>19.32</v>
+        <v>11.92</v>
       </c>
       <c r="N66" t="n">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="O66" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Overstocked (33 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($143 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Apothic Merlot 750ml</t>
+          <t>Belle Glos Dairyman Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>085000032145</t>
+          <t>855622000811</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Merlot</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>147</v>
+        <v>47</v>
       </c>
       <c r="F67" t="n">
-        <v>35</v>
+        <v>25.2</v>
       </c>
       <c r="G67" t="n">
-        <v>6</v>
+        <v>-8</v>
       </c>
       <c r="H67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M67" t="n">
-        <v>7.37</v>
+        <v>31.77</v>
       </c>
       <c r="N67" t="n">
-        <v>88</v>
+        <v>763</v>
       </c>
       <c r="O67" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($763 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kim Crawford Pinot Grigio 750ml</t>
+          <t>Saldo Zinfandel 750ml</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>689352010310</t>
+          <t>086003258006</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -12104,19 +12496,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="F68" t="n">
-        <v>37.1</v>
+        <v>27.4</v>
       </c>
       <c r="G68" t="n">
-        <v>18</v>
+        <v>-12</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -12128,13 +12520,13 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>10.7</v>
+        <v>20.35</v>
       </c>
       <c r="N68" t="n">
-        <v>128</v>
+        <v>244</v>
       </c>
       <c r="O68" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
@@ -12144,19 +12536,19 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($128 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($244 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>90+ Cellars Prosecco Rose (3pk) 187ml</t>
+          <t>LaMarca Prosecco Rose 187ml</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>810879023655</t>
+          <t>085000034705</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -12166,20 +12558,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>136.66</v>
+        <v>27</v>
       </c>
       <c r="F69" t="n">
-        <v>41.8</v>
+        <v>28.9</v>
       </c>
       <c r="G69" t="n">
-        <v>-25</v>
+        <v>-54</v>
       </c>
       <c r="H69" t="n">
-        <v>6.2</v>
+        <v>2.2</v>
       </c>
       <c r="I69" t="n">
         <v>1</v>
@@ -12188,64 +12580,64 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="L69" t="n">
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>9.25</v>
+        <v>4.53</v>
       </c>
       <c r="N69" t="n">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="O69" t="n">
-        <v>58</v>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+        </is>
+      </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Overstocked (42 wks on hand) - confirm before buying more; Seasonal - last year ~6/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($109 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Apothic Inferno 750ml</t>
+          <t>Risata Moscato d'Asti 1.5L</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>085000024904</t>
+          <t>084279989266</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Moscato</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>217</v>
+        <v>69</v>
       </c>
       <c r="F70" t="n">
-        <v>46.5</v>
+        <v>32.9</v>
       </c>
       <c r="G70" t="n">
-        <v>-37</v>
+        <v>-31</v>
       </c>
       <c r="H70" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
         <v>2</v>
@@ -12254,70 +12646,70 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L70" t="n">
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>8.59</v>
+        <v>19.32</v>
       </c>
       <c r="N70" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="O70" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($103 to next deal) - confirm</t>
+          <t>Overstocked (33 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Harken Chardonnay 750ml</t>
+          <t>Apothic Merlot 750ml</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>847159001812</t>
+          <t>085000032145</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>236</v>
+        <v>147</v>
       </c>
       <c r="F71" t="n">
-        <v>50.6</v>
+        <v>35</v>
       </c>
       <c r="G71" t="n">
-        <v>-14</v>
+        <v>6</v>
       </c>
       <c r="H71" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I71" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K71" t="n">
         <v>12</v>
@@ -12326,21 +12718,351 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>5.93</v>
+        <v>7.37</v>
       </c>
       <c r="N71" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="O71" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Kim Crawford Pinot Grigio 750ml</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>689352010310</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Pinot Grigio/Gris</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>130</v>
+      </c>
+      <c r="F72" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>18</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>12</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="N72" t="n">
+        <v>128</v>
+      </c>
+      <c r="O72" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Buy-month stock-up ($128 to next deal) - confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>90+ Cellars Prosecco Rose (3pk) 187ml</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>810879023655</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Sparkling</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Bellboy Corporation</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>136.66</v>
+      </c>
+      <c r="F73" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-25</v>
+      </c>
+      <c r="H73" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>8</v>
+      </c>
+      <c r="L73" t="n">
+        <v>1</v>
+      </c>
+      <c r="M73" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="N73" t="n">
+        <v>74</v>
+      </c>
+      <c r="O73" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Overstocked (42 wks on hand) - confirm before buying more; Seasonal - last year ~6/wk vs 3 now, buy ahead?</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Summit Sauvignon Blanc 3L Box</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>083120016403</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Sauvignon Blanc</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>32</v>
+      </c>
+      <c r="F74" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="G74" t="n">
+        <v>-77</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>2</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>6</v>
+      </c>
+      <c r="L74" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="N74" t="n">
+        <v>67</v>
+      </c>
+      <c r="O74" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Overstocked (46 wks on hand) - confirm before buying more</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Apothic Inferno 750ml</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>085000024904</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Red Blends</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>217</v>
+      </c>
+      <c r="F75" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-37</v>
+      </c>
+      <c r="H75" t="n">
+        <v>5</v>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>12</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>8.59</v>
+      </c>
+      <c r="N75" t="n">
+        <v>103</v>
+      </c>
+      <c r="O75" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Buy-month stock-up ($103 to next deal) - confirm</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Harken Chardonnay 750ml</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>847159001812</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Chardonnay</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>236</v>
+      </c>
+      <c r="F76" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H76" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I76" t="n">
+        <v>3</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>12</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="N76" t="n">
+        <v>71</v>
+      </c>
+      <c r="O76" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
+        <is>
           <t>In buy-month (Jan, Mar, Jul, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>Buy-month stock-up ($71 to next deal) - confirm</t>
         </is>

--- a/data/Wine Recommended Order.xlsx
+++ b/data/Wine Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2520,21 +2520,25 @@
         <v>28</v>
       </c>
       <c r="K36" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="L36" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M36" t="n">
         <v>7.92</v>
       </c>
       <c r="N36" t="n">
-        <v>380</v>
+        <v>760</v>
       </c>
       <c r="O36" t="n">
         <v>34</v>
       </c>
-      <c r="Q36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
     </row>
@@ -3124,21 +3128,25 @@
         <v>74</v>
       </c>
       <c r="K46" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M46" t="n">
         <v>8.289999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>199</v>
+        <v>497</v>
       </c>
       <c r="O46" t="n">
         <v>36</v>
       </c>
-      <c r="Q46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
     </row>
@@ -3505,12 +3513,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Barefoot Pinot Grigio 750ml</t>
+          <t>Il Valore Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>085000014448</t>
+          <t>015643744785</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3520,68 +3528,64 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Rue 38 LLC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100</v>
+        <v>349</v>
       </c>
       <c r="F53" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="G53" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H53" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="I53" t="n">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="J53" t="n">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="K53" t="n">
-        <v>408</v>
+        <v>36</v>
       </c>
       <c r="L53" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="M53" t="n">
-        <v>4.32</v>
+        <v>7.08</v>
       </c>
       <c r="N53" t="n">
-        <v>1763</v>
+        <v>255</v>
       </c>
       <c r="O53" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($1,763 to next deal) - confirm</t>
-        </is>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LaMarca Prosecco 750ml</t>
+          <t>Barefoot Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>085000017739</t>
+          <t>085000014448</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3590,64 +3594,64 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>992</v>
+        <v>100</v>
       </c>
       <c r="F54" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="G54" t="n">
-        <v>-14</v>
+        <v>20</v>
       </c>
       <c r="H54" t="n">
-        <v>163.5</v>
+        <v>25</v>
       </c>
       <c r="I54" t="n">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="J54" t="n">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="K54" t="n">
-        <v>3864</v>
+        <v>408</v>
       </c>
       <c r="L54" t="n">
-        <v>322</v>
+        <v>34</v>
       </c>
       <c r="M54" t="n">
-        <v>9.949999999999999</v>
+        <v>4.32</v>
       </c>
       <c r="N54" t="n">
-        <v>38444</v>
+        <v>1763</v>
       </c>
       <c r="O54" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Large buy ($38,444) - confirm; Buy-month stock-up ($38,444 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,763 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Apothic Red 750ml</t>
+          <t>LaMarca Prosecco 750ml</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>085000017746</t>
+          <t>085000017739</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3656,64 +3660,64 @@
         </is>
       </c>
       <c r="E55" t="n">
+        <v>992</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H55" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="I55" t="n">
+        <v>106</v>
+      </c>
+      <c r="J55" t="n">
+        <v>106</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3864</v>
+      </c>
+      <c r="L55" t="n">
         <v>322</v>
       </c>
-      <c r="F55" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H55" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="I55" t="n">
-        <v>15</v>
-      </c>
-      <c r="J55" t="n">
-        <v>13</v>
-      </c>
-      <c r="K55" t="n">
-        <v>204</v>
-      </c>
-      <c r="L55" t="n">
-        <v>17</v>
-      </c>
       <c r="M55" t="n">
-        <v>6.46</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>1318</v>
+        <v>38444</v>
       </c>
       <c r="O55" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,318 to next deal) - confirm</t>
+          <t>Large buy ($38,444) - confirm; Buy-month stock-up ($38,444 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LaMarca Prosecco 3 Pack 187ml</t>
+          <t>Apothic Red 750ml</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>085000322437</t>
+          <t>085000017746</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3722,154 +3726,154 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>118.76</v>
+        <v>322</v>
       </c>
       <c r="F56" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="G56" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="H56" t="n">
-        <v>17.8</v>
+        <v>74.8</v>
       </c>
       <c r="I56" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J56" t="n">
         <v>13</v>
       </c>
       <c r="K56" t="n">
-        <v>448</v>
+        <v>204</v>
       </c>
       <c r="L56" t="n">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="M56" t="n">
-        <v>12.02</v>
+        <v>6.46</v>
       </c>
       <c r="N56" t="n">
-        <v>5385</v>
+        <v>1318</v>
       </c>
       <c r="O56" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Large buy ($5,385) - confirm; Buy-month stock-up ($5,385 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,318 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Frank Family Cabernet 750ml</t>
+          <t>LaMarca Prosecco 3 Pack 187ml</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>894910000409</t>
+          <t>085000322437</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>30</v>
+        <v>118.76</v>
       </c>
       <c r="F57" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="G57" t="n">
-        <v>67</v>
+        <v>-6</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>17.8</v>
       </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J57" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K57" t="n">
-        <v>12</v>
+        <v>448</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="M57" t="n">
-        <v>37.44</v>
+        <v>12.02</v>
       </c>
       <c r="N57" t="n">
-        <v>449</v>
+        <v>5385</v>
       </c>
       <c r="O57" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($449 to next deal) - confirm</t>
+          <t>Large buy ($5,385) - confirm; Buy-month stock-up ($5,385 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Santa Margherita Pinot Grigio 750ml</t>
+          <t>La Vieille Ferme Rose 750ml</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>086891022871</t>
+          <t>089419000177</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>The Wine Company</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>258</v>
+        <v>545</v>
       </c>
       <c r="F58" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="G58" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H58" t="n">
-        <v>36.8</v>
+        <v>49.2</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K58" t="n">
         <v>12</v>
@@ -3878,106 +3882,102 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>19.35</v>
+        <v>6.13</v>
       </c>
       <c r="N58" t="n">
-        <v>232</v>
+        <v>74</v>
       </c>
       <c r="O58" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>In buy-month (Mar, May, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($232 to next deal) - confirm</t>
-        </is>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Colle Corviano Cerasuolo Rose 750ml</t>
+          <t>Frank Family Cabernet 750ml</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>181856000892</t>
+          <t>894910000409</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Small Lot MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="F59" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="G59" t="n">
-        <v>-33</v>
+        <v>67</v>
       </c>
       <c r="H59" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="J59" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K59" t="n">
-        <v>372</v>
+        <v>12</v>
       </c>
       <c r="L59" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>6</v>
+        <v>37.44</v>
       </c>
       <c r="N59" t="n">
-        <v>2233</v>
+        <v>449</v>
       </c>
       <c r="O59" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, May, Jun, Jul, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($2,233 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($449 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Conundrum Red 750ml</t>
+          <t>Santa Margherita Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>017224760122</t>
+          <t>086891022871</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3986,22 +3986,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>366</v>
+        <v>258</v>
       </c>
       <c r="F60" t="n">
-        <v>7.9</v>
+        <v>6.8</v>
       </c>
       <c r="G60" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="H60" t="n">
-        <v>19.5</v>
+        <v>36.8</v>
       </c>
       <c r="I60" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K60" t="n">
         <v>12</v>
@@ -4010,318 +4010,326 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>6.23</v>
+        <v>19.35</v>
       </c>
       <c r="N60" t="n">
-        <v>75</v>
+        <v>232</v>
       </c>
       <c r="O60" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>ON AD - Sunday special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>In buy-month (Mar, May, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Buy-month stock-up ($232 to next deal) - confirm</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Pacific Rim Sweet Riesling 750ml</t>
+          <t>Colle Corviano Cerasuolo Rose 750ml</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>899552102276</t>
+          <t>181856000892</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Small Lot MN</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="F61" t="n">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
       <c r="G61" t="n">
-        <v>25</v>
+        <v>-33</v>
       </c>
       <c r="H61" t="n">
-        <v>3.8</v>
+        <v>9</v>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K61" t="n">
-        <v>24</v>
+        <v>372</v>
       </c>
       <c r="L61" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="M61" t="n">
-        <v>5.44</v>
+        <v>6</v>
       </c>
       <c r="N61" t="n">
-        <v>131</v>
+        <v>2233</v>
       </c>
       <c r="O61" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Feb, Jul, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Apr, May, Jun, Jul, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($131 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($2,233 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Barefoot Pink Moscato 750ml</t>
+          <t>Pacific Rim Sweet Riesling 750ml</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>085000020456</t>
+          <t>899552102276</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="F62" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="G62" t="n">
-        <v>-8</v>
+        <v>25</v>
       </c>
       <c r="H62" t="n">
-        <v>36</v>
+        <v>3.8</v>
       </c>
       <c r="I62" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J62" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K62" t="n">
-        <v>264</v>
+        <v>24</v>
       </c>
       <c r="L62" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="M62" t="n">
-        <v>4.32</v>
+        <v>5.44</v>
       </c>
       <c r="N62" t="n">
-        <v>1141</v>
+        <v>131</v>
       </c>
       <c r="O62" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Jan, Feb, Jul, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,141 to next deal) - confirm; Seasonal - last year ~36/wk vs 20 now, buy ahead?</t>
+          <t>Buy-month stock-up ($131 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Underwood Pinot Gris 375ml</t>
+          <t>Barefoot Pink Moscato 750ml</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>856036001067</t>
+          <t>085000020456</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>99</v>
+        <v>181</v>
       </c>
       <c r="F63" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="G63" t="n">
-        <v>53</v>
+        <v>-8</v>
       </c>
       <c r="H63" t="n">
-        <v>8.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J63" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K63" t="n">
-        <v>12</v>
+        <v>264</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="M63" t="n">
-        <v>4.27</v>
+        <v>4.32</v>
       </c>
       <c r="N63" t="n">
-        <v>51</v>
+        <v>1141</v>
       </c>
       <c r="O63" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($51 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,141 to next deal) - confirm; Seasonal - last year ~36/wk vs 20 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Barefoot Sauv Blanc 750ml</t>
+          <t>Underwood Pinot Gris 375ml</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>018341751024</t>
+          <t>856036001067</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="F64" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="G64" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="H64" t="n">
-        <v>3.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J64" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K64" t="n">
-        <v>156</v>
+        <v>12</v>
       </c>
       <c r="L64" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="N64" t="n">
-        <v>676</v>
+        <v>51</v>
       </c>
       <c r="O64" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($676 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($51 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ferrari Carano Chardonnay 750ml</t>
+          <t>Barefoot Sauv Blanc 750ml</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>742651107195</t>
+          <t>018341751024</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E65" t="n">
         <v>113</v>
       </c>
       <c r="F65" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="H65" t="n">
-        <v>8.5</v>
+        <v>3.5</v>
       </c>
       <c r="I65" t="n">
         <v>11</v>
@@ -4330,107 +4338,107 @@
         <v>8</v>
       </c>
       <c r="K65" t="n">
-        <v>12</v>
+        <v>156</v>
       </c>
       <c r="L65" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M65" t="n">
-        <v>13.8</v>
+        <v>4.33</v>
       </c>
       <c r="N65" t="n">
-        <v>166</v>
+        <v>676</v>
       </c>
       <c r="O65" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($166 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($676 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Barefoot Moscato 750ml</t>
+          <t>Ferrari Carano Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>085000016688</t>
+          <t>742651107195</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Moscato</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="F66" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="G66" t="n">
-        <v>-16</v>
+        <v>11</v>
       </c>
       <c r="H66" t="n">
-        <v>30</v>
+        <v>8.5</v>
       </c>
       <c r="I66" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J66" t="n">
+        <v>8</v>
+      </c>
+      <c r="K66" t="n">
         <v>12</v>
       </c>
-      <c r="K66" t="n">
-        <v>204</v>
-      </c>
       <c r="L66" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>4.35</v>
+        <v>13.8</v>
       </c>
       <c r="N66" t="n">
-        <v>887</v>
+        <v>166</v>
       </c>
       <c r="O66" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($887 to next deal) - confirm; Seasonal - last year ~30/wk vs 16 now, buy ahead?</t>
+          <t>Buy-month stock-up ($166 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Risata Moscato d'Asti 750ml</t>
+          <t>Barefoot Moscato 750ml</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>084279977638</t>
+          <t>085000016688</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4440,170 +4448,170 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>422.9996</v>
+        <v>156</v>
       </c>
       <c r="F67" t="n">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
       <c r="G67" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="H67" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K67" t="n">
-        <v>120</v>
+        <v>204</v>
       </c>
       <c r="L67" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M67" t="n">
-        <v>0.87</v>
+        <v>4.35</v>
       </c>
       <c r="N67" t="n">
-        <v>104</v>
+        <v>887</v>
       </c>
       <c r="O67" t="n">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
-          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($104 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($887 to next deal) - confirm; Seasonal - last year ~30/wk vs 16 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Charles Smith Kung Fu Girl Riesling 750ml</t>
+          <t>Risata Moscato d'Asti 750ml</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>083120015048</t>
+          <t>084279977638</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Moscato</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>87</v>
+        <v>422.9996</v>
       </c>
       <c r="F68" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="G68" t="n">
-        <v>11</v>
+        <v>-15</v>
       </c>
       <c r="H68" t="n">
-        <v>5.5</v>
+        <v>42</v>
       </c>
       <c r="I68" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="L68" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M68" t="n">
-        <v>7.49</v>
+        <v>0.87</v>
       </c>
       <c r="N68" t="n">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="O68" t="n">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($180 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($104 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Barefoot Apple Moscato 750ml</t>
+          <t>Charles Smith Kung Fu Girl Riesling 750ml</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>085000029022</t>
+          <t>083120015048</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="F69" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="G69" t="n">
         <v>11</v>
       </c>
-      <c r="G69" t="n">
-        <v>-15</v>
-      </c>
       <c r="H69" t="n">
-        <v>14.8</v>
+        <v>5.5</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K69" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="L69" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M69" t="n">
-        <v>4.35</v>
+        <v>7.49</v>
       </c>
       <c r="N69" t="n">
-        <v>313</v>
+        <v>180</v>
       </c>
       <c r="O69" t="n">
         <v>46</v>
@@ -4611,314 +4619,314 @@
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($313 to next deal) - confirm; Seasonal - last year ~15/wk vs 6 now, buy ahead?</t>
+          <t>Buy-month stock-up ($180 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Robert Mondavi PS Cab Sauv BB 750ml</t>
+          <t>Barefoot Apple Moscato 750ml</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>086003780217</t>
+          <t>085000029022</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>127</v>
+        <v>64</v>
       </c>
       <c r="F70" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="G70" t="n">
-        <v>-5</v>
+        <v>-15</v>
       </c>
       <c r="H70" t="n">
-        <v>13.2</v>
+        <v>14.8</v>
       </c>
       <c r="I70" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M70" t="n">
-        <v>8.69</v>
+        <v>4.35</v>
       </c>
       <c r="N70" t="n">
-        <v>209</v>
+        <v>313</v>
       </c>
       <c r="O70" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($209 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($313 to next deal) - confirm; Seasonal - last year ~15/wk vs 6 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Barefoot Rose 750ml</t>
+          <t>Robert Mondavi PS Cab Sauv BB 750ml</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>085000025871</t>
+          <t>086003780217</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="F71" t="n">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="G71" t="n">
-        <v>18</v>
+        <v>-5</v>
       </c>
       <c r="H71" t="n">
-        <v>11.5</v>
+        <v>13.2</v>
       </c>
       <c r="I71" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="J71" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K71" t="n">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="L71" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M71" t="n">
-        <v>4.39</v>
+        <v>8.69</v>
       </c>
       <c r="N71" t="n">
-        <v>475</v>
+        <v>209</v>
       </c>
       <c r="O71" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($475 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($209 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Kim Crawford Sauvignon Blanc Illuminate 750ml</t>
+          <t>Barefoot Rose 750ml</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>689352010082</t>
+          <t>085000025871</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="F72" t="n">
-        <v>11.7</v>
+        <v>11.4</v>
       </c>
       <c r="G72" t="n">
+        <v>18</v>
+      </c>
+      <c r="H72" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I72" t="n">
         <v>6</v>
       </c>
-      <c r="H72" t="n">
-        <v>14</v>
-      </c>
-      <c r="I72" t="n">
+      <c r="J72" t="n">
+        <v>4</v>
+      </c>
+      <c r="K72" t="n">
+        <v>108</v>
+      </c>
+      <c r="L72" t="n">
         <v>9</v>
       </c>
-      <c r="J72" t="n">
-        <v>5</v>
-      </c>
-      <c r="K72" t="n">
-        <v>24</v>
-      </c>
-      <c r="L72" t="n">
-        <v>2</v>
-      </c>
       <c r="M72" t="n">
-        <v>10.7</v>
+        <v>4.39</v>
       </c>
       <c r="N72" t="n">
-        <v>257</v>
+        <v>475</v>
       </c>
       <c r="O72" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($257 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($475 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Underwood Rose 375ml</t>
+          <t>Kim Crawford Sauvignon Blanc Illuminate 750ml</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>856036001074</t>
+          <t>689352010082</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="F73" t="n">
         <v>11.7</v>
       </c>
       <c r="G73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H73" t="n">
-        <v>3.5</v>
+        <v>14</v>
       </c>
       <c r="I73" t="n">
         <v>9</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K73" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M73" t="n">
-        <v>4.16</v>
+        <v>10.7</v>
       </c>
       <c r="N73" t="n">
-        <v>50</v>
+        <v>257</v>
       </c>
       <c r="O73" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($50 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($257 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Apothic White 750ml</t>
+          <t>Underwood Rose 375ml</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>085000019733</t>
+          <t>856036001074</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>White Blends</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F74" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="G74" t="n">
-        <v>-18</v>
+        <v>5</v>
       </c>
       <c r="H74" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -4930,40 +4938,40 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>7.21</v>
+        <v>4.16</v>
       </c>
       <c r="N74" t="n">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="O74" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($86 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($50 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Barefoot Bright &amp; Breezy Pinot Grigio 750ml</t>
+          <t>Apothic White 750ml</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>085000032879</t>
+          <t>085000019733</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>White Blends</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4972,460 +4980,460 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="F75" t="n">
         <v>11.9</v>
       </c>
       <c r="G75" t="n">
-        <v>133</v>
+        <v>-18</v>
       </c>
       <c r="H75" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="I75" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="L75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>4.5</v>
+        <v>7.21</v>
       </c>
       <c r="N75" t="n">
-        <v>162</v>
+        <v>86</v>
       </c>
       <c r="O75" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($162 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($86 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Risata Prosecco 750ml</t>
+          <t>Barefoot Bright &amp; Breezy Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>084279992464</t>
+          <t>085000032879</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>193</v>
+        <v>39</v>
       </c>
       <c r="F76" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="G76" t="n">
-        <v>-3</v>
+        <v>133</v>
       </c>
       <c r="H76" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M76" t="n">
-        <v>8.960000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="N76" t="n">
-        <v>215</v>
+        <v>162</v>
       </c>
       <c r="O76" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
-          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($215 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($162 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Barefoot Pineapple Moscato 750ml</t>
+          <t>Risata Prosecco 750ml</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>085000033319</t>
+          <t>084279992464</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>36</v>
+        <v>193</v>
       </c>
       <c r="F77" t="n">
-        <v>12.9</v>
+        <v>12</v>
       </c>
       <c r="G77" t="n">
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="H77" t="n">
-        <v>6.8</v>
+        <v>3.2</v>
       </c>
       <c r="I77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M77" t="n">
-        <v>4.36</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="N77" t="n">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="O77" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($157 to next deal) - confirm; Seasonal - last year ~7/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($215 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Quilt Napa Cabernet Sauvignon 750ml</t>
+          <t>Barefoot Pineapple Moscato 750ml</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>859889006005</t>
+          <t>085000033319</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="F78" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="G78" t="n">
-        <v>-2</v>
+        <v>-12</v>
       </c>
       <c r="H78" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I78" t="n">
         <v>3</v>
       </c>
-      <c r="I78" t="n">
-        <v>11</v>
-      </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>144</v>
+        <v>36</v>
       </c>
       <c r="L78" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M78" t="n">
-        <v>33.3</v>
+        <v>4.36</v>
       </c>
       <c r="N78" t="n">
-        <v>4795</v>
+        <v>157</v>
       </c>
       <c r="O78" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Large buy ($4,795) - confirm; Buy-month stock-up ($4,795 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($157 to next deal) - confirm; Seasonal - last year ~7/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Barefoot Peach Moscato 750ml</t>
+          <t>Quilt Napa Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>085000029008</t>
+          <t>859889006005</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>193</v>
+        <v>85</v>
       </c>
       <c r="F79" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="G79" t="n">
         <v>-2</v>
       </c>
       <c r="H79" t="n">
-        <v>31.2</v>
+        <v>3</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="L79" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M79" t="n">
-        <v>3.14</v>
+        <v>33.3</v>
       </c>
       <c r="N79" t="n">
-        <v>415</v>
+        <v>4795</v>
       </c>
       <c r="O79" t="n">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($415 to next deal) - confirm; Seasonal - last year ~31/wk vs 14 now, buy ahead?</t>
+          <t>Large buy ($4,795) - confirm; Buy-month stock-up ($4,795 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Stags' Leap Cabernet Sauvignon Napa 750ml</t>
+          <t>Barefoot Peach Moscato 750ml</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>089819042401</t>
+          <t>085000029008</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>77</v>
+        <v>193</v>
       </c>
       <c r="F80" t="n">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
       <c r="G80" t="n">
-        <v>25</v>
+        <v>-2</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>12</v>
+        <v>132</v>
       </c>
       <c r="L80" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M80" t="n">
-        <v>39.89</v>
+        <v>3.14</v>
       </c>
       <c r="N80" t="n">
-        <v>479</v>
+        <v>415</v>
       </c>
       <c r="O80" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($479 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($415 to next deal) - confirm; Seasonal - last year ~31/wk vs 14 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>LaMarca Prosecco Demi Sec 750ml</t>
+          <t>Stags' Leap Cabernet Sauvignon Napa 750ml</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>085000040669</t>
+          <t>089819042401</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="F81" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="G81" t="n">
-        <v>-11</v>
+        <v>25</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>108</v>
+        <v>12</v>
       </c>
       <c r="L81" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>12.47</v>
+        <v>39.89</v>
       </c>
       <c r="N81" t="n">
-        <v>1347</v>
+        <v>479</v>
       </c>
       <c r="O81" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,347 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($479 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Barefoot Chardonnay 750ml</t>
+          <t>LaMarca Prosecco Demi Sec 750ml</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>018341751055</t>
+          <t>085000040669</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5434,196 +5442,196 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="F82" t="n">
-        <v>15.6</v>
+        <v>14.5</v>
       </c>
       <c r="G82" t="n">
-        <v>22</v>
+        <v>-11</v>
       </c>
       <c r="H82" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J82" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K82" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="L82" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M82" t="n">
-        <v>4.42</v>
+        <v>12.47</v>
       </c>
       <c r="N82" t="n">
-        <v>318</v>
+        <v>1347</v>
       </c>
       <c r="O82" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($318 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,347 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Decoy Limited Alexander Valley Cabernet Sauvignon 750ml</t>
+          <t>Barefoot Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>669576020449</t>
+          <t>018341751055</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>70</v>
+        <v>157</v>
       </c>
       <c r="F83" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="G83" t="n">
-        <v>-17</v>
+        <v>22</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K83" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="L83" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M83" t="n">
-        <v>16</v>
+        <v>4.42</v>
       </c>
       <c r="N83" t="n">
-        <v>192</v>
+        <v>318</v>
       </c>
       <c r="O83" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($192 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($318 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Barefoot White Zin 750ml</t>
+          <t>Decoy Limited Alexander Valley Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>018341751062</t>
+          <t>669576020449</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="F84" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="G84" t="n">
+        <v>-17</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>12</v>
+      </c>
+      <c r="L84" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" t="n">
         <v>16</v>
       </c>
-      <c r="G84" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H84" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>48</v>
-      </c>
-      <c r="L84" t="n">
-        <v>4</v>
-      </c>
-      <c r="M84" t="n">
-        <v>4.37</v>
-      </c>
       <c r="N84" t="n">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="O84" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($210 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($192 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LaMarca Prosecco Rose 750ml</t>
+          <t>Barefoot White Zin 750ml</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>085000032442</t>
+          <t>018341751062</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5632,130 +5640,130 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="F85" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="G85" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="H85" t="n">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>48</v>
+      </c>
+      <c r="L85" t="n">
         <v>4</v>
       </c>
-      <c r="J85" t="n">
-        <v>4</v>
-      </c>
-      <c r="K85" t="n">
-        <v>96</v>
-      </c>
-      <c r="L85" t="n">
-        <v>8</v>
-      </c>
       <c r="M85" t="n">
-        <v>12.29</v>
+        <v>4.37</v>
       </c>
       <c r="N85" t="n">
-        <v>1180</v>
+        <v>210</v>
       </c>
       <c r="O85" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,180 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($210 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Belle Glos Dairyman Pinot Noir 750ml</t>
+          <t>Les Allies Brut Sparkling Rose 750ml</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>855622000811</t>
+          <t>763955408108</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Maverick Beverage Co., LLC - MN</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="F86" t="n">
-        <v>16.8</v>
+        <v>16.2</v>
       </c>
       <c r="G86" t="n">
-        <v>14</v>
+        <v>-14</v>
       </c>
       <c r="H86" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I86" t="n">
+        <v>4</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>12</v>
+      </c>
+      <c r="L86" t="n">
         <v>1</v>
       </c>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>48</v>
-      </c>
-      <c r="L86" t="n">
-        <v>4</v>
-      </c>
       <c r="M86" t="n">
-        <v>31.86</v>
+        <v>5.83</v>
       </c>
       <c r="N86" t="n">
-        <v>1529</v>
+        <v>70</v>
       </c>
       <c r="O86" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,529 to next deal) - confirm</t>
+          <t>Overstocked (16 wks on hand) - confirm before buying more; Seasonal - last year ~14/wk vs 7 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Barefoot Riesling 750ml</t>
+          <t>LaMarca Prosecco Rose 750ml</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>085000015810</t>
+          <t>085000032442</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5764,64 +5772,64 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>119</v>
+        <v>152</v>
       </c>
       <c r="F87" t="n">
-        <v>17</v>
+        <v>16.7</v>
       </c>
       <c r="G87" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="H87" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="I87" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J87" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K87" t="n">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="L87" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M87" t="n">
-        <v>4.33</v>
+        <v>12.29</v>
       </c>
       <c r="N87" t="n">
-        <v>156</v>
+        <v>1180</v>
       </c>
       <c r="O87" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($156 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,180 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Quilt Threadcount Red Blend 750ml</t>
+          <t>Belle Glos Dairyman Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>860009046009</t>
+          <t>855622000811</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5830,37 +5838,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F88" t="n">
-        <v>17.1</v>
+        <v>16.8</v>
       </c>
       <c r="G88" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H88" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>48</v>
+      </c>
+      <c r="L88" t="n">
         <v>4</v>
       </c>
-      <c r="J88" t="n">
-        <v>4</v>
-      </c>
-      <c r="K88" t="n">
-        <v>36</v>
-      </c>
-      <c r="L88" t="n">
-        <v>3</v>
-      </c>
       <c r="M88" t="n">
-        <v>13.42</v>
+        <v>31.86</v>
       </c>
       <c r="N88" t="n">
-        <v>483</v>
+        <v>1529</v>
       </c>
       <c r="O88" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
@@ -5870,24 +5878,24 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($483 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,529 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Apothic Rose 750ml</t>
+          <t>Barefoot Riesling 750ml</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>085000021545</t>
+          <t>085000015810</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -5896,130 +5904,130 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="F89" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="G89" t="n">
-        <v>12</v>
+        <v>-8</v>
       </c>
       <c r="H89" t="n">
-        <v>6.2</v>
+        <v>9.5</v>
       </c>
       <c r="I89" t="n">
+        <v>10</v>
+      </c>
+      <c r="J89" t="n">
+        <v>10</v>
+      </c>
+      <c r="K89" t="n">
+        <v>36</v>
+      </c>
+      <c r="L89" t="n">
         <v>3</v>
       </c>
-      <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="n">
-        <v>12</v>
-      </c>
-      <c r="L89" t="n">
-        <v>1</v>
-      </c>
       <c r="M89" t="n">
-        <v>7.12</v>
+        <v>4.33</v>
       </c>
       <c r="N89" t="n">
-        <v>85</v>
+        <v>156</v>
       </c>
       <c r="O89" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($85 to next deal) - confirm; Seasonal - last year ~6/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($156 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Barefoot Mango Moscato 750ml</t>
+          <t>Quilt Threadcount Red Blend 750ml</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>085000032176</t>
+          <t>860009046009</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="F90" t="n">
-        <v>17.8</v>
+        <v>17.1</v>
       </c>
       <c r="G90" t="n">
-        <v>-9</v>
+        <v>20</v>
       </c>
       <c r="H90" t="n">
-        <v>7.8</v>
+        <v>0.8</v>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K90" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M90" t="n">
-        <v>4.32</v>
+        <v>13.42</v>
       </c>
       <c r="N90" t="n">
-        <v>52</v>
+        <v>483</v>
       </c>
       <c r="O90" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~8/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($483 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Barefoot Red Moscato 750ml</t>
+          <t>Apothic Rose 750ml</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>085000019894</t>
+          <t>085000021545</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6028,13 +6036,13 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="F91" t="n">
-        <v>18.3</v>
+        <v>17.5</v>
       </c>
       <c r="G91" t="n">
-        <v>-20</v>
+        <v>12</v>
       </c>
       <c r="H91" t="n">
         <v>6.2</v>
@@ -6046,64 +6054,64 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>4.38</v>
+        <v>7.12</v>
       </c>
       <c r="N91" t="n">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="O91" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($105 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($85 to next deal) - confirm; Seasonal - last year ~6/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>90+ Cellars Pinot Grigio Trentino 750ml</t>
+          <t>Barefoot Mango Moscato 750ml</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>894655001600</t>
+          <t>085000032176</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>954</v>
+        <v>54</v>
       </c>
       <c r="F92" t="n">
-        <v>18.5</v>
+        <v>17.8</v>
       </c>
       <c r="G92" t="n">
-        <v>7</v>
+        <v>-9</v>
       </c>
       <c r="H92" t="n">
-        <v>67</v>
+        <v>7.8</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -6118,35 +6126,35 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>6.48</v>
+        <v>4.32</v>
       </c>
       <c r="N92" t="n">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="O92" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+        </is>
+      </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Overstocked (18 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~8/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Barefoot Strawberry Moscato 750ml</t>
+          <t>Barefoot Red Moscato 750ml</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>085000029015</t>
+          <t>085000019894</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6160,37 +6168,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>162</v>
+        <v>111</v>
       </c>
       <c r="F93" t="n">
-        <v>18.8</v>
+        <v>18.3</v>
       </c>
       <c r="G93" t="n">
-        <v>-12</v>
+        <v>-20</v>
       </c>
       <c r="H93" t="n">
-        <v>15.5</v>
+        <v>6.2</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="L93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M93" t="n">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="N93" t="n">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="O93" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
@@ -6200,24 +6208,24 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($157 to next deal) - confirm; Seasonal - last year ~16/wk vs 9 now, buy ahead?</t>
+          <t>Buy-month stock-up ($105 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Apothic Cabernet Sauv 750ml</t>
+          <t>Barefoot Strawberry Moscato 750ml</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>085000030967</t>
+          <t>085000029015</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6226,64 +6234,64 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="F94" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="G94" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="H94" t="n">
-        <v>6.8</v>
+        <v>15.5</v>
       </c>
       <c r="I94" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="L94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M94" t="n">
-        <v>7.28</v>
+        <v>4.35</v>
       </c>
       <c r="N94" t="n">
-        <v>87</v>
+        <v>157</v>
       </c>
       <c r="O94" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($87 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($157 to next deal) - confirm; Seasonal - last year ~16/wk vs 9 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Barefoot Watermelon Moscato 750ml</t>
+          <t>Apothic Cabernet Sauv 750ml</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>085000029923</t>
+          <t>085000030967</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6292,19 +6300,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>9</v>
+        <v>132</v>
       </c>
       <c r="F95" t="n">
-        <v>19.3</v>
+        <v>18.9</v>
       </c>
       <c r="G95" t="n">
-        <v>-33</v>
+        <v>-4</v>
       </c>
       <c r="H95" t="n">
-        <v>3.2</v>
+        <v>6.8</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -6316,61 +6324,61 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>4.31</v>
+        <v>7.28</v>
       </c>
       <c r="N95" t="n">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="O95" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~3/wk vs 0 now, buy ahead?</t>
+          <t>Buy-month stock-up ($87 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Creamery Cabernet Sauvignon 750ml</t>
+          <t>Barefoot Watermelon Moscato 750ml</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>847159003588</t>
+          <t>085000029923</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="F96" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="G96" t="n">
-        <v>200</v>
+        <v>-33</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -6382,23 +6390,23 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>7.58</v>
+        <v>4.31</v>
       </c>
       <c r="N96" t="n">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="O96" t="n">
-        <v>57</v>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R96" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+        </is>
+      </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>Overstocked (20 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~3/wk vs 0 now, buy ahead?</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S78"/>
+  <dimension ref="A1:S77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9125,7 +9133,11 @@
       <c r="O18" t="n">
         <v>26</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>In buy-month (Mar, May, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
@@ -10790,12 +10802,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LaMarca Prosecco Rose 750ml</t>
+          <t>Les Allies Brut Sparkling Rose 750ml</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>085000032442</t>
+          <t>763955408108</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -10805,224 +10817,224 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Maverick Beverage Co., LLC - MN</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="F44" t="n">
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
       <c r="G44" t="n">
-        <v>-2</v>
+        <v>-14</v>
       </c>
       <c r="H44" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="I44" t="n">
         <v>4</v>
       </c>
       <c r="J44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="L44" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>12.29</v>
+        <v>5.83</v>
       </c>
       <c r="N44" t="n">
-        <v>1180</v>
+        <v>70</v>
       </c>
       <c r="O44" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,180 to next deal) - confirm</t>
+          <t>Overstocked (16 wks on hand) - confirm before buying more; Seasonal - last year ~14/wk vs 7 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Belle Glos Dairyman Pinot Noir 750ml</t>
+          <t>LaMarca Prosecco Rose 750ml</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>855622000811</t>
+          <t>085000032442</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="F45" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="G45" t="n">
-        <v>14</v>
+        <v>-2</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K45" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="L45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M45" t="n">
-        <v>31.86</v>
+        <v>12.29</v>
       </c>
       <c r="N45" t="n">
-        <v>1529</v>
+        <v>1180</v>
       </c>
       <c r="O45" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,529 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,180 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Barefoot Riesling 750ml</t>
+          <t>Belle Glos Dairyman Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>085000015810</t>
+          <t>855622000811</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>119</v>
+        <v>43</v>
       </c>
       <c r="F46" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="G46" t="n">
-        <v>-8</v>
+        <v>14</v>
       </c>
       <c r="H46" t="n">
-        <v>9.5</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="L46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M46" t="n">
-        <v>4.33</v>
+        <v>31.86</v>
       </c>
       <c r="N46" t="n">
-        <v>156</v>
+        <v>1529</v>
       </c>
       <c r="O46" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($156 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,529 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Quilt Threadcount Red Blend 750ml</t>
+          <t>Barefoot Riesling 750ml</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>860009046009</t>
+          <t>085000015810</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="F47" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="G47" t="n">
-        <v>20</v>
+        <v>-8</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8</v>
+        <v>9.5</v>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J47" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K47" t="n">
         <v>36</v>
@@ -11031,106 +11043,106 @@
         <v>3</v>
       </c>
       <c r="M47" t="n">
-        <v>13.42</v>
+        <v>4.33</v>
       </c>
       <c r="N47" t="n">
-        <v>483</v>
+        <v>156</v>
       </c>
       <c r="O47" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($483 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($156 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Apothic Rose 750ml</t>
+          <t>Quilt Threadcount Red Blend 750ml</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>085000021545</t>
+          <t>860009046009</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="F48" t="n">
-        <v>17.5</v>
+        <v>17.1</v>
       </c>
       <c r="G48" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H48" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="I48" t="n">
+        <v>4</v>
+      </c>
+      <c r="J48" t="n">
+        <v>4</v>
+      </c>
+      <c r="K48" t="n">
+        <v>36</v>
+      </c>
+      <c r="L48" t="n">
         <v>3</v>
       </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>12</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1</v>
-      </c>
       <c r="M48" t="n">
-        <v>7.12</v>
+        <v>13.42</v>
       </c>
       <c r="N48" t="n">
-        <v>85</v>
+        <v>483</v>
       </c>
       <c r="O48" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($85 to next deal) - confirm; Seasonal - last year ~6/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($483 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Barefoot Mango Moscato 750ml</t>
+          <t>Apothic Rose 750ml</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>085000032176</t>
+          <t>085000021545</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -11139,19 +11151,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="G49" t="n">
-        <v>-9</v>
+        <v>12</v>
       </c>
       <c r="H49" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -11163,35 +11175,35 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>4.32</v>
+        <v>7.12</v>
       </c>
       <c r="N49" t="n">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="O49" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~8/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($85 to next deal) - confirm; Seasonal - last year ~6/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Barefoot Red Moscato 750ml</t>
+          <t>Barefoot Mango Moscato 750ml</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>085000019894</t>
+          <t>085000032176</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -11205,37 +11217,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="F50" t="n">
-        <v>18.3</v>
+        <v>17.8</v>
       </c>
       <c r="G50" t="n">
-        <v>-20</v>
+        <v>-9</v>
       </c>
       <c r="H50" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M50" t="n">
-        <v>4.38</v>
+        <v>4.32</v>
       </c>
       <c r="N50" t="n">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="O50" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
@@ -11245,73 +11257,73 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($105 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~8/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>90+ Cellars Pinot Grigio Trentino 750ml</t>
+          <t>Barefoot Red Moscato 750ml</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>894655001600</t>
+          <t>085000019894</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>954</v>
+        <v>111</v>
       </c>
       <c r="F51" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="G51" t="n">
-        <v>7</v>
+        <v>-20</v>
       </c>
       <c r="H51" t="n">
-        <v>67</v>
+        <v>6.2</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
-        <v>6.48</v>
+        <v>4.38</v>
       </c>
       <c r="N51" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="O51" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+        </is>
+      </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Overstocked (18 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($105 to next deal) - confirm</t>
         </is>
       </c>
     </row>
@@ -11516,38 +11528,38 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Creamery Cabernet Sauvignon 750ml</t>
+          <t>Barefoot Sweet Red 750ml</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>847159003588</t>
+          <t>085000018491</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="F55" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="G55" t="n">
-        <v>200</v>
+        <v>-34</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -11559,35 +11571,35 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>7.58</v>
+        <v>4.25</v>
       </c>
       <c r="N55" t="n">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="O55" t="n">
-        <v>57</v>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+        </is>
+      </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Overstocked (20 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($51 to next deal) - confirm; Seasonal - last year ~8/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Barefoot Sweet Red 750ml</t>
+          <t>Barefoot Pear Moscato 750ml</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>085000018491</t>
+          <t>085000037607</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -11601,19 +11613,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="F56" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="G56" t="n">
-        <v>-34</v>
+        <v>29</v>
       </c>
       <c r="H56" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -11625,13 +11637,13 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>4.25</v>
+        <v>4.32</v>
       </c>
       <c r="N56" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O56" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
@@ -11641,48 +11653,48 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($51 to next deal) - confirm; Seasonal - last year ~8/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~8/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Barefoot Pear Moscato 750ml</t>
+          <t>Risata Pink Moscato 750ml</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>085000037607</t>
+          <t>084279988108</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="F57" t="n">
-        <v>20</v>
+        <v>20.9</v>
       </c>
       <c r="G57" t="n">
-        <v>29</v>
+        <v>-20</v>
       </c>
       <c r="H57" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K57" t="n">
         <v>12</v>
@@ -11691,40 +11703,40 @@
         <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>4.32</v>
+        <v>11.02</v>
       </c>
       <c r="N57" t="n">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="O57" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~8/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($132 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Risata Pink Moscato 750ml</t>
+          <t>Pizzolato Rosso 750ml</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>084279988108</t>
+          <t>185554000529</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Other Reds</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11733,22 +11745,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="F58" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="G58" t="n">
-        <v>-20</v>
+        <v>-8</v>
       </c>
       <c r="H58" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
         <v>12</v>
@@ -11757,40 +11769,40 @@
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>11.02</v>
+        <v>9.01</v>
       </c>
       <c r="N58" t="n">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="O58" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
-          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($132 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($108 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Pizzolato Rosso 750ml</t>
+          <t>Pizzolato Cabernet 750ml</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>185554000529</t>
+          <t>185554000352</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Other Reds</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11799,13 +11811,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>114</v>
+        <v>179</v>
       </c>
       <c r="F59" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="G59" t="n">
-        <v>-8</v>
+        <v>3</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -11823,13 +11835,13 @@
         <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>9.01</v>
+        <v>3.77</v>
       </c>
       <c r="N59" t="n">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="O59" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
@@ -11839,48 +11851,48 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($108 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($45 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Pizzolato Cabernet 750ml</t>
+          <t>Barefoot Blueberry Moscato 750ml</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>185554000352</t>
+          <t>085000031780</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="F60" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="G60" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K60" t="n">
         <v>12</v>
@@ -11889,101 +11901,101 @@
         <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>3.77</v>
+        <v>4.2</v>
       </c>
       <c r="N60" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O60" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($45 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($50 to next deal) - confirm; Seasonal - last year ~12/wk vs 6 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Barefoot Blueberry Moscato 750ml</t>
+          <t>Belle Glos Clark &amp; Telephone 750ml</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>085000031780</t>
+          <t>855622000118</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>131</v>
+        <v>36</v>
       </c>
       <c r="F61" t="n">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="G61" t="n">
-        <v>15</v>
+        <v>-22</v>
       </c>
       <c r="H61" t="n">
-        <v>12.2</v>
+        <v>1.8</v>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M61" t="n">
-        <v>4.2</v>
+        <v>32.37</v>
       </c>
       <c r="N61" t="n">
-        <v>50</v>
+        <v>777</v>
       </c>
       <c r="O61" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($50 to next deal) - confirm; Seasonal - last year ~12/wk vs 6 now, buy ahead?</t>
+          <t>Buy-month stock-up ($777 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Belle Glos Clark &amp; Telephone 750ml</t>
+          <t>Decoy Sonoma Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>855622000118</t>
+          <t>669576019221</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -11993,89 +12005,89 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>36</v>
+        <v>171</v>
       </c>
       <c r="F62" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="G62" t="n">
-        <v>-22</v>
+        <v>-4</v>
       </c>
       <c r="H62" t="n">
-        <v>1.8</v>
+        <v>11</v>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M62" t="n">
-        <v>32.37</v>
+        <v>13.1</v>
       </c>
       <c r="N62" t="n">
-        <v>777</v>
+        <v>157</v>
       </c>
       <c r="O62" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($777 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($157 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Decoy Sonoma Pinot Noir 750ml</t>
+          <t>Santa Margherita Chianti Clas</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>669576019221</t>
+          <t>086891077666</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Other Reds</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>171</v>
+        <v>124</v>
       </c>
       <c r="F63" t="n">
-        <v>22.2</v>
+        <v>28</v>
       </c>
       <c r="G63" t="n">
-        <v>-4</v>
+        <v>36</v>
       </c>
       <c r="H63" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -12087,61 +12099,61 @@
         <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>13.1</v>
+        <v>17.84</v>
       </c>
       <c r="N63" t="n">
-        <v>157</v>
+        <v>214</v>
       </c>
       <c r="O63" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Mar, May, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($157 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($214 to next deal) - confirm; Seasonal - last year ~8/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Santa Margherita Chianti Clas</t>
+          <t>Apothic Dark 750ml</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>086891077666</t>
+          <t>085000022863</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Other Reds</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>124</v>
+        <v>26.75</v>
       </c>
       <c r="F64" t="n">
-        <v>28</v>
+        <v>28.7</v>
       </c>
       <c r="G64" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="H64" t="n">
-        <v>8.199999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -12153,40 +12165,40 @@
         <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>17.84</v>
+        <v>7.37</v>
       </c>
       <c r="N64" t="n">
-        <v>214</v>
+        <v>88</v>
       </c>
       <c r="O64" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, May, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($214 to next deal) - confirm; Seasonal - last year ~8/wk vs 4 now, buy ahead?</t>
+          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Apothic Dark 750ml</t>
+          <t>LaMarca Prosecco Rose 187ml</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>085000022863</t>
+          <t>085000034705</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -12195,82 +12207,82 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>26.75</v>
+        <v>27</v>
       </c>
       <c r="F65" t="n">
-        <v>28.7</v>
+        <v>28.9</v>
       </c>
       <c r="G65" t="n">
-        <v>9</v>
+        <v>-43</v>
       </c>
       <c r="H65" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
       <c r="M65" t="n">
-        <v>7.37</v>
+        <v>4.53</v>
       </c>
       <c r="N65" t="n">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="O65" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($109 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LaMarca Prosecco Rose 187ml</t>
+          <t>Ferrari Carano Fume Blanc 750ml</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>085000034705</t>
+          <t>742651123102</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>27</v>
+        <v>212</v>
       </c>
       <c r="F66" t="n">
-        <v>28.9</v>
+        <v>31.3</v>
       </c>
       <c r="G66" t="n">
-        <v>-43</v>
+        <v>-22</v>
       </c>
       <c r="H66" t="n">
-        <v>2.5</v>
+        <v>13.5</v>
       </c>
       <c r="I66" t="n">
         <v>1</v>
@@ -12279,64 +12291,64 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L66" t="n">
         <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>4.53</v>
+        <v>9.99</v>
       </c>
       <c r="N66" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="O66" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($109 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
+          <t>Buy-month stock-up ($120 to next deal) - confirm; Seasonal - last year ~14/wk vs 7 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Ferrari Carano Fume Blanc 750ml</t>
+          <t>Decoy Merlot 750ml</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>742651123102</t>
+          <t>669576019252</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>212</v>
+        <v>121</v>
       </c>
       <c r="F67" t="n">
-        <v>31.3</v>
+        <v>34.6</v>
       </c>
       <c r="G67" t="n">
-        <v>-22</v>
+        <v>-20</v>
       </c>
       <c r="H67" t="n">
-        <v>13.5</v>
+        <v>4</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
@@ -12351,61 +12363,61 @@
         <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>9.99</v>
+        <v>12.79</v>
       </c>
       <c r="N67" t="n">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="O67" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($120 to next deal) - confirm; Seasonal - last year ~14/wk vs 7 now, buy ahead?</t>
+          <t>Buy-month stock-up ($153 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Decoy Merlot 750ml</t>
+          <t>Cooks Spumante 750ml</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>669576019252</t>
+          <t>083804047198</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Merlot</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>121</v>
+        <v>185</v>
       </c>
       <c r="F68" t="n">
-        <v>34.6</v>
+        <v>37.8</v>
       </c>
       <c r="G68" t="n">
-        <v>-20</v>
+        <v>-5</v>
       </c>
       <c r="H68" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -12417,58 +12429,58 @@
         <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>12.79</v>
+        <v>6</v>
       </c>
       <c r="N68" t="n">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="O68" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($153 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($72 to next deal) - confirm; Seasonal - last year ~8/wk vs 5 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cooks Spumante 750ml</t>
+          <t>Apothic Merlot 750ml</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>083804047198</t>
+          <t>085000032145</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>142</v>
       </c>
       <c r="F69" t="n">
-        <v>37.8</v>
+        <v>38</v>
       </c>
       <c r="G69" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="H69" t="n">
-        <v>8.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="I69" t="n">
         <v>2</v>
@@ -12483,58 +12495,58 @@
         <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>6</v>
+        <v>7.37</v>
       </c>
       <c r="N69" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="O69" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($72 to next deal) - confirm; Seasonal - last year ~8/wk vs 5 now, buy ahead?</t>
+          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Apothic Merlot 750ml</t>
+          <t>Kim Crawford Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>085000032145</t>
+          <t>689352010310</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Merlot</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="F70" t="n">
-        <v>38</v>
+        <v>38.6</v>
       </c>
       <c r="G70" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
         <v>2</v>
@@ -12549,58 +12561,58 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>7.37</v>
+        <v>10.7</v>
       </c>
       <c r="N70" t="n">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="O70" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($128 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kim Crawford Pinot Grigio 750ml</t>
+          <t>Apothic Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>689352010310</t>
+          <t>085000032336</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="F71" t="n">
-        <v>38.6</v>
+        <v>39.1</v>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I71" t="n">
         <v>2</v>
@@ -12615,64 +12627,64 @@
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>10.7</v>
+        <v>7.11</v>
       </c>
       <c r="N71" t="n">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="O71" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($128 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($85 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Apothic Pinot Noir 750ml</t>
+          <t>Harken Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>085000032336</t>
+          <t>847159001812</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>146</v>
+        <v>225</v>
       </c>
       <c r="F72" t="n">
-        <v>39.1</v>
+        <v>40.2</v>
       </c>
       <c r="G72" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H72" t="n">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K72" t="n">
         <v>12</v>
@@ -12681,64 +12693,64 @@
         <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>7.11</v>
+        <v>5.85</v>
       </c>
       <c r="N72" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="O72" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, Jul, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($85 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($70 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Harken Chardonnay 750ml</t>
+          <t>Apothic Inferno 750ml</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>847159001812</t>
+          <t>085000024904</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="F73" t="n">
-        <v>40.2</v>
+        <v>41.1</v>
       </c>
       <c r="G73" t="n">
-        <v>-5</v>
+        <v>-24</v>
       </c>
       <c r="H73" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="I73" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
         <v>12</v>
@@ -12747,40 +12759,40 @@
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>5.85</v>
+        <v>8.57</v>
       </c>
       <c r="N73" t="n">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="O73" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, Jul, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($70 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($103 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Apothic Inferno 750ml</t>
+          <t>Apothic Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>085000024904</t>
+          <t>085000035405</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12789,16 +12801,16 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>211</v>
+        <v>41</v>
       </c>
       <c r="F74" t="n">
-        <v>41.1</v>
+        <v>43.9</v>
       </c>
       <c r="G74" t="n">
-        <v>-24</v>
+        <v>33</v>
       </c>
       <c r="H74" t="n">
-        <v>7.5</v>
+        <v>1.2</v>
       </c>
       <c r="I74" t="n">
         <v>2</v>
@@ -12813,13 +12825,13 @@
         <v>1</v>
       </c>
       <c r="M74" t="n">
-        <v>8.57</v>
+        <v>7.68</v>
       </c>
       <c r="N74" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="O74" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
@@ -12829,45 +12841,45 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($103 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Apothic Chardonnay 750ml</t>
+          <t>Acrobat Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>085000035405</t>
+          <t>768675085929</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="F75" t="n">
-        <v>43.9</v>
+        <v>45.3</v>
       </c>
       <c r="G75" t="n">
-        <v>33</v>
+        <v>-19</v>
       </c>
       <c r="H75" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -12879,40 +12891,40 @@
         <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>7.68</v>
+        <v>12.15</v>
       </c>
       <c r="N75" t="n">
-        <v>92</v>
+        <v>146</v>
       </c>
       <c r="O75" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Apr, May, Aug, Sep, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($146 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Acrobat Pinot Noir 750ml</t>
+          <t>Saldo Zinfandel 750ml</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>768675085929</t>
+          <t>086003258006</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12921,19 +12933,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="F76" t="n">
-        <v>45.3</v>
+        <v>46.3</v>
       </c>
       <c r="G76" t="n">
-        <v>-19</v>
+        <v>-27</v>
       </c>
       <c r="H76" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -12945,10 +12957,10 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>12.15</v>
+        <v>20.31</v>
       </c>
       <c r="N76" t="n">
-        <v>146</v>
+        <v>244</v>
       </c>
       <c r="O76" t="n">
         <v>42</v>
@@ -12956,50 +12968,50 @@
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, May, Aug, Sep, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($146 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($244 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Saldo Zinfandel 750ml</t>
+          <t>Boen Tri Appellation Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>086003258006</t>
+          <t>856184006310</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="F77" t="n">
-        <v>46.3</v>
+        <v>48.6</v>
       </c>
       <c r="G77" t="n">
-        <v>-27</v>
+        <v>50</v>
       </c>
       <c r="H77" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -13011,87 +13023,21 @@
         <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>20.31</v>
+        <v>12.15</v>
       </c>
       <c r="N77" t="n">
-        <v>244</v>
+        <v>146</v>
       </c>
       <c r="O77" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($244 to next deal) - confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Boen Tri Appellation Chardonnay 750ml</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>856184006310</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Chardonnay</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Oxford Street Merchants</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>34</v>
-      </c>
-      <c r="F78" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="G78" t="n">
-        <v>50</v>
-      </c>
-      <c r="H78" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I78" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>12</v>
-      </c>
-      <c r="L78" t="n">
-        <v>1</v>
-      </c>
-      <c r="M78" t="n">
-        <v>12.15</v>
-      </c>
-      <c r="N78" t="n">
-        <v>146</v>
-      </c>
-      <c r="O78" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr">
         <is>
           <t>Buy-month stock-up ($146 to next deal) - confirm; Seasonal - last year ~2/wk vs 1 now, buy ahead?</t>
         </is>
@@ -13108,7 +13054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13313,73 +13259,77 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Franzia Chardonnay 5L Box</t>
+          <t>Daou Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>083120102090</t>
+          <t>890409002398</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>89</v>
+        <v>150</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>6.6</v>
       </c>
       <c r="G4" t="n">
+        <v>-32</v>
+      </c>
+      <c r="H4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21</v>
+      </c>
+      <c r="K4" t="n">
+        <v>12</v>
+      </c>
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>56</v>
-      </c>
-      <c r="J4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>48</v>
-      </c>
-      <c r="L4" t="n">
-        <v>12</v>
-      </c>
       <c r="M4" t="n">
-        <v>14</v>
+        <v>17.33</v>
       </c>
       <c r="N4" t="n">
-        <v>672</v>
+        <v>208</v>
       </c>
       <c r="O4" t="n">
-        <v>33</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Franzia Crisp White 5L Box</t>
+          <t>Franzia Chardonnay 5L Box</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>083120102892</t>
+          <t>083120102090</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>White Blends</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -13388,54 +13338,54 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>20.2</v>
+        <v>31.2</v>
       </c>
       <c r="I5" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="J5" t="n">
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M5" t="n">
-        <v>11.82</v>
+        <v>14</v>
       </c>
       <c r="N5" t="n">
-        <v>284</v>
+        <v>672</v>
       </c>
       <c r="O5" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Franzia Pinot Grigio 5L Box</t>
+          <t>Franzia Crisp White 5L Box</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>083120100393</t>
+          <t>083120102892</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>White Blends</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -13444,54 +13394,54 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>26</v>
+        <v>20.2</v>
       </c>
       <c r="I6" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>11.82</v>
       </c>
       <c r="N6" t="n">
-        <v>560</v>
+        <v>284</v>
       </c>
       <c r="O6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Franzia Rich and Buttery Chardonnay 5L Box</t>
+          <t>Franzia Pinot Grigio 5L Box</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>083120010128</t>
+          <t>083120100393</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -13500,54 +13450,54 @@
         </is>
       </c>
       <c r="E7" t="n">
+        <v>102</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G7" t="n">
         <v>14</v>
       </c>
-      <c r="F7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-4</v>
-      </c>
       <c r="H7" t="n">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>45.47</v>
+        <v>14</v>
       </c>
       <c r="N7" t="n">
-        <v>364</v>
+        <v>560</v>
       </c>
       <c r="O7" t="n">
-        <v>-117</v>
+        <v>33</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Franzia Sunset Blush 5L Box</t>
+          <t>Franzia Rich and Buttery Chardonnay 5L Box</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>083120103691</t>
+          <t>083120010128</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -13556,197 +13506,253 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G8" t="n">
-        <v>-13</v>
+        <v>-4</v>
       </c>
       <c r="H8" t="n">
-        <v>9.5</v>
+        <v>6.2</v>
       </c>
       <c r="I8" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>9.42</v>
+        <v>45.47</v>
       </c>
       <c r="N8" t="n">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="O8" t="n">
-        <v>48</v>
+        <v>-117</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ganbei Baljiu 750ML/ D</t>
+          <t>Franzia Sunset Blush 5L Box</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>860000297004</t>
+          <t>083120103691</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>-1</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.3</v>
+        <v>2.8</v>
       </c>
       <c r="G9" t="n">
-        <v>50</v>
+        <v>-13</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>28.67</v>
+        <v>9.42</v>
       </c>
       <c r="N9" t="n">
-        <v>29</v>
+        <v>377</v>
       </c>
       <c r="O9" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Imagery Cabernet Sauvignon 750ml</t>
+          <t>Ganbei Baljiu 750ML/ D</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>081308004426</t>
+          <t>860000297004</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cabernet</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>130</v>
+        <v>-1</v>
       </c>
       <c r="F10" t="n">
-        <v>29.3</v>
+        <v>-4.3</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>9.33</v>
+        <v>28.67</v>
       </c>
       <c r="N10" t="n">
-        <v>112</v>
+        <v>29</v>
       </c>
       <c r="O10" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Imagery Cabernet Sauvignon 750ml</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>081308004426</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cabernet</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>130</v>
+      </c>
+      <c r="F11" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>12</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="N11" t="n">
+        <v>112</v>
+      </c>
+      <c r="O11" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Moss Roxx Ancient Vine Zinfandel 750ml</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>082544006502</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Zinfandel</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E12" t="n">
         <v>1</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F12" t="n">
         <v>2.1</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G12" t="n">
         <v>100</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H12" t="n">
         <v>0.2</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I12" t="n">
         <v>2</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>2</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" t="n">
         <v>2</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M12" t="n">
         <v>12.29</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N12" t="n">
         <v>25</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O12" t="n">
         <v>41</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Wine Recommended Order.xlsx
+++ b/data/Wine Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S134"/>
+  <dimension ref="A1:S133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4534,41 +4534,41 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>La Vieille Ferme Rose 750ml</t>
+          <t>Frank Family Cabernet 750ml</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>089419000177</t>
+          <t>894910000409</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>The Wine Company</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>497</v>
+        <v>28</v>
       </c>
       <c r="F70" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="G70" t="n">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="H70" t="n">
-        <v>47.2</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="J70" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="K70" t="n">
         <v>12</v>
@@ -4577,31 +4577,35 @@
         <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>6.42</v>
+        <v>37.61</v>
       </c>
       <c r="N70" t="n">
-        <v>77</v>
+        <v>451</v>
       </c>
       <c r="O70" t="n">
-        <v>53</v>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>ON AD - Sunday special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Buy-month stock-up ($451 to next deal) - confirm</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Frank Family Cabernet 750ml</t>
+          <t>Decoy Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>894910000409</t>
+          <t>669576019269</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4615,125 +4619,125 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>28</v>
+        <v>217</v>
       </c>
       <c r="F71" t="n">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="G71" t="n">
-        <v>62</v>
+        <v>-5</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>26.8</v>
       </c>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J71" t="n">
+        <v>12</v>
+      </c>
+      <c r="K71" t="n">
+        <v>48</v>
+      </c>
+      <c r="L71" t="n">
         <v>4</v>
       </c>
-      <c r="K71" t="n">
-        <v>12</v>
-      </c>
-      <c r="L71" t="n">
-        <v>1</v>
-      </c>
       <c r="M71" t="n">
-        <v>37.61</v>
+        <v>13.47</v>
       </c>
       <c r="N71" t="n">
-        <v>451</v>
+        <v>647</v>
       </c>
       <c r="O71" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($451 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($647 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Decoy Cabernet Sauvignon 750ml</t>
+          <t>Underwood Pinot Gris 375ml</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>669576019269</t>
+          <t>856036001067</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>217</v>
+        <v>87</v>
       </c>
       <c r="F72" t="n">
         <v>7.3</v>
       </c>
       <c r="G72" t="n">
-        <v>-5</v>
+        <v>51</v>
       </c>
       <c r="H72" t="n">
-        <v>26.8</v>
+        <v>9.5</v>
       </c>
       <c r="I72" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K72" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="L72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M72" t="n">
-        <v>13.47</v>
+        <v>4.23</v>
       </c>
       <c r="N72" t="n">
-        <v>647</v>
+        <v>102</v>
       </c>
       <c r="O72" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($647 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($102 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Underwood Pinot Gris 375ml</t>
+          <t>Santa Margherita Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>856036001067</t>
+          <t>086891022871</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4747,170 +4751,170 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>87</v>
+        <v>253</v>
       </c>
       <c r="F73" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="G73" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="H73" t="n">
-        <v>9.5</v>
+        <v>36.5</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
         <v>17</v>
       </c>
       <c r="K73" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>4.23</v>
+        <v>19.37</v>
       </c>
       <c r="N73" t="n">
-        <v>102</v>
+        <v>232</v>
       </c>
       <c r="O73" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q73" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Mar, May, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($102 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($232 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Santa Margherita Pinot Grigio 750ml</t>
+          <t>Charles Smith Kung Fu Girl Riesling 750ml</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>086891022871</t>
+          <t>083120015048</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>253</v>
+        <v>74</v>
       </c>
       <c r="F74" t="n">
         <v>7.4</v>
       </c>
       <c r="G74" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H74" t="n">
-        <v>36.5</v>
+        <v>5.2</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J74" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K74" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="L74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M74" t="n">
-        <v>19.37</v>
+        <v>7.51</v>
       </c>
       <c r="N74" t="n">
-        <v>232</v>
+        <v>450</v>
       </c>
       <c r="O74" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, May, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($232 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($450 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Charles Smith Kung Fu Girl Riesling 750ml</t>
+          <t>Barefoot Sauv Blanc 750ml</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>083120015048</t>
+          <t>018341751024</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="F75" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G75" t="n">
+        <v>35</v>
+      </c>
+      <c r="H75" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I75" t="n">
+        <v>28</v>
+      </c>
+      <c r="J75" t="n">
         <v>25</v>
       </c>
-      <c r="H75" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I75" t="n">
-        <v>15</v>
-      </c>
-      <c r="J75" t="n">
-        <v>13</v>
-      </c>
       <c r="K75" t="n">
-        <v>60</v>
+        <v>192</v>
       </c>
       <c r="L75" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M75" t="n">
-        <v>7.51</v>
+        <v>4.33</v>
       </c>
       <c r="N75" t="n">
-        <v>450</v>
+        <v>832</v>
       </c>
       <c r="O75" t="n">
         <v>46</v>
@@ -4918,170 +4922,170 @@
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($450 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($832 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Barefoot Sauv Blanc 750ml</t>
+          <t>Colle Corviano Cerasuolo Rose 750ml</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>018341751024</t>
+          <t>181856000892</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Small Lot MN</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="F76" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="G76" t="n">
-        <v>35</v>
+        <v>-44</v>
       </c>
       <c r="H76" t="n">
-        <v>3.5</v>
+        <v>11.2</v>
       </c>
       <c r="I76" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J76" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K76" t="n">
-        <v>192</v>
+        <v>288</v>
       </c>
       <c r="L76" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M76" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="N76" t="n">
-        <v>832</v>
+        <v>1729</v>
       </c>
       <c r="O76" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, May, Jun, Jul, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($832 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,729 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Colle Corviano Cerasuolo Rose 750ml</t>
+          <t>Risata Moscato d'Asti 750ml</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>181856000892</t>
+          <t>084279977638</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Moscato</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Small Lot MN</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>84</v>
+        <v>367.9996</v>
       </c>
       <c r="F77" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="G77" t="n">
-        <v>-44</v>
+        <v>-4</v>
       </c>
       <c r="H77" t="n">
-        <v>11.2</v>
+        <v>44.8</v>
       </c>
       <c r="I77" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J77" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K77" t="n">
-        <v>288</v>
+        <v>228</v>
       </c>
       <c r="L77" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="M77" t="n">
-        <v>6</v>
+        <v>0.79</v>
       </c>
       <c r="N77" t="n">
-        <v>1729</v>
+        <v>179</v>
       </c>
       <c r="O77" t="n">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, May, Jun, Jul, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,729 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($179 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Risata Moscato d'Asti 750ml</t>
+          <t>Barefoot Pink Moscato 750ml</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>084279977638</t>
+          <t>085000020456</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Moscato</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>367.9996</v>
+        <v>173</v>
       </c>
       <c r="F78" t="n">
         <v>8.1</v>
@@ -5090,248 +5094,248 @@
         <v>-4</v>
       </c>
       <c r="H78" t="n">
-        <v>44.8</v>
+        <v>40</v>
       </c>
       <c r="I78" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J78" t="n">
         <v>7</v>
       </c>
       <c r="K78" t="n">
-        <v>228</v>
+        <v>300</v>
       </c>
       <c r="L78" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M78" t="n">
-        <v>0.79</v>
+        <v>4.32</v>
       </c>
       <c r="N78" t="n">
-        <v>179</v>
+        <v>1296</v>
       </c>
       <c r="O78" t="n">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
-          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($179 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,296 to next deal) - confirm; Seasonal - last year ~40/wk vs 21 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Barefoot Pink Moscato 750ml</t>
+          <t>Pacific Rim Sweet Riesling 750ml</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>085000020456</t>
+          <t>899552102276</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>173</v>
+        <v>35</v>
       </c>
       <c r="F79" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="H79" t="n">
-        <v>40</v>
+        <v>4.2</v>
       </c>
       <c r="I79" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J79" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K79" t="n">
-        <v>300</v>
+        <v>24</v>
       </c>
       <c r="L79" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="M79" t="n">
-        <v>4.32</v>
+        <v>5.35</v>
       </c>
       <c r="N79" t="n">
-        <v>1296</v>
+        <v>128</v>
       </c>
       <c r="O79" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Jan, Feb, Jul, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,296 to next deal) - confirm; Seasonal - last year ~40/wk vs 21 now, buy ahead?</t>
+          <t>Buy-month stock-up ($128 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Pacific Rim Sweet Riesling 750ml</t>
+          <t>Robert Mondavi PS Cab Sauv BB 750ml</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>899552102276</t>
+          <t>086003780217</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>35</v>
+        <v>114</v>
       </c>
       <c r="F80" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="G80" t="n">
         <v>12</v>
       </c>
       <c r="H80" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="I80" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="K80" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="L80" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M80" t="n">
-        <v>5.35</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N80" t="n">
-        <v>128</v>
+        <v>626</v>
       </c>
       <c r="O80" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Feb, Jul, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($128 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($626 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Robert Mondavi PS Cab Sauv BB 750ml</t>
+          <t>Barefoot Apple Moscato 750ml</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>086003780217</t>
+          <t>085000029022</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="F81" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="G81" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>3.2</v>
+        <v>16.2</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="L81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M81" t="n">
-        <v>8.699999999999999</v>
+        <v>4.34</v>
       </c>
       <c r="N81" t="n">
-        <v>626</v>
+        <v>365</v>
       </c>
       <c r="O81" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($626 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($365 to next deal) - confirm; Seasonal - last year ~16/wk vs 7 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Barefoot Apple Moscato 750ml</t>
+          <t>Barefoot Pineapple Moscato 750ml</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>085000029022</t>
+          <t>085000033319</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5345,37 +5349,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="F82" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H82" t="n">
-        <v>16.2</v>
+        <v>6.5</v>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="L82" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M82" t="n">
-        <v>4.34</v>
+        <v>4.36</v>
       </c>
       <c r="N82" t="n">
-        <v>365</v>
+        <v>209</v>
       </c>
       <c r="O82" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
@@ -5385,24 +5389,24 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($365 to next deal) - confirm; Seasonal - last year ~16/wk vs 7 now, buy ahead?</t>
+          <t>Buy-month stock-up ($209 to next deal) - confirm; Seasonal - last year ~6/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Barefoot Pineapple Moscato 750ml</t>
+          <t>Barefoot Moscato 750ml</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>085000033319</t>
+          <t>085000016688</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Moscato</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5411,37 +5415,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>32</v>
+        <v>158</v>
       </c>
       <c r="F83" t="n">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="G83" t="n">
-        <v>12</v>
+        <v>-12</v>
       </c>
       <c r="H83" t="n">
-        <v>6.5</v>
+        <v>32.2</v>
       </c>
       <c r="I83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>48</v>
+        <v>204</v>
       </c>
       <c r="L83" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="M83" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="N83" t="n">
-        <v>209</v>
+        <v>883</v>
       </c>
       <c r="O83" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
@@ -5451,312 +5455,312 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($209 to next deal) - confirm; Seasonal - last year ~6/wk vs 4 now, buy ahead?</t>
+          <t>Buy-month stock-up ($883 to next deal) - confirm; Seasonal - last year ~32/wk vs 17 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Barefoot Moscato 750ml</t>
+          <t>Decoy Sauvignon Blanc 750ml</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>085000016688</t>
+          <t>669576019214</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Moscato</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="F84" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>-12</v>
+        <v>15</v>
       </c>
       <c r="H84" t="n">
-        <v>32.2</v>
+        <v>18.8</v>
       </c>
       <c r="I84" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>204</v>
+        <v>12</v>
       </c>
       <c r="L84" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>4.33</v>
+        <v>11.04</v>
       </c>
       <c r="N84" t="n">
-        <v>883</v>
+        <v>133</v>
       </c>
       <c r="O84" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($883 to next deal) - confirm; Seasonal - last year ~32/wk vs 17 now, buy ahead?</t>
+          <t>Buy-month stock-up ($133 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Decoy Sauvignon Blanc 750ml</t>
+          <t>Risata Prosecco 750ml</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>669576019214</t>
+          <t>084279992464</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="F85" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="G85" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H85" t="n">
-        <v>18.8</v>
+        <v>6</v>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K85" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M85" t="n">
-        <v>11.04</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="N85" t="n">
-        <v>133</v>
+        <v>537</v>
       </c>
       <c r="O85" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($133 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($537 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Risata Prosecco 750ml</t>
+          <t>90+ Cellars Sauvignon Blanc Cali 750ml</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>084279992464</t>
+          <t>894655001822</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>179</v>
+        <v>269</v>
       </c>
       <c r="F86" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="G86" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H86" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I86" t="n">
+        <v>20</v>
+      </c>
+      <c r="J86" t="n">
+        <v>17</v>
+      </c>
+      <c r="K86" t="n">
         <v>12</v>
       </c>
-      <c r="H86" t="n">
-        <v>6</v>
-      </c>
-      <c r="I86" t="n">
-        <v>9</v>
-      </c>
-      <c r="J86" t="n">
-        <v>6</v>
-      </c>
-      <c r="K86" t="n">
+      <c r="L86" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="N86" t="n">
+        <v>78</v>
+      </c>
+      <c r="O86" t="n">
         <v>60</v>
       </c>
-      <c r="L86" t="n">
-        <v>5</v>
-      </c>
-      <c r="M86" t="n">
-        <v>8.960000000000001</v>
-      </c>
-      <c r="N86" t="n">
-        <v>537</v>
-      </c>
-      <c r="O86" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
-        </is>
-      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($537 to next deal) - confirm</t>
+          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>90+ Cellars Sauvignon Blanc Cali 750ml</t>
+          <t>Barefoot Sweet Red 750ml</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>894655001822</t>
+          <t>085000018491</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>269</v>
+        <v>24</v>
       </c>
       <c r="F87" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="G87" t="n">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="H87" t="n">
-        <v>24.8</v>
+        <v>7.8</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M87" t="n">
-        <v>6.46</v>
+        <v>4.24</v>
       </c>
       <c r="N87" t="n">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="O87" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+        </is>
+      </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($153 to next deal) - confirm; Seasonal - last year ~8/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Barefoot Sweet Red 750ml</t>
+          <t>Kim Crawford Sauvignon Blanc Illuminate 750ml</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>085000018491</t>
+          <t>689352010082</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>142</v>
       </c>
       <c r="F88" t="n">
-        <v>10.3</v>
+        <v>11.1</v>
       </c>
       <c r="G88" t="n">
-        <v>-3</v>
+        <v>9</v>
       </c>
       <c r="H88" t="n">
-        <v>7.8</v>
+        <v>14.8</v>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K88" t="n">
         <v>36</v>
@@ -5765,106 +5769,106 @@
         <v>3</v>
       </c>
       <c r="M88" t="n">
-        <v>4.24</v>
+        <v>10.7</v>
       </c>
       <c r="N88" t="n">
-        <v>153</v>
+        <v>385</v>
       </c>
       <c r="O88" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($153 to next deal) - confirm; Seasonal - last year ~8/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($385 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Kim Crawford Sauvignon Blanc Illuminate 750ml</t>
+          <t>Decoy Red Wine 750ml</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>689352010082</t>
+          <t>669576019207</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="F89" t="n">
-        <v>11.1</v>
+        <v>11.5</v>
       </c>
       <c r="G89" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="H89" t="n">
-        <v>14.8</v>
+        <v>2.2</v>
       </c>
       <c r="I89" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J89" t="n">
         <v>6</v>
       </c>
       <c r="K89" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="L89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>10.7</v>
+        <v>13.88</v>
       </c>
       <c r="N89" t="n">
-        <v>385</v>
+        <v>167</v>
       </c>
       <c r="O89" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($385 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($167 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Decoy Red Wine 750ml</t>
+          <t>Decoy Sonoma Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>669576019207</t>
+          <t>669576019245</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5873,22 +5877,22 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>86</v>
+        <v>183</v>
       </c>
       <c r="F90" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="G90" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="H90" t="n">
-        <v>2.2</v>
+        <v>14.8</v>
       </c>
       <c r="I90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J90" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K90" t="n">
         <v>12</v>
@@ -5897,13 +5901,13 @@
         <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>13.88</v>
+        <v>11.54</v>
       </c>
       <c r="N90" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="O90" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
@@ -5913,90 +5917,90 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($167 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($138 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Decoy Sonoma Chardonnay 750ml</t>
+          <t>Barefoot Rose 750ml</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>669576019245</t>
+          <t>085000025871</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>183</v>
+        <v>104</v>
       </c>
       <c r="F91" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="G91" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H91" t="n">
-        <v>14.8</v>
+        <v>13.5</v>
       </c>
       <c r="I91" t="n">
+        <v>6</v>
+      </c>
+      <c r="J91" t="n">
+        <v>6</v>
+      </c>
+      <c r="K91" t="n">
+        <v>84</v>
+      </c>
+      <c r="L91" t="n">
         <v>7</v>
       </c>
-      <c r="J91" t="n">
-        <v>4</v>
-      </c>
-      <c r="K91" t="n">
-        <v>12</v>
-      </c>
-      <c r="L91" t="n">
-        <v>1</v>
-      </c>
       <c r="M91" t="n">
-        <v>11.54</v>
+        <v>4.4</v>
       </c>
       <c r="N91" t="n">
-        <v>138</v>
+        <v>369</v>
       </c>
       <c r="O91" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($138 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($369 to next deal) - confirm; Seasonal - last year ~14/wk vs 9 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Barefoot Rose 750ml</t>
+          <t>LaMarca Prosecco Rose 750ml</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>085000025871</t>
+          <t>085000032442</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6005,64 +6009,64 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="F92" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G92" t="n">
+        <v>7</v>
+      </c>
+      <c r="H92" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I92" t="n">
+        <v>8</v>
+      </c>
+      <c r="J92" t="n">
+        <v>7</v>
+      </c>
+      <c r="K92" t="n">
+        <v>144</v>
+      </c>
+      <c r="L92" t="n">
         <v>12</v>
       </c>
-      <c r="G92" t="n">
-        <v>6</v>
-      </c>
-      <c r="H92" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I92" t="n">
-        <v>6</v>
-      </c>
-      <c r="J92" t="n">
-        <v>6</v>
-      </c>
-      <c r="K92" t="n">
-        <v>84</v>
-      </c>
-      <c r="L92" t="n">
-        <v>7</v>
-      </c>
       <c r="M92" t="n">
-        <v>4.4</v>
+        <v>12.3</v>
       </c>
       <c r="N92" t="n">
-        <v>369</v>
+        <v>1771</v>
       </c>
       <c r="O92" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($369 to next deal) - confirm; Seasonal - last year ~14/wk vs 9 now, buy ahead?</t>
+          <t>Buy-month stock-up ($1,771 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LaMarca Prosecco Rose 750ml</t>
+          <t>Barefoot Bright &amp; Breezy Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>085000032442</t>
+          <t>085000032879</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6071,64 +6075,64 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>136</v>
+        <v>39</v>
       </c>
       <c r="F93" t="n">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
       <c r="G93" t="n">
-        <v>7</v>
+        <v>129</v>
       </c>
       <c r="H93" t="n">
-        <v>9.199999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="I93" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J93" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>144</v>
+        <v>36</v>
       </c>
       <c r="L93" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M93" t="n">
-        <v>12.3</v>
+        <v>4.5</v>
       </c>
       <c r="N93" t="n">
-        <v>1771</v>
+        <v>162</v>
       </c>
       <c r="O93" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,771 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($162 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Barefoot Bright &amp; Breezy Pinot Grigio 750ml</t>
+          <t>Barefoot Peach Moscato 750ml</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>085000032879</t>
+          <t>085000029008</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6137,37 +6141,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="F94" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="G94" t="n">
-        <v>129</v>
+        <v>-7</v>
       </c>
       <c r="H94" t="n">
-        <v>0.8</v>
+        <v>33.5</v>
       </c>
       <c r="I94" t="n">
+        <v>1</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>120</v>
+      </c>
+      <c r="L94" t="n">
         <v>10</v>
       </c>
-      <c r="J94" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" t="n">
-        <v>36</v>
-      </c>
-      <c r="L94" t="n">
-        <v>3</v>
-      </c>
       <c r="M94" t="n">
-        <v>4.5</v>
+        <v>3.06</v>
       </c>
       <c r="N94" t="n">
-        <v>162</v>
+        <v>367</v>
       </c>
       <c r="O94" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
@@ -6177,246 +6181,246 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($162 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($367 to next deal) - confirm; Seasonal - last year ~34/wk vs 14 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Barefoot Peach Moscato 750ml</t>
+          <t>Decoy Zinfandel 750ml</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>085000029008</t>
+          <t>669576019238</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="F95" t="n">
         <v>13.1</v>
       </c>
       <c r="G95" t="n">
-        <v>-7</v>
+        <v>86</v>
       </c>
       <c r="H95" t="n">
-        <v>33.5</v>
+        <v>1.8</v>
       </c>
       <c r="I95" t="n">
+        <v>3</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>12</v>
+      </c>
+      <c r="L95" t="n">
         <v>1</v>
       </c>
-      <c r="J95" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" t="n">
-        <v>120</v>
-      </c>
-      <c r="L95" t="n">
-        <v>10</v>
-      </c>
       <c r="M95" t="n">
-        <v>3.06</v>
+        <v>13.97</v>
       </c>
       <c r="N95" t="n">
-        <v>367</v>
+        <v>168</v>
       </c>
       <c r="O95" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($367 to next deal) - confirm; Seasonal - last year ~34/wk vs 14 now, buy ahead?</t>
+          <t>Buy-month stock-up ($168 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Decoy Zinfandel 750ml</t>
+          <t>Quilt Napa Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>669576019238</t>
+          <t>859889006005</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="F96" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="G96" t="n">
-        <v>86</v>
+        <v>-5</v>
       </c>
       <c r="H96" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K96" t="n">
+        <v>144</v>
+      </c>
+      <c r="L96" t="n">
         <v>12</v>
       </c>
-      <c r="L96" t="n">
-        <v>1</v>
-      </c>
       <c r="M96" t="n">
-        <v>13.97</v>
+        <v>33.45</v>
       </c>
       <c r="N96" t="n">
-        <v>168</v>
+        <v>4816</v>
       </c>
       <c r="O96" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($168 to next deal) - confirm</t>
+          <t>Large buy ($4,816) - confirm; Buy-month stock-up ($4,816 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Quilt Napa Cabernet Sauvignon 750ml</t>
+          <t>Apothic White 750ml</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>859889006005</t>
+          <t>085000019733</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>White Blends</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F97" t="n">
         <v>13.2</v>
       </c>
       <c r="G97" t="n">
-        <v>-5</v>
+        <v>-20</v>
       </c>
       <c r="H97" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="I97" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J97" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>144</v>
+        <v>12</v>
       </c>
       <c r="L97" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>33.45</v>
+        <v>7.22</v>
       </c>
       <c r="N97" t="n">
-        <v>4816</v>
+        <v>87</v>
       </c>
       <c r="O97" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Large buy ($4,816) - confirm; Buy-month stock-up ($4,816 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($87 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Apothic White 750ml</t>
+          <t>Cooks Brut 750ml</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>085000019733</t>
+          <t>083804047211</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>White Blends</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="F98" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="G98" t="n">
-        <v>-20</v>
+        <v>-16</v>
       </c>
       <c r="H98" t="n">
-        <v>6.2</v>
+        <v>14.8</v>
       </c>
       <c r="I98" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K98" t="n">
         <v>12</v>
@@ -6425,35 +6429,35 @@
         <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>7.22</v>
+        <v>5.76</v>
       </c>
       <c r="N98" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="O98" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($87 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($69 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Cooks Brut 750ml</t>
+          <t>LaMarca Prosecco Demi Sec 750ml</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>083804047211</t>
+          <t>085000040669</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6463,129 +6467,129 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>175</v>
+        <v>121</v>
       </c>
       <c r="F99" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="G99" t="n">
-        <v>-16</v>
+        <v>-13</v>
       </c>
       <c r="H99" t="n">
-        <v>14.8</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
+        <v>9</v>
+      </c>
+      <c r="J99" t="n">
         <v>6</v>
       </c>
-      <c r="J99" t="n">
-        <v>4</v>
-      </c>
       <c r="K99" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="L99" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M99" t="n">
-        <v>5.76</v>
+        <v>12.48</v>
       </c>
       <c r="N99" t="n">
-        <v>69</v>
+        <v>1497</v>
       </c>
       <c r="O99" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($69 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,497 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LaMarca Prosecco Demi Sec 750ml</t>
+          <t>Risata Red Moscato 750ml</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>085000040669</t>
+          <t>084279999951</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="F100" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="G100" t="n">
-        <v>-13</v>
+        <v>-3</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="I100" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J100" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="L100" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>12.48</v>
+        <v>11.03</v>
       </c>
       <c r="N100" t="n">
-        <v>1497</v>
+        <v>132</v>
       </c>
       <c r="O100" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,497 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($132 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Risata Red Moscato 750ml</t>
+          <t>Barefoot Riesling 750ml</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>084279999951</t>
+          <t>085000015810</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6595,68 +6599,68 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="F101" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="G101" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="I101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K101" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M101" t="n">
-        <v>11.03</v>
+        <v>4.33</v>
       </c>
       <c r="N101" t="n">
-        <v>132</v>
+        <v>312</v>
       </c>
       <c r="O101" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
-          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($132 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($312 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Barefoot Riesling 750ml</t>
+          <t>Barefoot White Zin 750ml</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>085000015810</t>
+          <t>018341751062</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -6665,37 +6669,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F102" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="I102" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J102" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="L102" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M102" t="n">
-        <v>4.33</v>
+        <v>4.37</v>
       </c>
       <c r="N102" t="n">
-        <v>312</v>
+        <v>262</v>
       </c>
       <c r="O102" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
@@ -6705,24 +6709,24 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($312 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($262 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Barefoot White Zin 750ml</t>
+          <t>Barefoot Blueberry Moscato 750ml</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>018341751062</t>
+          <t>085000031780</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6731,22 +6735,22 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="F103" t="n">
-        <v>14.6</v>
+        <v>14.9</v>
       </c>
       <c r="G103" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="H103" t="n">
-        <v>5.5</v>
+        <v>13.8</v>
       </c>
       <c r="I103" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K103" t="n">
         <v>60</v>
@@ -6755,13 +6759,13 @@
         <v>5</v>
       </c>
       <c r="M103" t="n">
-        <v>4.37</v>
+        <v>4.21</v>
       </c>
       <c r="N103" t="n">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="O103" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
@@ -6771,19 +6775,19 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($262 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($253 to next deal) - confirm; Seasonal - last year ~14/wk vs 9 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Barefoot Blueberry Moscato 750ml</t>
+          <t>Barefoot Red Moscato 750ml</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>085000031780</t>
+          <t>085000019894</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6797,37 +6801,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="F104" t="n">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
       <c r="G104" t="n">
-        <v>44</v>
+        <v>-12</v>
       </c>
       <c r="H104" t="n">
-        <v>13.8</v>
+        <v>6.2</v>
       </c>
       <c r="I104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J104" t="n">
         <v>5</v>
       </c>
       <c r="K104" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="L104" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M104" t="n">
-        <v>4.21</v>
+        <v>4.39</v>
       </c>
       <c r="N104" t="n">
-        <v>253</v>
+        <v>211</v>
       </c>
       <c r="O104" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
@@ -6837,19 +6841,19 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($253 to next deal) - confirm; Seasonal - last year ~14/wk vs 9 now, buy ahead?</t>
+          <t>Buy-month stock-up ($211 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Barefoot Red Moscato 750ml</t>
+          <t>Barefoot Strawberry Moscato 750ml</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>085000019894</t>
+          <t>085000029015</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6863,37 +6867,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103</v>
+        <v>149</v>
       </c>
       <c r="F105" t="n">
+        <v>16</v>
+      </c>
+      <c r="G105" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" t="n">
         <v>15.2</v>
       </c>
-      <c r="G105" t="n">
-        <v>-12</v>
-      </c>
-      <c r="H105" t="n">
-        <v>6.2</v>
-      </c>
       <c r="I105" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>60</v>
+      </c>
+      <c r="L105" t="n">
         <v>5</v>
       </c>
-      <c r="J105" t="n">
-        <v>5</v>
-      </c>
-      <c r="K105" t="n">
-        <v>48</v>
-      </c>
-      <c r="L105" t="n">
-        <v>4</v>
-      </c>
       <c r="M105" t="n">
-        <v>4.39</v>
+        <v>4.35</v>
       </c>
       <c r="N105" t="n">
-        <v>211</v>
+        <v>261</v>
       </c>
       <c r="O105" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr">
@@ -6903,24 +6907,24 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($211 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($261 to next deal) - confirm; Seasonal - last year ~15/wk vs 9 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Barefoot Strawberry Moscato 750ml</t>
+          <t>Apothic Crush 750ml</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>085000029015</t>
+          <t>085000023488</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6929,64 +6933,64 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="F106" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G106" t="n">
+        <v>-2</v>
+      </c>
+      <c r="H106" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I106" t="n">
+        <v>5</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>12</v>
+      </c>
+      <c r="L106" t="n">
         <v>1</v>
       </c>
-      <c r="H106" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="I106" t="n">
-        <v>1</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="n">
-        <v>60</v>
-      </c>
-      <c r="L106" t="n">
-        <v>5</v>
-      </c>
       <c r="M106" t="n">
-        <v>4.35</v>
+        <v>6.3</v>
       </c>
       <c r="N106" t="n">
-        <v>261</v>
+        <v>76</v>
       </c>
       <c r="O106" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($261 to next deal) - confirm; Seasonal - last year ~15/wk vs 9 now, buy ahead?</t>
+          <t>Buy-month stock-up ($76 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Apothic Crush 750ml</t>
+          <t>Barefoot Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>085000023488</t>
+          <t>018341751055</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6995,130 +6999,130 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="F107" t="n">
         <v>17</v>
       </c>
       <c r="G107" t="n">
-        <v>-2</v>
+        <v>9</v>
       </c>
       <c r="H107" t="n">
-        <v>11.2</v>
+        <v>7.8</v>
       </c>
       <c r="I107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K107" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="L107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M107" t="n">
-        <v>6.3</v>
+        <v>4.42</v>
       </c>
       <c r="N107" t="n">
-        <v>76</v>
+        <v>212</v>
       </c>
       <c r="O107" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($76 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($212 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Barefoot Chardonnay 750ml</t>
+          <t>Quilt Red Blend 750ml</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>018341751055</t>
+          <t>859889006302</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>151</v>
+        <v>8</v>
       </c>
       <c r="F108" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="G108" t="n">
-        <v>9</v>
+        <v>100</v>
       </c>
       <c r="H108" t="n">
-        <v>7.8</v>
+        <v>0.8</v>
       </c>
       <c r="I108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="L108" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>4.42</v>
+        <v>25.23</v>
       </c>
       <c r="N108" t="n">
-        <v>212</v>
+        <v>303</v>
       </c>
       <c r="O108" t="n">
-        <v>45</v>
+        <v>-5</v>
       </c>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($212 to next deal) - confirm</t>
+          <t>Margin looks off - check retail/cost; Buy-month stock-up ($303 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Quilt Red Blend 750ml</t>
+          <t>Risata Pink Moscato 750ml</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>859889006302</t>
+          <t>084279988108</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7127,22 +7131,22 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>8</v>
+        <v>148</v>
       </c>
       <c r="F109" t="n">
-        <v>17.1</v>
+        <v>17.6</v>
       </c>
       <c r="G109" t="n">
-        <v>100</v>
+        <v>-10</v>
       </c>
       <c r="H109" t="n">
-        <v>0.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K109" t="n">
         <v>12</v>
@@ -7151,64 +7155,64 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>25.23</v>
+        <v>11.02</v>
       </c>
       <c r="N109" t="n">
-        <v>303</v>
+        <v>132</v>
       </c>
       <c r="O109" t="n">
-        <v>-5</v>
+        <v>15</v>
       </c>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>Margin looks off - check retail/cost; Buy-month stock-up ($303 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($132 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Risata Pink Moscato 750ml</t>
+          <t>90+ Cellars Lot 210 Paso Robles Cabernet Sauvignon  750ml</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>084279988108</t>
+          <t>810879020838</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>148</v>
+        <v>443</v>
       </c>
       <c r="F110" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="G110" t="n">
         <v>-10</v>
       </c>
       <c r="H110" t="n">
-        <v>9.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="I110" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K110" t="n">
         <v>12</v>
@@ -7217,193 +7221,193 @@
         <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>11.02</v>
+        <v>8.59</v>
       </c>
       <c r="N110" t="n">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="O110" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($132 to next deal) - confirm</t>
+          <t>Overstocked (18 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>90+ Cellars Lot 210 Paso Robles Cabernet Sauvignon  750ml</t>
+          <t>Belle Glos Dairyman Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>810879020838</t>
+          <t>855622000811</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>443</v>
+        <v>42</v>
       </c>
       <c r="F111" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="G111" t="n">
-        <v>-10</v>
+        <v>3</v>
       </c>
       <c r="H111" t="n">
-        <v>22</v>
+        <v>1.2</v>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="L111" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M111" t="n">
-        <v>8.59</v>
+        <v>31.9</v>
       </c>
       <c r="N111" t="n">
-        <v>103</v>
+        <v>1531</v>
       </c>
       <c r="O111" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R111" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+        </is>
+      </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>Overstocked (18 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($1,531 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Belle Glos Dairyman Pinot Noir 750ml</t>
+          <t>Stags' Leap Cabernet Sauvignon Napa 750ml</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>855622000811</t>
+          <t>089819042401</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="F112" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="G112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="L112" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>31.9</v>
+        <v>39.89</v>
       </c>
       <c r="N112" t="n">
-        <v>1531</v>
+        <v>479</v>
       </c>
       <c r="O112" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,531 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($479 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Stags' Leap Cabernet Sauvignon Napa 750ml</t>
+          <t>Les Allies Brut Sparkling Rose 750ml</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>089819042401</t>
+          <t>763955408108</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Maverick Beverage Co., LLC - MN</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="F113" t="n">
-        <v>18.1</v>
+        <v>19</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>-26</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -7415,61 +7419,61 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>39.89</v>
+        <v>5.83</v>
       </c>
       <c r="N113" t="n">
-        <v>479</v>
+        <v>70</v>
       </c>
       <c r="O113" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q113" t="inlineStr"/>
-      <c r="R113" t="inlineStr">
-        <is>
-          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($479 to next deal) - confirm</t>
+          <t>Overstocked (19 wks on hand) - confirm before buying more; Seasonal - last year ~13/wk vs 6 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Les Allies Brut Sparkling Rose 750ml</t>
+          <t>Apothic Rose 750ml</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>763955408108</t>
+          <t>085000021545</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Maverick Beverage Co., LLC - MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="F114" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="G114" t="n">
-        <v>-26</v>
+        <v>10</v>
       </c>
       <c r="H114" t="n">
-        <v>13.2</v>
+        <v>4.8</v>
       </c>
       <c r="I114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -7481,40 +7485,40 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>5.83</v>
+        <v>6.89</v>
       </c>
       <c r="N114" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="O114" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R114" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>Overstocked (19 wks on hand) - confirm before buying more; Seasonal - last year ~13/wk vs 6 now, buy ahead?</t>
+          <t>Buy-month stock-up ($83 to next deal) - confirm; Seasonal - last year ~5/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Apothic Rose 750ml</t>
+          <t>Barefoot Pear Moscato 750ml</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>085000021545</t>
+          <t>085000037607</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7523,22 +7527,22 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F115" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="G115" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H115" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I115" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K115" t="n">
         <v>12</v>
@@ -7547,35 +7551,35 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>6.89</v>
+        <v>4.32</v>
       </c>
       <c r="N115" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="O115" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($83 to next deal) - confirm; Seasonal - last year ~5/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~9/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Barefoot Pear Moscato 750ml</t>
+          <t>Barefoot Watermelon Moscato 750ml</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>085000037607</t>
+          <t>085000029923</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7589,22 +7593,22 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="F116" t="n">
         <v>19.3</v>
       </c>
       <c r="G116" t="n">
-        <v>24</v>
+        <v>-33</v>
       </c>
       <c r="H116" t="n">
-        <v>9.199999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="I116" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
         <v>12</v>
@@ -7613,7 +7617,7 @@
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="N116" t="n">
         <v>52</v>
@@ -7629,151 +7633,151 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~9/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~3/wk vs 0 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Barefoot Watermelon Moscato 750ml</t>
+          <t>Cooks Brut 1.5L</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>085000029923</t>
+          <t>083804043152</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="F117" t="n">
-        <v>19.3</v>
+        <v>20.5</v>
       </c>
       <c r="G117" t="n">
-        <v>-33</v>
+        <v>-30</v>
       </c>
       <c r="H117" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L117" t="n">
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>4.31</v>
+        <v>10.33</v>
       </c>
       <c r="N117" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="O117" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~3/wk vs 0 now, buy ahead?</t>
+          <t>Buy-month stock-up ($62 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Cooks Brut 1.5L</t>
+          <t>Apothic Cabernet Sauv 750ml</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>083804043152</t>
+          <t>085000030967</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="F118" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="G118" t="n">
-        <v>-30</v>
+        <v>-8</v>
       </c>
       <c r="H118" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="I118" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L118" t="n">
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>10.33</v>
+        <v>7.28</v>
       </c>
       <c r="N118" t="n">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="O118" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($62 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($87 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Apothic Cabernet Sauv 750ml</t>
+          <t>Big Bad Bourbon Barrel Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>085000030967</t>
+          <t>684586922941</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7783,20 +7787,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Paustis Wine</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>130</v>
+        <v>572</v>
       </c>
       <c r="F119" t="n">
-        <v>20.6</v>
+        <v>21.5</v>
       </c>
       <c r="G119" t="n">
-        <v>-8</v>
+        <v>3</v>
       </c>
       <c r="H119" t="n">
-        <v>6.5</v>
+        <v>59.5</v>
       </c>
       <c r="I119" t="n">
         <v>2</v>
@@ -7811,35 +7815,35 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>7.28</v>
+        <v>6.24</v>
       </c>
       <c r="N119" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="O119" t="n">
-        <v>39</v>
-      </c>
-      <c r="Q119" t="inlineStr"/>
-      <c r="R119" t="inlineStr">
-        <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($87 to next deal) - confirm</t>
+          <t>Overstocked (22 wks on hand) - confirm before buying more; Seasonal - last year ~60/wk vs 27 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Big Bad Bourbon Barrel Cabernet Sauvignon 750ml</t>
+          <t>Pizzolato Cabernet 750ml</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>684586922941</t>
+          <t>185554000352</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7849,20 +7853,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Paustis Wine</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>572</v>
+        <v>172</v>
       </c>
       <c r="F120" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="G120" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="H120" t="n">
-        <v>59.5</v>
+        <v>1.8</v>
       </c>
       <c r="I120" t="n">
         <v>2</v>
@@ -7877,40 +7881,40 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>6.24</v>
+        <v>3.86</v>
       </c>
       <c r="N120" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="O120" t="n">
-        <v>58</v>
-      </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, Apr, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+        </is>
+      </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>Overstocked (22 wks on hand) - confirm before buying more; Seasonal - last year ~60/wk vs 27 now, buy ahead?</t>
+          <t>Buy-month stock-up ($46 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Pizzolato Cabernet 750ml</t>
+          <t>Boen Tri Appellation Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>185554000352</t>
+          <t>856184006112</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -7919,22 +7923,22 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="F121" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="G121" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="H121" t="n">
-        <v>1.8</v>
+        <v>49.2</v>
       </c>
       <c r="I121" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K121" t="n">
         <v>12</v>
@@ -7943,35 +7947,35 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>3.86</v>
+        <v>5.19</v>
       </c>
       <c r="N121" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="O121" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($46 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($62 to next deal) - confirm; Seasonal - last year ~49/wk vs 8 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Boen Tri Appellation Pinot Noir 750ml</t>
+          <t>Belle Glos Clark &amp; Telephone 750ml</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>856184006112</t>
+          <t>855622000118</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7985,64 +7989,64 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>183</v>
+        <v>36</v>
       </c>
       <c r="F122" t="n">
-        <v>21.8</v>
+        <v>25.7</v>
       </c>
       <c r="G122" t="n">
-        <v>5</v>
+        <v>-28</v>
       </c>
       <c r="H122" t="n">
-        <v>49.2</v>
+        <v>2</v>
       </c>
       <c r="I122" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M122" t="n">
-        <v>5.19</v>
+        <v>32.37</v>
       </c>
       <c r="N122" t="n">
-        <v>62</v>
+        <v>777</v>
       </c>
       <c r="O122" t="n">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($62 to next deal) - confirm; Seasonal - last year ~49/wk vs 8 now, buy ahead?</t>
+          <t>Buy-month stock-up ($777 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Belle Glos Clark &amp; Telephone 750ml</t>
+          <t>Quilt Threadcount Red Blend 750ml</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>855622000118</t>
+          <t>860009046009</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -8051,37 +8055,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F123" t="n">
-        <v>25.7</v>
+        <v>26.6</v>
       </c>
       <c r="G123" t="n">
-        <v>-28</v>
+        <v>-25</v>
       </c>
       <c r="H123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>12</v>
+      </c>
+      <c r="L123" t="n">
         <v>1</v>
       </c>
-      <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="n">
-        <v>24</v>
-      </c>
-      <c r="L123" t="n">
-        <v>2</v>
-      </c>
       <c r="M123" t="n">
-        <v>32.37</v>
+        <v>13.42</v>
       </c>
       <c r="N123" t="n">
-        <v>777</v>
+        <v>161</v>
       </c>
       <c r="O123" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr">
@@ -8091,45 +8095,45 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($777 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($161 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Quilt Threadcount Red Blend 750ml</t>
+          <t>Ferrari Carano Fume Blanc 750ml</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>860009046009</t>
+          <t>742651123102</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>31</v>
+        <v>217</v>
       </c>
       <c r="F124" t="n">
-        <v>26.6</v>
+        <v>27.4</v>
       </c>
       <c r="G124" t="n">
-        <v>-25</v>
+        <v>-14</v>
       </c>
       <c r="H124" t="n">
-        <v>1</v>
+        <v>14.2</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -8141,58 +8145,58 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>13.42</v>
+        <v>9.99</v>
       </c>
       <c r="N124" t="n">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="O124" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($161 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($120 to next deal) - confirm; Seasonal - last year ~14/wk vs 8 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Ferrari Carano Fume Blanc 750ml</t>
+          <t>Apothic Dark 750ml</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>742651123102</t>
+          <t>085000022863</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>217</v>
+        <v>26.75</v>
       </c>
       <c r="F125" t="n">
-        <v>27.4</v>
+        <v>28.7</v>
       </c>
       <c r="G125" t="n">
-        <v>-14</v>
+        <v>20</v>
       </c>
       <c r="H125" t="n">
-        <v>14.2</v>
+        <v>1.2</v>
       </c>
       <c r="I125" t="n">
         <v>2</v>
@@ -8207,58 +8211,58 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>9.99</v>
+        <v>7.37</v>
       </c>
       <c r="N125" t="n">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="O125" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($120 to next deal) - confirm; Seasonal - last year ~14/wk vs 8 now, buy ahead?</t>
+          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Apothic Dark 750ml</t>
+          <t>Cooks Spumante 750ml</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>085000022863</t>
+          <t>083804047198</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>26.75</v>
+        <v>180</v>
       </c>
       <c r="F126" t="n">
-        <v>28.7</v>
+        <v>30.9</v>
       </c>
       <c r="G126" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H126" t="n">
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="I126" t="n">
         <v>2</v>
@@ -8273,61 +8277,61 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>7.37</v>
+        <v>6</v>
       </c>
       <c r="N126" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="O126" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($72 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Cooks Spumante 750ml</t>
+          <t>Apothic Merlot 750ml</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>083804047198</t>
+          <t>085000032145</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>180</v>
+        <v>137</v>
       </c>
       <c r="F127" t="n">
-        <v>30.9</v>
+        <v>32.6</v>
       </c>
       <c r="G127" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H127" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="I127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -8339,61 +8343,61 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>6</v>
+        <v>7.37</v>
       </c>
       <c r="N127" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="O127" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($72 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Apothic Merlot 750ml</t>
+          <t>Acrobat Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>085000032145</t>
+          <t>768675085929</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Merlot</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="F128" t="n">
-        <v>32.6</v>
+        <v>33.3</v>
       </c>
       <c r="G128" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="H128" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="I128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -8405,40 +8409,40 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>7.37</v>
+        <v>12.16</v>
       </c>
       <c r="N128" t="n">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="O128" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Apr, May, Aug, Sep, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($146 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Acrobat Pinot Noir 750ml</t>
+          <t>Saldo Zinfandel 750ml</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>768675085929</t>
+          <t>086003258006</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8447,19 +8451,19 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="F129" t="n">
-        <v>33.3</v>
+        <v>33.6</v>
       </c>
       <c r="G129" t="n">
-        <v>-7</v>
+        <v>-15</v>
       </c>
       <c r="H129" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -8471,10 +8475,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>12.16</v>
+        <v>20.33</v>
       </c>
       <c r="N129" t="n">
-        <v>146</v>
+        <v>244</v>
       </c>
       <c r="O129" t="n">
         <v>42</v>
@@ -8482,29 +8486,29 @@
       <c r="Q129" t="inlineStr"/>
       <c r="R129" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, May, Aug, Sep, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($146 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($244 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Saldo Zinfandel 750ml</t>
+          <t>Charles Smith Velvet Devil Merlot 750ml</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>086003258006</t>
+          <t>083120015055</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8513,19 +8517,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F130" t="n">
-        <v>33.6</v>
+        <v>36.3</v>
       </c>
       <c r="G130" t="n">
-        <v>-15</v>
+        <v>-5</v>
       </c>
       <c r="H130" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="I130" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -8537,58 +8541,58 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>20.33</v>
+        <v>7.29</v>
       </c>
       <c r="N130" t="n">
-        <v>244</v>
+        <v>88</v>
       </c>
       <c r="O130" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($244 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Charles Smith Velvet Devil Merlot 750ml</t>
+          <t>Apothic Inferno 750ml</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>083120015055</t>
+          <t>085000024904</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Merlot</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>110</v>
+        <v>207</v>
       </c>
       <c r="F131" t="n">
-        <v>36.3</v>
+        <v>42.2</v>
       </c>
       <c r="G131" t="n">
-        <v>-5</v>
+        <v>-24</v>
       </c>
       <c r="H131" t="n">
-        <v>4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I131" t="n">
         <v>1</v>
@@ -8603,40 +8607,40 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>7.29</v>
+        <v>8.56</v>
       </c>
       <c r="N131" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="O131" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($103 to next deal) - confirm; Seasonal - last year ~9/wk vs 5 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Apothic Inferno 750ml</t>
+          <t>Apothic Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>085000024904</t>
+          <t>085000035405</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8645,19 +8649,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>207</v>
+        <v>40</v>
       </c>
       <c r="F132" t="n">
-        <v>42.2</v>
+        <v>42.9</v>
       </c>
       <c r="G132" t="n">
-        <v>-24</v>
+        <v>20</v>
       </c>
       <c r="H132" t="n">
-        <v>8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -8669,13 +8673,13 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>8.56</v>
+        <v>7.68</v>
       </c>
       <c r="N132" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="O132" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr">
@@ -8685,24 +8689,24 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($103 to next deal) - confirm; Seasonal - last year ~9/wk vs 5 now, buy ahead?</t>
+          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Apothic Chardonnay 750ml</t>
+          <t>Apothic Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>085000035405</t>
+          <t>085000032336</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8711,19 +8715,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>40</v>
+        <v>145</v>
       </c>
       <c r="F133" t="n">
-        <v>42.9</v>
+        <v>56.5</v>
       </c>
       <c r="G133" t="n">
-        <v>20</v>
+        <v>-31</v>
       </c>
       <c r="H133" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="I133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -8735,13 +8739,13 @@
         <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>7.68</v>
+        <v>7.14</v>
       </c>
       <c r="N133" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="O133" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="Q133" t="inlineStr"/>
       <c r="R133" t="inlineStr">
@@ -8750,72 +8754,6 @@
         </is>
       </c>
       <c r="S133" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Apothic Pinot Noir 750ml</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>085000032336</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Pinot Noir</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Johnson Brothers - St. Paul</t>
-        </is>
-      </c>
-      <c r="E134" t="n">
-        <v>145</v>
-      </c>
-      <c r="F134" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="G134" t="n">
-        <v>-31</v>
-      </c>
-      <c r="H134" t="n">
-        <v>3</v>
-      </c>
-      <c r="I134" t="n">
-        <v>1</v>
-      </c>
-      <c r="J134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" t="n">
-        <v>12</v>
-      </c>
-      <c r="L134" t="n">
-        <v>1</v>
-      </c>
-      <c r="M134" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="N134" t="n">
-        <v>86</v>
-      </c>
-      <c r="O134" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q134" t="inlineStr"/>
-      <c r="R134" t="inlineStr">
-        <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
-      <c r="S134" t="inlineStr">
         <is>
           <t>Buy-month stock-up ($86 to next deal) - confirm</t>
         </is>

--- a/data/Wine Recommended Order.xlsx
+++ b/data/Wine Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S126"/>
+  <dimension ref="A1:S127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4353,78 +4353,74 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Decoy Cabernet Sauvignon 750ml</t>
+          <t>La Vieille Ferme Rose 750ml</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>669576019269</t>
+          <t>089419000177</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>The Wine Company</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>213</v>
+        <v>487</v>
       </c>
       <c r="F67" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="G67" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H67" t="n">
-        <v>27</v>
+        <v>47.5</v>
       </c>
       <c r="I67" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J67" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K67" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="L67" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>13.49</v>
+        <v>6.41</v>
       </c>
       <c r="N67" t="n">
-        <v>971</v>
+        <v>77</v>
       </c>
       <c r="O67" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($971 to next deal) - confirm</t>
-        </is>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>ON AD - Sunday special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Frank Family Cabernet 750ml</t>
+          <t>Decoy Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>894910000409</t>
+          <t>669576019269</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4438,232 +4434,232 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>28</v>
+        <v>213</v>
       </c>
       <c r="F68" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="G68" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K68" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M68" t="n">
-        <v>37.61</v>
+        <v>13.49</v>
       </c>
       <c r="N68" t="n">
-        <v>451</v>
+        <v>971</v>
       </c>
       <c r="O68" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($451 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($971 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Underwood Pinot Gris 375ml</t>
+          <t>Frank Family Cabernet 750ml</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>856036001067</t>
+          <t>894910000409</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="F69" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="G69" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="H69" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="J69" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>4.23</v>
+        <v>37.61</v>
       </c>
       <c r="N69" t="n">
-        <v>101</v>
+        <v>451</v>
       </c>
       <c r="O69" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($101 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($451 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Barefoot Pink Moscato 750ml</t>
+          <t>Underwood Pinot Gris 375ml</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>085000020456</t>
+          <t>856036001067</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>173</v>
+        <v>86</v>
       </c>
       <c r="F70" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="G70" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="H70" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I70" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K70" t="n">
-        <v>348</v>
+        <v>24</v>
       </c>
       <c r="L70" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
-        <v>4.32</v>
+        <v>4.23</v>
       </c>
       <c r="N70" t="n">
-        <v>1504</v>
+        <v>101</v>
       </c>
       <c r="O70" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,504 to next deal) - confirm; Seasonal - last year ~40/wk vs 24 now, buy ahead?</t>
+          <t>Buy-month stock-up ($101 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Charles Smith Kung Fu Girl Riesling 750ml</t>
+          <t>Barefoot Pink Moscato 750ml</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>083120015048</t>
+          <t>085000020456</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>74</v>
+        <v>173</v>
       </c>
       <c r="F71" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="G71" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="H71" t="n">
-        <v>5.2</v>
+        <v>40</v>
       </c>
       <c r="I71" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K71" t="n">
-        <v>60</v>
+        <v>348</v>
       </c>
       <c r="L71" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="M71" t="n">
-        <v>7.51</v>
+        <v>4.32</v>
       </c>
       <c r="N71" t="n">
-        <v>450</v>
+        <v>1504</v>
       </c>
       <c r="O71" t="n">
         <v>46</v>
@@ -4671,359 +4667,359 @@
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($450 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,504 to next deal) - confirm; Seasonal - last year ~40/wk vs 24 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Risata Moscato d'Asti 750ml</t>
+          <t>Charles Smith Kung Fu Girl Riesling 750ml</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>084279977638</t>
+          <t>083120015048</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Moscato</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>362.9996</v>
+        <v>74</v>
       </c>
       <c r="F72" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="G72" t="n">
-        <v>-4</v>
+        <v>26</v>
       </c>
       <c r="H72" t="n">
-        <v>44</v>
+        <v>5.2</v>
       </c>
       <c r="I72" t="n">
+        <v>15</v>
+      </c>
+      <c r="J72" t="n">
         <v>13</v>
       </c>
-      <c r="J72" t="n">
-        <v>8</v>
-      </c>
       <c r="K72" t="n">
-        <v>228</v>
+        <v>60</v>
       </c>
       <c r="L72" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="M72" t="n">
-        <v>0.8</v>
+        <v>7.51</v>
       </c>
       <c r="N72" t="n">
-        <v>182</v>
+        <v>450</v>
       </c>
       <c r="O72" t="n">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
-          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($182 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($450 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Colle Corviano Cerasuolo Rose 750ml</t>
+          <t>Risata Moscato d'Asti 750ml</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>181856000892</t>
+          <t>084279977638</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Moscato</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Small Lot MN</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>84</v>
+        <v>362.9996</v>
       </c>
       <c r="F73" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="G73" t="n">
-        <v>-45</v>
+        <v>-4</v>
       </c>
       <c r="H73" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="I73" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J73" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K73" t="n">
-        <v>276</v>
+        <v>228</v>
       </c>
       <c r="L73" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="M73" t="n">
-        <v>6</v>
+        <v>0.8</v>
       </c>
       <c r="N73" t="n">
-        <v>1657</v>
+        <v>182</v>
       </c>
       <c r="O73" t="n">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, May, Jun, Jul, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,657 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($182 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Pacific Rim Sweet Riesling 750ml</t>
+          <t>Colle Corviano Cerasuolo Rose 750ml</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>899552102276</t>
+          <t>181856000892</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Small Lot MN</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="F74" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>12</v>
+        <v>-45</v>
       </c>
       <c r="H74" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I74" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J74" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K74" t="n">
-        <v>24</v>
+        <v>276</v>
       </c>
       <c r="L74" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="M74" t="n">
-        <v>5.87</v>
+        <v>6</v>
       </c>
       <c r="N74" t="n">
-        <v>141</v>
+        <v>1657</v>
       </c>
       <c r="O74" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Feb, Jul, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Apr, May, Jun, Jul, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($141 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,657 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Robert Mondavi PS Cab Sauv BB 750ml</t>
+          <t>Pacific Rim Sweet Riesling 750ml</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>086003780217</t>
+          <t>899552102276</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>113</v>
+        <v>35</v>
       </c>
       <c r="F75" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G75" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H75" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="J75" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K75" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="L75" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M75" t="n">
-        <v>8.69</v>
+        <v>5.87</v>
       </c>
       <c r="N75" t="n">
-        <v>626</v>
+        <v>141</v>
       </c>
       <c r="O75" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Feb, Jul, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($626 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($141 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Barefoot Sauv Blanc 750ml</t>
+          <t>Robert Mondavi PS Cab Sauv BB 750ml</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>018341751024</t>
+          <t>086003780217</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F76" t="n">
         <v>8.5</v>
       </c>
       <c r="G76" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="H76" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="I76" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K76" t="n">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="L76" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M76" t="n">
-        <v>4.33</v>
+        <v>8.69</v>
       </c>
       <c r="N76" t="n">
-        <v>780</v>
+        <v>626</v>
       </c>
       <c r="O76" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($780 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($626 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Barefoot Apple Moscato 750ml</t>
+          <t>Barefoot Sauv Blanc 750ml</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>085000029022</t>
+          <t>018341751024</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5032,34 +5028,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="F77" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="G77" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="H77" t="n">
-        <v>17.5</v>
+        <v>3.8</v>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K77" t="n">
-        <v>84</v>
+        <v>180</v>
       </c>
       <c r="L77" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M77" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="N77" t="n">
-        <v>365</v>
+        <v>780</v>
       </c>
       <c r="O77" t="n">
         <v>46</v>
@@ -5072,19 +5068,19 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($365 to next deal) - confirm; Seasonal - last year ~18/wk vs 7 now, buy ahead?</t>
+          <t>Buy-month stock-up ($780 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Barefoot Sweet Red 750ml</t>
+          <t>Barefoot Apple Moscato 750ml</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>085000018491</t>
+          <t>085000029022</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5098,37 +5094,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="F78" t="n">
         <v>9</v>
       </c>
       <c r="G78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H78" t="n">
-        <v>7.8</v>
+        <v>17.5</v>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="L78" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M78" t="n">
-        <v>4.24</v>
+        <v>4.34</v>
       </c>
       <c r="N78" t="n">
-        <v>153</v>
+        <v>365</v>
       </c>
       <c r="O78" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
@@ -5138,19 +5134,19 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($153 to next deal) - confirm; Seasonal - last year ~8/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($365 to next deal) - confirm; Seasonal - last year ~18/wk vs 7 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Barefoot Pineapple Moscato 750ml</t>
+          <t>Barefoot Sweet Red 750ml</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>085000033319</t>
+          <t>085000018491</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5164,37 +5160,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F79" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="G79" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H79" t="n">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="I79" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="L79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M79" t="n">
-        <v>4.36</v>
+        <v>4.24</v>
       </c>
       <c r="N79" t="n">
-        <v>209</v>
+        <v>153</v>
       </c>
       <c r="O79" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
@@ -5204,24 +5200,24 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($209 to next deal) - confirm; Seasonal - last year ~6/wk vs 4 now, buy ahead?</t>
+          <t>Buy-month stock-up ($153 to next deal) - confirm; Seasonal - last year ~8/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Barefoot Moscato 750ml</t>
+          <t>Barefoot Pineapple Moscato 750ml</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>085000016688</t>
+          <t>085000033319</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Moscato</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5230,37 +5226,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>168</v>
+        <v>32</v>
       </c>
       <c r="F80" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="G80" t="n">
-        <v>-8</v>
+        <v>12</v>
       </c>
       <c r="H80" t="n">
-        <v>33.5</v>
+        <v>6.5</v>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>204</v>
+        <v>48</v>
       </c>
       <c r="L80" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="M80" t="n">
-        <v>4.32</v>
+        <v>4.36</v>
       </c>
       <c r="N80" t="n">
-        <v>882</v>
+        <v>209</v>
       </c>
       <c r="O80" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
@@ -5270,151 +5266,151 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($882 to next deal) - confirm; Seasonal - last year ~34/wk vs 17 now, buy ahead?</t>
+          <t>Buy-month stock-up ($209 to next deal) - confirm; Seasonal - last year ~6/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Risata Prosecco 750ml</t>
+          <t>Barefoot Moscato 750ml</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>084279992464</t>
+          <t>085000016688</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Moscato</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="F81" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="G81" t="n">
-        <v>11</v>
+        <v>-8</v>
       </c>
       <c r="H81" t="n">
-        <v>6</v>
+        <v>33.5</v>
       </c>
       <c r="I81" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>60</v>
+        <v>204</v>
       </c>
       <c r="L81" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="M81" t="n">
-        <v>8.960000000000001</v>
+        <v>4.32</v>
       </c>
       <c r="N81" t="n">
-        <v>537</v>
+        <v>882</v>
       </c>
       <c r="O81" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
-          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($537 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($882 to next deal) - confirm; Seasonal - last year ~34/wk vs 17 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>90+ Cellars Sauvignon Blanc Cali 750ml</t>
+          <t>Risata Prosecco 750ml</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>894655001822</t>
+          <t>084279992464</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>267</v>
+        <v>179</v>
       </c>
       <c r="F82" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="G82" t="n">
-        <v>-12</v>
+        <v>11</v>
       </c>
       <c r="H82" t="n">
-        <v>24.2</v>
+        <v>6</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J82" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K82" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M82" t="n">
-        <v>6.46</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="N82" t="n">
-        <v>78</v>
+        <v>537</v>
       </c>
       <c r="O82" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+        </is>
+      </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($537 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kim Crawford Sauvignon Blanc Illuminate 750ml</t>
+          <t>90+ Cellars Sauvignon Blanc Cali 750ml</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>689352010082</t>
+          <t>894655001822</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5424,464 +5420,464 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>142</v>
+        <v>267</v>
       </c>
       <c r="F83" t="n">
-        <v>11.1</v>
+        <v>10.3</v>
       </c>
       <c r="G83" t="n">
-        <v>9</v>
+        <v>-12</v>
       </c>
       <c r="H83" t="n">
-        <v>14.8</v>
+        <v>24.2</v>
       </c>
       <c r="I83" t="n">
+        <v>20</v>
+      </c>
+      <c r="J83" t="n">
+        <v>17</v>
+      </c>
+      <c r="K83" t="n">
         <v>12</v>
       </c>
-      <c r="J83" t="n">
-        <v>6</v>
-      </c>
-      <c r="K83" t="n">
-        <v>36</v>
-      </c>
       <c r="L83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>10.7</v>
+        <v>6.46</v>
       </c>
       <c r="N83" t="n">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="O83" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($385 to next deal) - confirm</t>
+          <t>Overstocked (10 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Barefoot Rose 750ml</t>
+          <t>Kim Crawford Sauvignon Blanc Illuminate 750ml</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>085000025871</t>
+          <t>689352010082</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="F84" t="n">
-        <v>11.5</v>
+        <v>11.1</v>
       </c>
       <c r="G84" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H84" t="n">
         <v>14.8</v>
       </c>
       <c r="I84" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J84" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K84" t="n">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="L84" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M84" t="n">
-        <v>4.4</v>
+        <v>10.7</v>
       </c>
       <c r="N84" t="n">
-        <v>422</v>
+        <v>385</v>
       </c>
       <c r="O84" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($422 to next deal) - confirm; Seasonal - last year ~15/wk vs 9 now, buy ahead?</t>
+          <t>Buy-month stock-up ($385 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Decoy Sonoma Chardonnay 750ml</t>
+          <t>Barefoot Rose 750ml</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>669576019245</t>
+          <t>085000025871</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>181</v>
+        <v>102</v>
       </c>
       <c r="F85" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="G85" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H85" t="n">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="I85" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J85" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K85" t="n">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M85" t="n">
-        <v>11.54</v>
+        <v>4.4</v>
       </c>
       <c r="N85" t="n">
-        <v>138</v>
+        <v>422</v>
       </c>
       <c r="O85" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($138 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($422 to next deal) - confirm; Seasonal - last year ~15/wk vs 9 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LaMarca Prosecco Demi Sec 750ml</t>
+          <t>Decoy Sonoma Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>085000040669</t>
+          <t>669576019245</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>117</v>
+        <v>181</v>
       </c>
       <c r="F86" t="n">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="G86" t="n">
-        <v>-5</v>
+        <v>14</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="I86" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J86" t="n">
+        <v>4</v>
+      </c>
+      <c r="K86" t="n">
         <v>12</v>
       </c>
-      <c r="K86" t="n">
-        <v>144</v>
-      </c>
       <c r="L86" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M86" t="n">
-        <v>12.48</v>
+        <v>11.54</v>
       </c>
       <c r="N86" t="n">
-        <v>1797</v>
+        <v>138</v>
       </c>
       <c r="O86" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,797 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($138 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Decoy Red Wine 750ml</t>
+          <t>LaMarca Prosecco Demi Sec 750ml</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>669576019207</t>
+          <t>085000040669</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="F87" t="n">
         <v>11.9</v>
       </c>
       <c r="G87" t="n">
-        <v>43</v>
+        <v>-5</v>
       </c>
       <c r="H87" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J87" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K87" t="n">
+        <v>144</v>
+      </c>
+      <c r="L87" t="n">
         <v>12</v>
       </c>
-      <c r="L87" t="n">
-        <v>1</v>
-      </c>
       <c r="M87" t="n">
-        <v>13.88</v>
+        <v>12.48</v>
       </c>
       <c r="N87" t="n">
-        <v>167</v>
+        <v>1797</v>
       </c>
       <c r="O87" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($167 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,797 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Quilt Napa Cabernet Sauvignon 750ml</t>
+          <t>Decoy Red Wine 750ml</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>859889006005</t>
+          <t>669576019207</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F88" t="n">
-        <v>12.3</v>
+        <v>11.9</v>
       </c>
       <c r="G88" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="H88" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="I88" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J88" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K88" t="n">
-        <v>168</v>
+        <v>12</v>
       </c>
       <c r="L88" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>33.37</v>
+        <v>13.88</v>
       </c>
       <c r="N88" t="n">
-        <v>5606</v>
+        <v>167</v>
       </c>
       <c r="O88" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>Large buy ($5,606) - confirm; Buy-month stock-up ($5,606 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($167 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Barefoot Peach Moscato 750ml</t>
+          <t>Quilt Napa Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>085000029008</t>
+          <t>859889006005</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>177</v>
+        <v>89</v>
       </c>
       <c r="F89" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="G89" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
       <c r="H89" t="n">
-        <v>33.2</v>
+        <v>4.2</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K89" t="n">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="L89" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M89" t="n">
-        <v>3.04</v>
+        <v>33.37</v>
       </c>
       <c r="N89" t="n">
-        <v>401</v>
+        <v>5606</v>
       </c>
       <c r="O89" t="n">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($401 to next deal) - confirm; Seasonal - last year ~33/wk vs 14 now, buy ahead?</t>
+          <t>Large buy ($5,606) - confirm; Buy-month stock-up ($5,606 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Barefoot Bright &amp; Breezy Pinot Grigio 750ml</t>
+          <t>Barefoot Peach Moscato 750ml</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>085000032879</t>
+          <t>085000029008</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5890,37 +5886,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>39</v>
+        <v>177</v>
       </c>
       <c r="F90" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="G90" t="n">
-        <v>129</v>
+        <v>-4</v>
       </c>
       <c r="H90" t="n">
-        <v>0.8</v>
+        <v>33.2</v>
       </c>
       <c r="I90" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="L90" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M90" t="n">
-        <v>4.5</v>
+        <v>3.04</v>
       </c>
       <c r="N90" t="n">
-        <v>162</v>
+        <v>401</v>
       </c>
       <c r="O90" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
@@ -5930,126 +5926,126 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($162 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($401 to next deal) - confirm; Seasonal - last year ~33/wk vs 14 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Decoy Zinfandel 750ml</t>
+          <t>Barefoot Bright &amp; Breezy Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>669576019238</t>
+          <t>085000032879</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F91" t="n">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="G91" t="n">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="H91" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="I91" t="n">
+        <v>10</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>36</v>
+      </c>
+      <c r="L91" t="n">
         <v>3</v>
       </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>12</v>
-      </c>
-      <c r="L91" t="n">
-        <v>1</v>
-      </c>
       <c r="M91" t="n">
-        <v>13.97</v>
+        <v>4.5</v>
       </c>
       <c r="N91" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="O91" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($168 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($162 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>LaMarca Prosecco Rose 750ml</t>
+          <t>Decoy Zinfandel 750ml</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>085000032442</t>
+          <t>669576019238</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="F92" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="G92" t="n">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="H92" t="n">
-        <v>9</v>
+        <v>1.8</v>
       </c>
       <c r="I92" t="n">
+        <v>3</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>12</v>
+      </c>
+      <c r="L92" t="n">
         <v>1</v>
       </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
-        <v>144</v>
-      </c>
-      <c r="L92" t="n">
-        <v>12</v>
-      </c>
       <c r="M92" t="n">
-        <v>12.15</v>
+        <v>13.97</v>
       </c>
       <c r="N92" t="n">
-        <v>1749</v>
+        <v>168</v>
       </c>
       <c r="O92" t="n">
         <v>42</v>
@@ -6057,29 +6053,29 @@
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,749 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($168 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Barefoot Riesling 750ml</t>
+          <t>LaMarca Prosecco Rose 750ml</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>085000015810</t>
+          <t>085000032442</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6088,154 +6084,154 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="F93" t="n">
         <v>13.3</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H93" t="n">
-        <v>11.2</v>
+        <v>9</v>
       </c>
       <c r="I93" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>72</v>
+        <v>144</v>
       </c>
       <c r="L93" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M93" t="n">
-        <v>4.33</v>
+        <v>12.15</v>
       </c>
       <c r="N93" t="n">
-        <v>312</v>
+        <v>1749</v>
       </c>
       <c r="O93" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($312 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,749 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cooks Brut 750ml</t>
+          <t>Barefoot Riesling 750ml</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>083804047211</t>
+          <t>085000015810</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>184</v>
+        <v>109</v>
       </c>
       <c r="F94" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="G94" t="n">
-        <v>-12</v>
+        <v>2</v>
       </c>
       <c r="H94" t="n">
-        <v>15</v>
+        <v>11.2</v>
       </c>
       <c r="I94" t="n">
+        <v>10</v>
+      </c>
+      <c r="J94" t="n">
+        <v>10</v>
+      </c>
+      <c r="K94" t="n">
+        <v>72</v>
+      </c>
+      <c r="L94" t="n">
         <v>6</v>
       </c>
-      <c r="J94" t="n">
-        <v>4</v>
-      </c>
-      <c r="K94" t="n">
-        <v>12</v>
-      </c>
-      <c r="L94" t="n">
-        <v>1</v>
-      </c>
       <c r="M94" t="n">
-        <v>5.77</v>
+        <v>4.33</v>
       </c>
       <c r="N94" t="n">
-        <v>69</v>
+        <v>312</v>
       </c>
       <c r="O94" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($69 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($312 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Apothic White 750ml</t>
+          <t>Cooks Brut 750ml</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>085000019733</t>
+          <t>083804047211</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>White Blends</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>74</v>
+        <v>184</v>
       </c>
       <c r="F95" t="n">
-        <v>13.8</v>
+        <v>13.4</v>
       </c>
       <c r="G95" t="n">
-        <v>-23</v>
+        <v>-12</v>
       </c>
       <c r="H95" t="n">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="I95" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K95" t="n">
         <v>12</v>
@@ -6244,61 +6240,61 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>7.22</v>
+        <v>5.77</v>
       </c>
       <c r="N95" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="O95" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($87 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($69 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Risata Red Moscato 750ml</t>
+          <t>Apothic White 750ml</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>084279999951</t>
+          <t>085000019733</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>White Blends</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="F96" t="n">
-        <v>14.2</v>
+        <v>13.8</v>
       </c>
       <c r="G96" t="n">
-        <v>-6</v>
+        <v>-23</v>
       </c>
       <c r="H96" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="I96" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -6310,106 +6306,106 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>11.03</v>
+        <v>7.22</v>
       </c>
       <c r="N96" t="n">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="O96" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr">
         <is>
-          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($132 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($87 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Barefoot White Zin 750ml</t>
+          <t>Risata Red Moscato 750ml</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>018341751062</t>
+          <t>084279999951</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F97" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G97" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H97" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I97" t="n">
+        <v>5</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>12</v>
+      </c>
+      <c r="L97" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="N97" t="n">
+        <v>132</v>
+      </c>
+      <c r="O97" t="n">
         <v>15</v>
-      </c>
-      <c r="G97" t="n">
-        <v>6</v>
-      </c>
-      <c r="H97" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I97" t="n">
-        <v>4</v>
-      </c>
-      <c r="J97" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" t="n">
-        <v>60</v>
-      </c>
-      <c r="L97" t="n">
-        <v>5</v>
-      </c>
-      <c r="M97" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="N97" t="n">
-        <v>262</v>
-      </c>
-      <c r="O97" t="n">
-        <v>45</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($262 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($132 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Barefoot Blueberry Moscato 750ml</t>
+          <t>Barefoot White Zin 750ml</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>085000031780</t>
+          <t>018341751062</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6418,19 +6414,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="F98" t="n">
-        <v>15.8</v>
+        <v>15</v>
       </c>
       <c r="G98" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="H98" t="n">
-        <v>14</v>
+        <v>6.8</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -6442,13 +6438,13 @@
         <v>5</v>
       </c>
       <c r="M98" t="n">
-        <v>4.22</v>
+        <v>4.37</v>
       </c>
       <c r="N98" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="O98" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
@@ -6458,24 +6454,24 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($253 to next deal) - confirm; Seasonal - last year ~14/wk vs 9 now, buy ahead?</t>
+          <t>Buy-month stock-up ($262 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Barefoot Chardonnay 750ml</t>
+          <t>Barefoot Blueberry Moscato 750ml</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>018341751055</t>
+          <t>085000031780</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6484,19 +6480,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F99" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="G99" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="H99" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I99" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -6508,13 +6504,13 @@
         <v>5</v>
       </c>
       <c r="M99" t="n">
-        <v>4.42</v>
+        <v>4.22</v>
       </c>
       <c r="N99" t="n">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="O99" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
@@ -6524,24 +6520,24 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($265 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($253 to next deal) - confirm; Seasonal - last year ~14/wk vs 9 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Barefoot Red Moscato 750ml</t>
+          <t>Barefoot Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>085000019894</t>
+          <t>018341751055</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6550,34 +6546,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="F100" t="n">
-        <v>17</v>
+        <v>15.9</v>
       </c>
       <c r="G100" t="n">
-        <v>-11</v>
+        <v>12</v>
       </c>
       <c r="H100" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="L100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M100" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="N100" t="n">
-        <v>158</v>
+        <v>265</v>
       </c>
       <c r="O100" t="n">
         <v>45</v>
@@ -6590,42 +6586,42 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($158 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($265 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Quilt Red Blend 750ml</t>
+          <t>Barefoot Red Moscato 750ml</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>859889006302</t>
+          <t>085000019894</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>8</v>
+        <v>115</v>
       </c>
       <c r="F101" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="G101" t="n">
-        <v>100</v>
+        <v>-11</v>
       </c>
       <c r="H101" t="n">
-        <v>0.8</v>
+        <v>6.5</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
@@ -6634,202 +6630,202 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M101" t="n">
-        <v>25.23</v>
+        <v>4.39</v>
       </c>
       <c r="N101" t="n">
-        <v>303</v>
+        <v>158</v>
       </c>
       <c r="O101" t="n">
-        <v>-5</v>
+        <v>45</v>
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>Margin looks off - check retail/cost; Buy-month stock-up ($303 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($158 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Barefoot Strawberry Moscato 750ml</t>
+          <t>Quilt Red Blend 750ml</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>085000029015</t>
+          <t>859889006302</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>161</v>
+        <v>8</v>
       </c>
       <c r="F102" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="G102" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="H102" t="n">
-        <v>14.8</v>
+        <v>0.8</v>
       </c>
       <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>12</v>
+      </c>
+      <c r="L102" t="n">
         <v>1</v>
       </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>48</v>
-      </c>
-      <c r="L102" t="n">
-        <v>4</v>
-      </c>
       <c r="M102" t="n">
-        <v>4.35</v>
+        <v>25.23</v>
       </c>
       <c r="N102" t="n">
-        <v>209</v>
+        <v>303</v>
       </c>
       <c r="O102" t="n">
-        <v>46</v>
+        <v>-5</v>
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($209 to next deal) - confirm; Seasonal - last year ~15/wk vs 9 now, buy ahead?</t>
+          <t>Margin looks off - check retail/cost; Buy-month stock-up ($303 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Risata Pink Moscato 750ml</t>
+          <t>Barefoot Strawberry Moscato 750ml</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>084279988108</t>
+          <t>085000029015</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="F103" t="n">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="G103" t="n">
-        <v>-8</v>
+        <v>3</v>
       </c>
       <c r="H103" t="n">
-        <v>9.800000000000001</v>
+        <v>14.8</v>
       </c>
       <c r="I103" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="L103" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M103" t="n">
-        <v>11.02</v>
+        <v>4.35</v>
       </c>
       <c r="N103" t="n">
-        <v>132</v>
+        <v>209</v>
       </c>
       <c r="O103" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
         <is>
-          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($132 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($209 to next deal) - confirm; Seasonal - last year ~15/wk vs 9 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Stags' Leap Cabernet Sauvignon Napa 750ml</t>
+          <t>Risata Pink Moscato 750ml</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>089819042401</t>
+          <t>084279988108</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>76</v>
+        <v>148</v>
       </c>
       <c r="F104" t="n">
-        <v>18.1</v>
+        <v>17.6</v>
       </c>
       <c r="G104" t="n">
-        <v>4</v>
+        <v>-8</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K104" t="n">
         <v>12</v>
@@ -6838,61 +6834,61 @@
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>39.89</v>
+        <v>11.02</v>
       </c>
       <c r="N104" t="n">
-        <v>479</v>
+        <v>132</v>
       </c>
       <c r="O104" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($479 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($132 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Apothic Crush 750ml</t>
+          <t>Stags' Leap Cabernet Sauvignon Napa 750ml</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>085000023488</t>
+          <t>089819042401</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>162</v>
+        <v>76</v>
       </c>
       <c r="F105" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="G105" t="n">
-        <v>-10</v>
+        <v>4</v>
       </c>
       <c r="H105" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -6904,40 +6900,40 @@
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>6.29</v>
+        <v>39.89</v>
       </c>
       <c r="N105" t="n">
-        <v>76</v>
+        <v>479</v>
       </c>
       <c r="O105" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($76 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($479 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Apothic Rose 750ml</t>
+          <t>Apothic Crush 750ml</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>085000021545</t>
+          <t>085000023488</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6946,16 +6942,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>49</v>
+        <v>162</v>
       </c>
       <c r="F106" t="n">
-        <v>19.1</v>
+        <v>18.3</v>
       </c>
       <c r="G106" t="n">
-        <v>10</v>
+        <v>-10</v>
       </c>
       <c r="H106" t="n">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="I106" t="n">
         <v>3</v>
@@ -6970,13 +6966,13 @@
         <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>6.89</v>
+        <v>6.29</v>
       </c>
       <c r="N106" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="O106" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr">
@@ -6986,24 +6982,24 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($83 to next deal) - confirm; Seasonal - last year ~5/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($76 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Barefoot Pear Moscato 750ml</t>
+          <t>Apothic Rose 750ml</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>085000037607</t>
+          <t>085000021545</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -7012,22 +7008,22 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F107" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="G107" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="H107" t="n">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="I107" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J107" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K107" t="n">
         <v>12</v>
@@ -7036,35 +7032,35 @@
         <v>1</v>
       </c>
       <c r="M107" t="n">
-        <v>4.32</v>
+        <v>6.89</v>
       </c>
       <c r="N107" t="n">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="O107" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~9/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($83 to next deal) - confirm; Seasonal - last year ~5/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Barefoot Watermelon Moscato 750ml</t>
+          <t>Barefoot Pear Moscato 750ml</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>085000029923</t>
+          <t>085000037607</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7078,22 +7074,22 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="F108" t="n">
         <v>19.3</v>
       </c>
       <c r="G108" t="n">
-        <v>-33</v>
+        <v>33</v>
       </c>
       <c r="H108" t="n">
-        <v>2.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K108" t="n">
         <v>12</v>
@@ -7102,7 +7098,7 @@
         <v>1</v>
       </c>
       <c r="M108" t="n">
-        <v>4.31</v>
+        <v>4.32</v>
       </c>
       <c r="N108" t="n">
         <v>52</v>
@@ -7118,45 +7114,45 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~3/wk vs 0 now, buy ahead?</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~9/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Les Allies Brut Sparkling Rose 750ml</t>
+          <t>Barefoot Watermelon Moscato 750ml</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>763955408108</t>
+          <t>085000029923</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Maverick Beverage Co., LLC - MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>110</v>
+        <v>9</v>
       </c>
       <c r="F109" t="n">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
       <c r="G109" t="n">
-        <v>-29</v>
+        <v>-33</v>
       </c>
       <c r="H109" t="n">
-        <v>13</v>
+        <v>2.8</v>
       </c>
       <c r="I109" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -7168,167 +7164,167 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>5.83</v>
+        <v>4.31</v>
       </c>
       <c r="N109" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="O109" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+        </is>
+      </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>Overstocked (20 wks on hand) - confirm before buying more; Seasonal - last year ~13/wk vs 6 now, buy ahead?</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~3/wk vs 0 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Belle Glos Dairyman Pinot Noir 750ml</t>
+          <t>Les Allies Brut Sparkling Rose 750ml</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>855622000811</t>
+          <t>763955408108</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Maverick Beverage Co., LLC - MN</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="F110" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="G110" t="n">
-        <v>17</v>
+        <v>-29</v>
       </c>
       <c r="H110" t="n">
-        <v>1.2</v>
+        <v>13</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="L110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>31.9</v>
+        <v>5.83</v>
       </c>
       <c r="N110" t="n">
-        <v>1149</v>
+        <v>70</v>
       </c>
       <c r="O110" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,149 to next deal) - confirm</t>
+          <t>Overstocked (20 wks on hand) - confirm before buying more; Seasonal - last year ~13/wk vs 6 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Apothic Cabernet Sauv 750ml</t>
+          <t>Belle Glos Dairyman Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>085000030967</t>
+          <t>855622000811</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>129</v>
+        <v>42</v>
       </c>
       <c r="F111" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="G111" t="n">
-        <v>-9</v>
+        <v>17</v>
       </c>
       <c r="H111" t="n">
-        <v>7</v>
+        <v>1.2</v>
       </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="L111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M111" t="n">
-        <v>7.28</v>
+        <v>31.9</v>
       </c>
       <c r="N111" t="n">
-        <v>87</v>
+        <v>1149</v>
       </c>
       <c r="O111" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($87 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,149 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Pizzolato Cabernet 750ml</t>
+          <t>Apothic Cabernet Sauv 750ml</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>185554000352</t>
+          <t>085000030967</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7338,20 +7334,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="F112" t="n">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="G112" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="H112" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I112" t="n">
         <v>2</v>
@@ -7366,40 +7362,40 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>3.84</v>
+        <v>7.28</v>
       </c>
       <c r="N112" t="n">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="O112" t="n">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($46 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($87 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Quilt Threadcount Red Blend 750ml</t>
+          <t>Pizzolato Cabernet 750ml</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>860009046009</t>
+          <t>185554000352</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -7408,64 +7404,64 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>30</v>
+        <v>171</v>
       </c>
       <c r="F113" t="n">
-        <v>21.4</v>
+        <v>20.9</v>
       </c>
       <c r="G113" t="n">
-        <v>-14</v>
+        <v>-3</v>
       </c>
       <c r="H113" t="n">
+        <v>2</v>
+      </c>
+      <c r="I113" t="n">
+        <v>2</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>12</v>
+      </c>
+      <c r="L113" t="n">
         <v>1</v>
       </c>
-      <c r="I113" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" t="n">
-        <v>0</v>
-      </c>
-      <c r="K113" t="n">
-        <v>24</v>
-      </c>
-      <c r="L113" t="n">
-        <v>2</v>
-      </c>
       <c r="M113" t="n">
-        <v>13.38</v>
+        <v>3.84</v>
       </c>
       <c r="N113" t="n">
-        <v>321</v>
+        <v>46</v>
       </c>
       <c r="O113" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($321 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($46 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Boen Tri Appellation Pinot Noir 750ml</t>
+          <t>Quilt Threadcount Red Blend 750ml</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>856184006112</t>
+          <t>860009046009</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7474,280 +7470,280 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>182</v>
+        <v>30</v>
       </c>
       <c r="F114" t="n">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="G114" t="n">
-        <v>6</v>
+        <v>-14</v>
       </c>
       <c r="H114" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M114" t="n">
-        <v>5.15</v>
+        <v>13.38</v>
       </c>
       <c r="N114" t="n">
-        <v>62</v>
+        <v>321</v>
       </c>
       <c r="O114" t="n">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($62 to next deal) - confirm; Seasonal - last year ~49/wk vs 8 now, buy ahead?</t>
+          <t>Buy-month stock-up ($321 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Cooks Brut 1.5L</t>
+          <t>Boen Tri Appellation Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>083804043152</t>
+          <t>856184006112</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>73</v>
+        <v>182</v>
       </c>
       <c r="F115" t="n">
-        <v>22.3</v>
+        <v>21.7</v>
       </c>
       <c r="G115" t="n">
-        <v>-29</v>
+        <v>6</v>
       </c>
       <c r="H115" t="n">
-        <v>4.2</v>
+        <v>49</v>
       </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K115" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L115" t="n">
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>10.33</v>
+        <v>5.15</v>
       </c>
       <c r="N115" t="n">
         <v>62</v>
       </c>
       <c r="O115" t="n">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($62 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($62 to next deal) - confirm; Seasonal - last year ~49/wk vs 8 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Belle Glos Clark &amp; Telephone 750ml</t>
+          <t>Cooks Brut 1.5L</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>855622000118</t>
+          <t>083804043152</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="F116" t="n">
-        <v>25.7</v>
+        <v>22.3</v>
       </c>
       <c r="G116" t="n">
-        <v>-25</v>
+        <v>-29</v>
       </c>
       <c r="H116" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I116" t="n">
         <v>2</v>
       </c>
-      <c r="I116" t="n">
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>6</v>
+      </c>
+      <c r="L116" t="n">
         <v>1</v>
       </c>
-      <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="n">
-        <v>24</v>
-      </c>
-      <c r="L116" t="n">
-        <v>2</v>
-      </c>
       <c r="M116" t="n">
-        <v>32.37</v>
+        <v>10.33</v>
       </c>
       <c r="N116" t="n">
-        <v>777</v>
+        <v>62</v>
       </c>
       <c r="O116" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($777 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($62 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ferrari Carano Fume Blanc 750ml</t>
+          <t>Belle Glos Clark &amp; Telephone 750ml</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>742651123102</t>
+          <t>855622000118</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>216</v>
+        <v>36</v>
       </c>
       <c r="F117" t="n">
-        <v>27.2</v>
+        <v>25.7</v>
       </c>
       <c r="G117" t="n">
-        <v>-11</v>
+        <v>-25</v>
       </c>
       <c r="H117" t="n">
-        <v>14.8</v>
+        <v>2</v>
       </c>
       <c r="I117" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>24</v>
+      </c>
+      <c r="L117" t="n">
         <v>2</v>
       </c>
-      <c r="J117" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" t="n">
-        <v>12</v>
-      </c>
-      <c r="L117" t="n">
-        <v>1</v>
-      </c>
       <c r="M117" t="n">
-        <v>9.99</v>
+        <v>32.37</v>
       </c>
       <c r="N117" t="n">
-        <v>120</v>
+        <v>777</v>
       </c>
       <c r="O117" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($120 to next deal) - confirm; Seasonal - last year ~15/wk vs 8 now, buy ahead?</t>
+          <t>Buy-month stock-up ($777 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Apothic Dark 750ml</t>
+          <t>Ferrari Carano Fume Blanc 750ml</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>085000022863</t>
+          <t>742651123102</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>26.75</v>
+        <v>216</v>
       </c>
       <c r="F118" t="n">
-        <v>28.7</v>
+        <v>27.2</v>
       </c>
       <c r="G118" t="n">
-        <v>20</v>
+        <v>-11</v>
       </c>
       <c r="H118" t="n">
-        <v>1.2</v>
+        <v>14.8</v>
       </c>
       <c r="I118" t="n">
         <v>2</v>
@@ -7762,61 +7758,61 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>7.37</v>
+        <v>9.99</v>
       </c>
       <c r="N118" t="n">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="O118" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($120 to next deal) - confirm; Seasonal - last year ~15/wk vs 8 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Acrobat Pinot Noir 750ml</t>
+          <t>Apothic Dark 750ml</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>768675085929</t>
+          <t>085000022863</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>69</v>
+        <v>26.75</v>
       </c>
       <c r="F119" t="n">
-        <v>29.6</v>
+        <v>28.7</v>
       </c>
       <c r="G119" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H119" t="n">
-        <v>3.8</v>
+        <v>1.2</v>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -7828,61 +7824,61 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>12.16</v>
+        <v>7.37</v>
       </c>
       <c r="N119" t="n">
-        <v>146</v>
+        <v>88</v>
       </c>
       <c r="O119" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, May, Aug, Sep, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($146 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Apothic Chardonnay 750ml</t>
+          <t>Acrobat Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>085000035405</t>
+          <t>768675085929</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="F120" t="n">
-        <v>33.4</v>
+        <v>29.6</v>
       </c>
       <c r="G120" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="H120" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="I120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -7894,61 +7890,61 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>7.69</v>
+        <v>12.16</v>
       </c>
       <c r="N120" t="n">
-        <v>92</v>
+        <v>146</v>
       </c>
       <c r="O120" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, Apr, May, Aug, Sep, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($146 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Cooks Spumante 750ml</t>
+          <t>Apothic Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>083804047198</t>
+          <t>085000035405</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>180</v>
+        <v>39</v>
       </c>
       <c r="F121" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="G121" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="H121" t="n">
-        <v>8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -7960,40 +7956,40 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>6</v>
+        <v>7.69</v>
       </c>
       <c r="N121" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="O121" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($72 to next deal) - confirm; Seasonal - last year ~9/wk vs 5 now, buy ahead?</t>
+          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Charles Smith Velvet Devil Merlot 750ml</t>
+          <t>Cooks Spumante 750ml</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>083120015055</t>
+          <t>083804047198</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Merlot</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -8002,19 +7998,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="F122" t="n">
-        <v>36.3</v>
+        <v>33.5</v>
       </c>
       <c r="G122" t="n">
-        <v>-5</v>
+        <v>8</v>
       </c>
       <c r="H122" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -8026,40 +8022,40 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>7.29</v>
+        <v>6</v>
       </c>
       <c r="N122" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="O122" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($72 to next deal) - confirm; Seasonal - last year ~9/wk vs 5 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Saldo Zinfandel 750ml</t>
+          <t>Charles Smith Velvet Devil Merlot 750ml</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>086003258006</t>
+          <t>083120015055</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -8068,16 +8064,16 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F123" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="G123" t="n">
-        <v>-16</v>
+        <v>-5</v>
       </c>
       <c r="H123" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="I123" t="n">
         <v>1</v>
@@ -8092,58 +8088,58 @@
         <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>20.33</v>
+        <v>7.29</v>
       </c>
       <c r="N123" t="n">
-        <v>244</v>
+        <v>88</v>
       </c>
       <c r="O123" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($244 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Apothic Merlot 750ml</t>
+          <t>Saldo Zinfandel 750ml</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>085000032145</t>
+          <t>086003258006</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Merlot</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="F124" t="n">
-        <v>36.7</v>
+        <v>36.4</v>
       </c>
       <c r="G124" t="n">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="H124" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="I124" t="n">
         <v>1</v>
@@ -8158,40 +8154,40 @@
         <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>7.37</v>
+        <v>20.33</v>
       </c>
       <c r="N124" t="n">
-        <v>88</v>
+        <v>244</v>
       </c>
       <c r="O124" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($244 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Apothic Inferno 750ml</t>
+          <t>Apothic Merlot 750ml</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>085000024904</t>
+          <t>085000032145</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -8200,16 +8196,16 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>207</v>
+        <v>137</v>
       </c>
       <c r="F125" t="n">
-        <v>42.2</v>
+        <v>36.7</v>
       </c>
       <c r="G125" t="n">
-        <v>-24</v>
+        <v>-8</v>
       </c>
       <c r="H125" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="I125" t="n">
         <v>1</v>
@@ -8224,10 +8220,10 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>8.56</v>
+        <v>7.37</v>
       </c>
       <c r="N125" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="O125" t="n">
         <v>43</v>
@@ -8240,24 +8236,24 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($103 to next deal) - confirm; Seasonal - last year ~8/wk vs 5 now, buy ahead?</t>
+          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Apothic Pinot Noir 750ml</t>
+          <t>Apothic Inferno 750ml</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>085000032336</t>
+          <t>085000024904</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -8266,16 +8262,16 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
       <c r="F126" t="n">
-        <v>56.5</v>
+        <v>42.2</v>
       </c>
       <c r="G126" t="n">
-        <v>-31</v>
+        <v>-24</v>
       </c>
       <c r="H126" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="I126" t="n">
         <v>1</v>
@@ -8290,13 +8286,13 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>7.14</v>
+        <v>8.56</v>
       </c>
       <c r="N126" t="n">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="O126" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr">
@@ -8305,6 +8301,72 @@
         </is>
       </c>
       <c r="S126" t="inlineStr">
+        <is>
+          <t>Buy-month stock-up ($103 to next deal) - confirm; Seasonal - last year ~8/wk vs 5 now, buy ahead?</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Apothic Pinot Noir 750ml</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>085000032336</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Pinot Noir</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Johnson Brothers - St. Paul</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>145</v>
+      </c>
+      <c r="F127" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G127" t="n">
+        <v>-31</v>
+      </c>
+      <c r="H127" t="n">
+        <v>3</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>12</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1</v>
+      </c>
+      <c r="M127" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="N127" t="n">
+        <v>86</v>
+      </c>
+      <c r="O127" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
         <is>
           <t>Buy-month stock-up ($86 to next deal) - confirm</t>
         </is>

--- a/data/Wine Recommended Order.xlsx
+++ b/data/Wine Recommended Order.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recommended Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Needs Review" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Being Removed" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy-Month Wait" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transfer Plan" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S133"/>
+  <dimension ref="A1:S132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4542,79 +4542,83 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>La Vieille Ferme Rose 750ml</t>
+          <t>Barefoot Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>089419000177</t>
+          <t>085000014448</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>The Wine Company</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>440</v>
+        <v>131</v>
       </c>
       <c r="F70" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="G70" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H70" t="n">
-        <v>45.5</v>
+        <v>27.2</v>
       </c>
       <c r="I70" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="K70" t="n">
-        <v>12</v>
+        <v>420</v>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="M70" t="n">
-        <v>6.52</v>
+        <v>4.32</v>
       </c>
       <c r="N70" t="n">
-        <v>78</v>
+        <v>1815</v>
       </c>
       <c r="O70" t="n">
-        <v>53</v>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>ON AD - Sunday special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Buy-month stock-up ($1,815 to next deal) - confirm</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Barefoot Pinot Grigio 750ml</t>
+          <t>Barefoot Pink Moscato 750ml</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>085000014448</t>
+          <t>085000020456</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4623,34 +4627,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="F71" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="G71" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H71" t="n">
-        <v>27.2</v>
+        <v>36</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="J71" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K71" t="n">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="L71" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M71" t="n">
         <v>4.32</v>
       </c>
       <c r="N71" t="n">
-        <v>1815</v>
+        <v>1763</v>
       </c>
       <c r="O71" t="n">
         <v>46</v>
@@ -4663,19 +4667,19 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,815 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,763 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Barefoot Pink Moscato 750ml</t>
+          <t>Barefoot Sweet Red 750ml</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>085000020456</t>
+          <t>085000018491</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4689,37 +4693,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="F72" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="G72" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="H72" t="n">
-        <v>36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="J72" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>408</v>
+        <v>60</v>
       </c>
       <c r="L72" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="M72" t="n">
-        <v>4.32</v>
+        <v>4.24</v>
       </c>
       <c r="N72" t="n">
-        <v>1763</v>
+        <v>254</v>
       </c>
       <c r="O72" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
@@ -4729,288 +4733,288 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,763 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($254 to next deal) - confirm; Seasonal - last year ~10/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Barefoot Sweet Red 750ml</t>
+          <t>Underwood Pinot Gris 375ml</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>085000018491</t>
+          <t>856036001067</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E73" t="n">
+        <v>77</v>
+      </c>
+      <c r="F73" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="G73" t="n">
+        <v>43</v>
+      </c>
+      <c r="H73" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I73" t="n">
+        <v>25</v>
+      </c>
+      <c r="J73" t="n">
         <v>20</v>
       </c>
-      <c r="F73" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="G73" t="n">
-        <v>31</v>
-      </c>
-      <c r="H73" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="I73" t="n">
-        <v>5</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
       <c r="K73" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="L73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M73" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="N73" t="n">
-        <v>254</v>
+        <v>152</v>
       </c>
       <c r="O73" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($254 to next deal) - confirm; Seasonal - last year ~10/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($152 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Underwood Pinot Gris 375ml</t>
+          <t>Barefoot Apple Moscato 750ml</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>856036001067</t>
+          <t>085000029022</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="F74" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="G74" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="H74" t="n">
-        <v>8.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="I74" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="J74" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K74" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L74" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M74" t="n">
-        <v>4.21</v>
+        <v>4.35</v>
       </c>
       <c r="N74" t="n">
-        <v>152</v>
+        <v>522</v>
       </c>
       <c r="O74" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($152 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($522 to next deal) - confirm; Seasonal - last year ~16/wk vs 8 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Barefoot Apple Moscato 750ml</t>
+          <t>Decoy Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>085000029022</t>
+          <t>669576019269</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>50</v>
+        <v>225</v>
       </c>
       <c r="F75" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="G75" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H75" t="n">
-        <v>15.5</v>
+        <v>29.5</v>
       </c>
       <c r="I75" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J75" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K75" t="n">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="L75" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M75" t="n">
-        <v>4.35</v>
+        <v>13.54</v>
       </c>
       <c r="N75" t="n">
-        <v>522</v>
+        <v>975</v>
       </c>
       <c r="O75" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($522 to next deal) - confirm; Seasonal - last year ~16/wk vs 8 now, buy ahead?</t>
+          <t>Buy-month stock-up ($975 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Decoy Cabernet Sauvignon 750ml</t>
+          <t>Risata Moscato d'Asti 750ml</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>669576019269</t>
+          <t>084279977638</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Moscato</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>225</v>
+        <v>341.9996</v>
       </c>
       <c r="F76" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="G76" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>29.5</v>
+        <v>48.5</v>
       </c>
       <c r="I76" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="K76" t="n">
-        <v>72</v>
+        <v>288</v>
       </c>
       <c r="L76" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M76" t="n">
-        <v>13.54</v>
+        <v>1.17</v>
       </c>
       <c r="N76" t="n">
-        <v>975</v>
+        <v>337</v>
       </c>
       <c r="O76" t="n">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($975 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($337 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Risata Moscato d'Asti 750ml</t>
+          <t>Santa Margherita Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>084279977638</t>
+          <t>086891022871</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Moscato</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5019,64 +5023,68 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>341.9996</v>
+        <v>279</v>
       </c>
       <c r="F77" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H77" t="n">
-        <v>48.5</v>
+        <v>33.5</v>
       </c>
       <c r="I77" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J77" t="n">
         <v>22</v>
       </c>
       <c r="K77" t="n">
-        <v>288</v>
+        <v>12</v>
       </c>
       <c r="L77" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>1.17</v>
+        <v>19.5</v>
       </c>
       <c r="N77" t="n">
-        <v>337</v>
+        <v>234</v>
       </c>
       <c r="O77" t="n">
-        <v>92</v>
-      </c>
-      <c r="Q77" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Mar, May, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($337 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($234 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Santa Margherita Pinot Grigio 750ml</t>
+          <t>Risata Prosecco 750ml</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>086891022871</t>
+          <t>084279992464</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5085,261 +5093,257 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>279</v>
+        <v>152</v>
       </c>
       <c r="F78" t="n">
         <v>7.5</v>
       </c>
       <c r="G78" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H78" t="n">
-        <v>33.5</v>
+        <v>7</v>
       </c>
       <c r="I78" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K78" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M78" t="n">
-        <v>19.5</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="N78" t="n">
-        <v>234</v>
+        <v>1075</v>
       </c>
       <c r="O78" t="n">
         <v>25</v>
       </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
+      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, May, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($234 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,075 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Risata Prosecco 750ml</t>
+          <t>Frank Family Cabernet 750ml</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>084279992464</t>
+          <t>894910000409</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>152</v>
+        <v>28</v>
       </c>
       <c r="F79" t="n">
         <v>7.5</v>
       </c>
       <c r="G79" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="H79" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="L79" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>8.960000000000001</v>
+        <v>38.15</v>
       </c>
       <c r="N79" t="n">
-        <v>1075</v>
+        <v>458</v>
       </c>
       <c r="O79" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
-          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,075 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($458 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Frank Family Cabernet 750ml</t>
+          <t>Colle Corviano Cerasuolo Rose 750ml</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>894910000409</t>
+          <t>181856000892</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Small Lot MN</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="F80" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="G80" t="n">
-        <v>30</v>
+        <v>-43</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K80" t="n">
-        <v>12</v>
+        <v>288</v>
       </c>
       <c r="L80" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="M80" t="n">
-        <v>38.15</v>
+        <v>6</v>
       </c>
       <c r="N80" t="n">
-        <v>458</v>
+        <v>1729</v>
       </c>
       <c r="O80" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Apr, May, Jun, Jul, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($458 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,729 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Colle Corviano Cerasuolo Rose 750ml</t>
+          <t>Barefoot Sauv Blanc 750ml</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>181856000892</t>
+          <t>018341751024</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Small Lot MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="F81" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="G81" t="n">
-        <v>-43</v>
+        <v>38</v>
       </c>
       <c r="H81" t="n">
-        <v>15.2</v>
+        <v>3.5</v>
       </c>
       <c r="I81" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K81" t="n">
-        <v>288</v>
+        <v>180</v>
       </c>
       <c r="L81" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="M81" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="N81" t="n">
-        <v>1729</v>
+        <v>780</v>
       </c>
       <c r="O81" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, May, Jun, Jul, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,729 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($780 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Barefoot Sauv Blanc 750ml</t>
+          <t>Decoy Sauvignon Blanc 750ml</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>018341751024</t>
+          <t>669576019214</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5349,332 +5353,332 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F82" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="H82" t="n">
-        <v>3.5</v>
+        <v>14.5</v>
       </c>
       <c r="I82" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J82" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K82" t="n">
-        <v>180</v>
+        <v>12</v>
       </c>
       <c r="L82" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="M82" t="n">
-        <v>4.33</v>
+        <v>10.94</v>
       </c>
       <c r="N82" t="n">
-        <v>780</v>
+        <v>131</v>
       </c>
       <c r="O82" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($780 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($131 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Decoy Sauvignon Blanc 750ml</t>
+          <t>Barefoot Pineapple Moscato 750ml</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>669576019214</t>
+          <t>085000033319</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="F83" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="G83" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H83" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="I83" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K83" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="L83" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M83" t="n">
-        <v>10.94</v>
+        <v>4.36</v>
       </c>
       <c r="N83" t="n">
-        <v>131</v>
+        <v>209</v>
       </c>
       <c r="O83" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($131 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($209 to next deal) - confirm; Seasonal - last year ~8/wk vs 4 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Barefoot Pineapple Moscato 750ml</t>
+          <t>90+ Cellars Sauvignon Blanc Cali 750ml</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>085000033319</t>
+          <t>894655001822</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>30</v>
+        <v>239</v>
       </c>
       <c r="F84" t="n">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="G84" t="n">
-        <v>18</v>
+        <v>-9</v>
       </c>
       <c r="H84" t="n">
-        <v>8</v>
+        <v>30.8</v>
       </c>
       <c r="I84" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="K84" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="L84" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M84" t="n">
-        <v>4.36</v>
+        <v>6.47</v>
       </c>
       <c r="N84" t="n">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="O84" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
-        </is>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($209 to next deal) - confirm; Seasonal - last year ~8/wk vs 4 now, buy ahead?</t>
+          <t>Overstocked (9 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>90+ Cellars Sauvignon Blanc Cali 750ml</t>
+          <t>Barefoot Moscato 750ml</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>894655001822</t>
+          <t>085000016688</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Moscato</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>239</v>
+        <v>175</v>
       </c>
       <c r="F85" t="n">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="G85" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>30.8</v>
+        <v>34.8</v>
       </c>
       <c r="I85" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="J85" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>12</v>
+        <v>240</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="M85" t="n">
-        <v>6.47</v>
+        <v>4.32</v>
       </c>
       <c r="N85" t="n">
-        <v>78</v>
+        <v>1038</v>
       </c>
       <c r="O85" t="n">
-        <v>60</v>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+        </is>
+      </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>Overstocked (9 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($1,038 to next deal) - confirm; Seasonal - last year ~35/wk vs 19 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Barefoot Moscato 750ml</t>
+          <t>Robert Mondavi PS Cab Sauv BB 750ml</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>085000016688</t>
+          <t>086003780217</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Moscato</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>175</v>
+        <v>112</v>
       </c>
       <c r="F86" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H86" t="n">
-        <v>34.8</v>
+        <v>4.5</v>
       </c>
       <c r="I86" t="n">
+        <v>17</v>
+      </c>
+      <c r="J86" t="n">
+        <v>16</v>
+      </c>
+      <c r="K86" t="n">
+        <v>48</v>
+      </c>
+      <c r="L86" t="n">
         <v>4</v>
       </c>
-      <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>240</v>
-      </c>
-      <c r="L86" t="n">
-        <v>20</v>
-      </c>
       <c r="M86" t="n">
-        <v>4.32</v>
+        <v>8.69</v>
       </c>
       <c r="N86" t="n">
-        <v>1038</v>
+        <v>417</v>
       </c>
       <c r="O86" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,038 to next deal) - confirm; Seasonal - last year ~35/wk vs 19 now, buy ahead?</t>
+          <t>Buy-month stock-up ($417 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Robert Mondavi PS Cab Sauv BB 750ml</t>
+          <t>Cooks Brut 750ml</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>086003780217</t>
+          <t>083804047211</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5683,100 +5687,100 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>112</v>
+        <v>169</v>
       </c>
       <c r="F87" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H87" t="n">
-        <v>4.5</v>
+        <v>17.5</v>
       </c>
       <c r="I87" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J87" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K87" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="L87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M87" t="n">
-        <v>8.69</v>
+        <v>5.86</v>
       </c>
       <c r="N87" t="n">
-        <v>417</v>
+        <v>351</v>
       </c>
       <c r="O87" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($417 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($351 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cooks Brut 750ml</t>
+          <t>Decoy Red Wine 750ml</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>083804047211</t>
+          <t>669576019207</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>169</v>
+        <v>80</v>
       </c>
       <c r="F88" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="G88" t="n">
+        <v>50</v>
+      </c>
+      <c r="H88" t="n">
+        <v>2</v>
+      </c>
+      <c r="I88" t="n">
+        <v>7</v>
+      </c>
+      <c r="J88" t="n">
         <v>6</v>
       </c>
-      <c r="H88" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="I88" t="n">
-        <v>14</v>
-      </c>
-      <c r="J88" t="n">
-        <v>9</v>
-      </c>
       <c r="K88" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="L88" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>5.86</v>
+        <v>14.19</v>
       </c>
       <c r="N88" t="n">
-        <v>351</v>
+        <v>170</v>
       </c>
       <c r="O88" t="n">
         <v>41</v>
@@ -5784,119 +5788,119 @@
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($351 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($170 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Decoy Red Wine 750ml</t>
+          <t>Risata Red Moscato 750ml</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>669576019207</t>
+          <t>084279999951</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="F89" t="n">
-        <v>10.1</v>
+        <v>10.9</v>
       </c>
       <c r="G89" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="H89" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="I89" t="n">
         <v>7</v>
       </c>
       <c r="J89" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M89" t="n">
-        <v>14.19</v>
+        <v>11.03</v>
       </c>
       <c r="N89" t="n">
-        <v>170</v>
+        <v>397</v>
       </c>
       <c r="O89" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($170 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($397 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Risata Red Moscato 750ml</t>
+          <t>Kim Crawford Sauvignon Blanc Illuminate 750ml</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>084279999951</t>
+          <t>689352010082</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Sauvignon Blanc</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="F90" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="G90" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>5.8</v>
+        <v>15.8</v>
       </c>
       <c r="I90" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K90" t="n">
         <v>36</v>
@@ -5905,167 +5909,167 @@
         <v>3</v>
       </c>
       <c r="M90" t="n">
-        <v>11.03</v>
+        <v>10.7</v>
       </c>
       <c r="N90" t="n">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="O90" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
-          <t>In buy-month (Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($397 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($385 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Kim Crawford Sauvignon Blanc Illuminate 750ml</t>
+          <t>Barefoot Rose 750ml</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>689352010082</t>
+          <t>085000025871</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="F91" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="G91" t="n">
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>15.8</v>
+        <v>13.2</v>
       </c>
       <c r="I91" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J91" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K91" t="n">
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="L91" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M91" t="n">
-        <v>10.7</v>
+        <v>4.4</v>
       </c>
       <c r="N91" t="n">
-        <v>385</v>
+        <v>423</v>
       </c>
       <c r="O91" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($385 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($423 to next deal) - confirm; Seasonal - last year ~13/wk vs 8 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Barefoot Rose 750ml</t>
+          <t>Pacific Rim Sweet Riesling 750ml</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>085000025871</t>
+          <t>899552102276</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="F92" t="n">
-        <v>11.3</v>
+        <v>11.8</v>
       </c>
       <c r="G92" t="n">
+        <v>-27</v>
+      </c>
+      <c r="H92" t="n">
+        <v>4</v>
+      </c>
+      <c r="I92" t="n">
+        <v>4</v>
+      </c>
+      <c r="J92" t="n">
+        <v>4</v>
+      </c>
+      <c r="K92" t="n">
+        <v>12</v>
+      </c>
+      <c r="L92" t="n">
         <v>1</v>
       </c>
-      <c r="H92" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="I92" t="n">
-        <v>9</v>
-      </c>
-      <c r="J92" t="n">
-        <v>9</v>
-      </c>
-      <c r="K92" t="n">
-        <v>96</v>
-      </c>
-      <c r="L92" t="n">
-        <v>8</v>
-      </c>
       <c r="M92" t="n">
-        <v>4.4</v>
+        <v>5.78</v>
       </c>
       <c r="N92" t="n">
-        <v>423</v>
+        <v>69</v>
       </c>
       <c r="O92" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Jan, Feb, Jul, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($423 to next deal) - confirm; Seasonal - last year ~13/wk vs 8 now, buy ahead?</t>
+          <t>Buy-month stock-up ($69 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Pacific Rim Sweet Riesling 750ml</t>
+          <t>Charles Smith Kung Fu Girl Riesling 750ml</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>899552102276</t>
+          <t>083120015048</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6075,23 +6079,23 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="F93" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="G93" t="n">
-        <v>-27</v>
+        <v>-19</v>
       </c>
       <c r="H93" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="I93" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J93" t="n">
         <v>4</v>
@@ -6103,106 +6107,106 @@
         <v>1</v>
       </c>
       <c r="M93" t="n">
-        <v>5.78</v>
+        <v>7.51</v>
       </c>
       <c r="N93" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="O93" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Feb, Jul, Aug, Nov, Dec) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($69 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($90 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Charles Smith Kung Fu Girl Riesling 750ml</t>
+          <t>Barefoot Peach Moscato 750ml</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>083120015048</t>
+          <t>085000029008</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="F94" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="G94" t="n">
-        <v>-19</v>
+        <v>-8</v>
       </c>
       <c r="H94" t="n">
-        <v>5.8</v>
+        <v>29.2</v>
       </c>
       <c r="I94" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
+        <v>144</v>
+      </c>
+      <c r="L94" t="n">
         <v>12</v>
       </c>
-      <c r="L94" t="n">
-        <v>1</v>
-      </c>
       <c r="M94" t="n">
-        <v>7.51</v>
+        <v>2.92</v>
       </c>
       <c r="N94" t="n">
-        <v>90</v>
+        <v>421</v>
       </c>
       <c r="O94" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($90 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($421 to next deal) - confirm; Seasonal - last year ~29/wk vs 14 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Barefoot Peach Moscato 750ml</t>
+          <t>Apothic White 750ml</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>085000029008</t>
+          <t>085000019733</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>White Blends</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6211,85 +6215,85 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>162</v>
+        <v>68</v>
       </c>
       <c r="F95" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G95" t="n">
+        <v>-24</v>
+      </c>
+      <c r="H95" t="n">
+        <v>6</v>
+      </c>
+      <c r="I95" t="n">
+        <v>8</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
         <v>12</v>
       </c>
-      <c r="G95" t="n">
-        <v>-8</v>
-      </c>
-      <c r="H95" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="I95" t="n">
+      <c r="L95" t="n">
         <v>1</v>
       </c>
-      <c r="J95" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" t="n">
-        <v>144</v>
-      </c>
-      <c r="L95" t="n">
-        <v>12</v>
-      </c>
       <c r="M95" t="n">
-        <v>2.92</v>
+        <v>7.25</v>
       </c>
       <c r="N95" t="n">
-        <v>421</v>
+        <v>87</v>
       </c>
       <c r="O95" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($421 to next deal) - confirm; Seasonal - last year ~29/wk vs 14 now, buy ahead?</t>
+          <t>Buy-month stock-up ($87 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Apothic White 750ml</t>
+          <t>90+ Cellars Lot 210 Paso Robles Cabernet Sauvignon  750ml</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>085000019733</t>
+          <t>810879020838</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>White Blends</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Bellboy Corporation</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>68</v>
+        <v>395</v>
       </c>
       <c r="F96" t="n">
-        <v>12.1</v>
+        <v>12.5</v>
       </c>
       <c r="G96" t="n">
-        <v>-24</v>
+        <v>7</v>
       </c>
       <c r="H96" t="n">
-        <v>6</v>
+        <v>25.2</v>
       </c>
       <c r="I96" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -6301,142 +6305,142 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>7.25</v>
+        <v>8.57</v>
       </c>
       <c r="N96" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="O96" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($87 to next deal) - confirm</t>
+          <t>Overstocked (12 wks on hand) - confirm before buying more</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>90+ Cellars Lot 210 Paso Robles Cabernet Sauvignon  750ml</t>
+          <t>LaMarca Prosecco Rose 750ml</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>810879020838</t>
+          <t>085000032442</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Bellboy Corporation</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>395</v>
+        <v>138</v>
       </c>
       <c r="F97" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="G97" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H97" t="n">
-        <v>25.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>12</v>
+        <v>156</v>
       </c>
       <c r="L97" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M97" t="n">
-        <v>8.57</v>
+        <v>12.17</v>
       </c>
       <c r="N97" t="n">
-        <v>103</v>
+        <v>1898</v>
       </c>
       <c r="O97" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R97" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+        </is>
+      </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Overstocked (12 wks on hand) - confirm before buying more</t>
+          <t>Buy-month stock-up ($1,898 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LaMarca Prosecco Rose 750ml</t>
+          <t>Decoy Zinfandel 750ml</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>085000032442</t>
+          <t>669576019238</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>138</v>
+        <v>55</v>
       </c>
       <c r="F98" t="n">
-        <v>12.6</v>
+        <v>13.1</v>
       </c>
       <c r="G98" t="n">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="H98" t="n">
-        <v>8.800000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="I98" t="n">
+        <v>3</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>12</v>
+      </c>
+      <c r="L98" t="n">
         <v>1</v>
       </c>
-      <c r="J98" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" t="n">
-        <v>156</v>
-      </c>
-      <c r="L98" t="n">
-        <v>13</v>
-      </c>
       <c r="M98" t="n">
-        <v>12.17</v>
+        <v>13.97</v>
       </c>
       <c r="N98" t="n">
-        <v>1898</v>
+        <v>168</v>
       </c>
       <c r="O98" t="n">
         <v>42</v>
@@ -6444,222 +6448,222 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,898 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($168 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Decoy Zinfandel 750ml</t>
+          <t>LaMarca Prosecco Demi Sec 750ml</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>669576019238</t>
+          <t>085000040669</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="F99" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="G99" t="n">
-        <v>93</v>
+        <v>-16</v>
       </c>
       <c r="H99" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K99" t="n">
-        <v>12</v>
+        <v>108</v>
       </c>
       <c r="L99" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M99" t="n">
-        <v>13.97</v>
+        <v>12.48</v>
       </c>
       <c r="N99" t="n">
-        <v>168</v>
+        <v>1348</v>
       </c>
       <c r="O99" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
         <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($168 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,348 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LaMarca Prosecco Demi Sec 750ml</t>
+          <t>Quilt Napa Cabernet Sauvignon 750ml</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>085000040669</t>
+          <t>859889006005</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="F100" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="G100" t="n">
-        <v>-16</v>
+        <v>9</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I100" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J100" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K100" t="n">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="L100" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M100" t="n">
-        <v>12.48</v>
+        <v>33.6</v>
       </c>
       <c r="N100" t="n">
-        <v>1348</v>
+        <v>5241</v>
       </c>
       <c r="O100" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug) - stock up ~26wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,348 to next deal) - confirm</t>
+          <t>Large buy ($5,241) - confirm; Buy-month stock-up ($5,241 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Quilt Napa Cabernet Sauvignon 750ml</t>
+          <t>Barefoot Sangria 750ml</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>859889006005</t>
+          <t>085000025055</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>98</v>
+        <v>13</v>
       </c>
       <c r="F101" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="G101" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="H101" t="n">
-        <v>4.2</v>
+        <v>0.2</v>
       </c>
       <c r="I101" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>156</v>
+        <v>12</v>
       </c>
       <c r="L101" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>33.6</v>
+        <v>4.32</v>
       </c>
       <c r="N101" t="n">
-        <v>5241</v>
+        <v>52</v>
       </c>
       <c r="O101" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>Large buy ($5,241) - confirm; Buy-month stock-up ($5,241 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Barefoot Sangria 750ml</t>
+          <t>Barefoot Red Moscato 750ml</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>085000025055</t>
+          <t>085000019894</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6673,37 +6677,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>13</v>
+        <v>109</v>
       </c>
       <c r="F102" t="n">
-        <v>13.9</v>
+        <v>14.2</v>
       </c>
       <c r="G102" t="n">
-        <v>50</v>
+        <v>-3</v>
       </c>
       <c r="H102" t="n">
-        <v>0.2</v>
+        <v>5.2</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="L102" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M102" t="n">
-        <v>4.32</v>
+        <v>4.39</v>
       </c>
       <c r="N102" t="n">
-        <v>52</v>
+        <v>263</v>
       </c>
       <c r="O102" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
@@ -6713,19 +6717,19 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($263 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Barefoot Red Moscato 750ml</t>
+          <t>Barefoot Blueberry Moscato 750ml</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>085000019894</t>
+          <t>085000031780</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6739,37 +6743,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="F103" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="G103" t="n">
-        <v>-3</v>
+        <v>50</v>
       </c>
       <c r="H103" t="n">
-        <v>5.2</v>
+        <v>14.8</v>
       </c>
       <c r="I103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="L103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M103" t="n">
-        <v>4.39</v>
+        <v>4.22</v>
       </c>
       <c r="N103" t="n">
-        <v>263</v>
+        <v>304</v>
       </c>
       <c r="O103" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
@@ -6779,24 +6783,24 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($263 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($304 to next deal) - confirm; Seasonal - last year ~15/wk vs 9 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Barefoot Blueberry Moscato 750ml</t>
+          <t>Barefoot White Zin 750ml</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>085000031780</t>
+          <t>018341751062</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Zinfandel</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6805,37 +6809,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="F104" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="G104" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>14.8</v>
+        <v>7.8</v>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K104" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="L104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M104" t="n">
-        <v>4.22</v>
+        <v>4.37</v>
       </c>
       <c r="N104" t="n">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="O104" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
@@ -6845,24 +6849,24 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($304 to next deal) - confirm; Seasonal - last year ~15/wk vs 9 now, buy ahead?</t>
+          <t>Buy-month stock-up ($262 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Barefoot White Zin 750ml</t>
+          <t>Barefoot Strawberry Moscato 750ml</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>018341751062</t>
+          <t>085000029015</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Zinfandel</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6871,37 +6875,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="F105" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H105" t="n">
-        <v>7.8</v>
+        <v>15.2</v>
       </c>
       <c r="I105" t="n">
+        <v>2</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>72</v>
+      </c>
+      <c r="L105" t="n">
         <v>6</v>
       </c>
-      <c r="J105" t="n">
-        <v>5</v>
-      </c>
-      <c r="K105" t="n">
-        <v>60</v>
-      </c>
-      <c r="L105" t="n">
-        <v>5</v>
-      </c>
       <c r="M105" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="N105" t="n">
-        <v>262</v>
+        <v>313</v>
       </c>
       <c r="O105" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr">
@@ -6911,156 +6915,156 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($262 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($313 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Barefoot Strawberry Moscato 750ml</t>
+          <t>Belle Glos Clark &amp; Telephone 750ml</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>085000029015</t>
+          <t>855622000118</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>153</v>
+        <v>35</v>
       </c>
       <c r="F106" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="G106" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H106" t="n">
-        <v>15.2</v>
+        <v>4</v>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L106" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M106" t="n">
-        <v>4.35</v>
+        <v>32.35</v>
       </c>
       <c r="N106" t="n">
-        <v>313</v>
+        <v>1553</v>
       </c>
       <c r="O106" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($313 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($1,553 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Belle Glos Clark &amp; Telephone 750ml</t>
+          <t>Barefoot Riesling 750ml</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>855622000118</t>
+          <t>085000015810</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Other Whites</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="F107" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="G107" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H107" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="I107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="L107" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M107" t="n">
-        <v>32.35</v>
+        <v>4.33</v>
       </c>
       <c r="N107" t="n">
-        <v>1553</v>
+        <v>260</v>
       </c>
       <c r="O107" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($1,553 to next deal) - confirm; Seasonal - last year ~4/wk vs 2 now, buy ahead?</t>
+          <t>Buy-month stock-up ($260 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Barefoot Riesling 750ml</t>
+          <t>Apothic Rose 750ml</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>085000015810</t>
+          <t>085000021545</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Other Whites</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -7069,88 +7073,88 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="F108" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="G108" t="n">
+        <v>30</v>
+      </c>
+      <c r="H108" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I108" t="n">
+        <v>2</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>12</v>
+      </c>
+      <c r="L108" t="n">
         <v>1</v>
       </c>
-      <c r="H108" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="I108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" t="n">
-        <v>60</v>
-      </c>
-      <c r="L108" t="n">
-        <v>5</v>
-      </c>
       <c r="M108" t="n">
-        <v>4.33</v>
+        <v>7.24</v>
       </c>
       <c r="N108" t="n">
-        <v>260</v>
+        <v>87</v>
       </c>
       <c r="O108" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($260 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($87 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Apothic Rose 750ml</t>
+          <t>Boen Tri Appellation Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>085000021545</t>
+          <t>856184006112</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>46</v>
+        <v>170</v>
       </c>
       <c r="F109" t="n">
-        <v>15.2</v>
+        <v>16.2</v>
       </c>
       <c r="G109" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H109" t="n">
-        <v>3.8</v>
+        <v>48</v>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K109" t="n">
         <v>12</v>
@@ -7159,193 +7163,193 @@
         <v>1</v>
       </c>
       <c r="M109" t="n">
-        <v>7.24</v>
+        <v>5.44</v>
       </c>
       <c r="N109" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="O109" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($87 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($65 to next deal) - confirm; Seasonal - last year ~48/wk vs 10 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Boen Tri Appellation Pinot Noir 750ml</t>
+          <t>Barefoot Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>856184006112</t>
+          <t>018341751055</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="F110" t="n">
-        <v>16.2</v>
+        <v>16.7</v>
       </c>
       <c r="G110" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H110" t="n">
+        <v>9</v>
+      </c>
+      <c r="I110" t="n">
+        <v>2</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
         <v>48</v>
       </c>
-      <c r="I110" t="n">
-        <v>20</v>
-      </c>
-      <c r="J110" t="n">
-        <v>16</v>
-      </c>
-      <c r="K110" t="n">
-        <v>12</v>
-      </c>
       <c r="L110" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M110" t="n">
-        <v>5.44</v>
+        <v>4.42</v>
       </c>
       <c r="N110" t="n">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="O110" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($65 to next deal) - confirm; Seasonal - last year ~48/wk vs 10 now, buy ahead?</t>
+          <t>Buy-month stock-up ($212 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Barefoot Chardonnay 750ml</t>
+          <t>Quilt Red Blend 750ml</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>018341751055</t>
+          <t>859889006302</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>152</v>
+        <v>8</v>
       </c>
       <c r="F111" t="n">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="G111" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="H111" t="n">
-        <v>9</v>
+        <v>0.8</v>
       </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="L111" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>4.42</v>
+        <v>25.23</v>
       </c>
       <c r="N111" t="n">
-        <v>212</v>
+        <v>303</v>
       </c>
       <c r="O111" t="n">
-        <v>45</v>
+        <v>-5</v>
       </c>
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($212 to next deal) - confirm</t>
+          <t>Margin looks off - check retail/cost; Buy-month stock-up ($303 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Quilt Red Blend 750ml</t>
+          <t>Banshee Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>859889006302</t>
+          <t>853868006024</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="F112" t="n">
-        <v>17.1</v>
+        <v>18.4</v>
       </c>
       <c r="G112" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="H112" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -7357,64 +7361,64 @@
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>25.23</v>
+        <v>13.55</v>
       </c>
       <c r="N112" t="n">
-        <v>303</v>
+        <v>163</v>
       </c>
       <c r="O112" t="n">
-        <v>-5</v>
+        <v>41</v>
       </c>
       <c r="Q112" t="inlineStr"/>
       <c r="R112" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>Margin looks off - check retail/cost; Buy-month stock-up ($303 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($163 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Banshee Pinot Noir 750ml</t>
+          <t>Barefoot Pear Moscato 750ml</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>853868006024</t>
+          <t>085000037607</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="F113" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="G113" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H113" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K113" t="n">
         <v>12</v>
@@ -7423,64 +7427,64 @@
         <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>13.55</v>
+        <v>4.32</v>
       </c>
       <c r="N113" t="n">
-        <v>163</v>
+        <v>52</v>
       </c>
       <c r="O113" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q113" t="inlineStr"/>
       <c r="R113" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, Jun, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($163 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~8/wk vs 3 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Barefoot Pear Moscato 750ml</t>
+          <t>Stags' Leap Cabernet Sauvignon Napa 750ml</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>085000037607</t>
+          <t>089819042401</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="F114" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="G114" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J114" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K114" t="n">
         <v>12</v>
@@ -7489,61 +7493,61 @@
         <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>4.32</v>
+        <v>39.87</v>
       </c>
       <c r="N114" t="n">
-        <v>52</v>
+        <v>478</v>
       </c>
       <c r="O114" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~8/wk vs 3 now, buy ahead?</t>
+          <t>Buy-month stock-up ($478 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Stags' Leap Cabernet Sauvignon Napa 750ml</t>
+          <t>Pizzolato Rosso 750ml</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>089819042401</t>
+          <t>185554000529</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Other Reds</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="F115" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -7555,193 +7559,193 @@
         <v>1</v>
       </c>
       <c r="M115" t="n">
-        <v>39.87</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="N115" t="n">
-        <v>478</v>
+        <v>109</v>
       </c>
       <c r="O115" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Mar, May, Jun, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($478 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($109 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Pizzolato Rosso 750ml</t>
+          <t>Cooks Extra Dry 1.5L</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>185554000529</t>
+          <t>083804043169</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Other Reds</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="F116" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="G116" t="n">
-        <v>4</v>
+        <v>-33</v>
       </c>
       <c r="H116" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K116" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
       </c>
       <c r="M116" t="n">
-        <v>9.119999999999999</v>
+        <v>10.33</v>
       </c>
       <c r="N116" t="n">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="O116" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="Q116" t="inlineStr"/>
       <c r="R116" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($109 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($62 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Cooks Extra Dry 1.5L</t>
+          <t>Barefoot Watermelon Moscato 750ml</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>083804043169</t>
+          <t>085000029923</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Flavored</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="F117" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="G117" t="n">
-        <v>-33</v>
+        <v>-25</v>
       </c>
       <c r="H117" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="I117" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L117" t="n">
         <v>1</v>
       </c>
       <c r="M117" t="n">
-        <v>10.33</v>
+        <v>4.31</v>
       </c>
       <c r="N117" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="O117" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($62 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Barefoot Watermelon Moscato 750ml</t>
+          <t>Pizzolato Cabernet 750ml</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>085000029923</t>
+          <t>185554000352</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Flavored</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>9</v>
+        <v>167</v>
       </c>
       <c r="F118" t="n">
-        <v>19.3</v>
+        <v>21.1</v>
       </c>
       <c r="G118" t="n">
-        <v>-25</v>
+        <v>-6</v>
       </c>
       <c r="H118" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -7753,61 +7757,61 @@
         <v>1</v>
       </c>
       <c r="M118" t="n">
-        <v>4.31</v>
+        <v>3.89</v>
       </c>
       <c r="N118" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="O118" t="n">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, Apr, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($52 to next deal) - confirm; Seasonal - last year ~2/wk vs 0 now, buy ahead?</t>
+          <t>Buy-month stock-up ($47 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Pizzolato Cabernet 750ml</t>
+          <t>Decoy Limited Sonoma Coast Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>185554000352</t>
+          <t>669576020784</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>167</v>
+        <v>25</v>
       </c>
       <c r="F119" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="G119" t="n">
-        <v>-6</v>
+        <v>25</v>
       </c>
       <c r="H119" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -7819,61 +7823,61 @@
         <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>3.89</v>
+        <v>11.24</v>
       </c>
       <c r="N119" t="n">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c r="O119" t="n">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="Q119" t="inlineStr"/>
       <c r="R119" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, Aug, Sep, Nov, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($47 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($135 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Decoy Limited Sonoma Coast Pinot Noir 750ml</t>
+          <t>Les Allies Brut Sparkling Rose 750ml</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>669576020784</t>
+          <t>763955408108</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Sparkling</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Maverick Beverage Co., LLC - MN</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="F120" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="G120" t="n">
-        <v>25</v>
+        <v>-5</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -7885,58 +7889,58 @@
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>11.24</v>
+        <v>5.83</v>
       </c>
       <c r="N120" t="n">
-        <v>135</v>
+        <v>70</v>
       </c>
       <c r="O120" t="n">
-        <v>57</v>
-      </c>
-      <c r="Q120" t="inlineStr"/>
-      <c r="R120" t="inlineStr">
-        <is>
-          <t>In buy-month (Mar, Apr, Jul, Aug, Oct, Nov) - stock up ~9wks to next deal</t>
-        </is>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>ON AD - weekly special (buy to 4.5w)</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($135 to next deal) - confirm</t>
+          <t>Overstocked (22 wks on hand) - confirm before buying more; Seasonal - last year ~13/wk vs 7 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Les Allies Brut Sparkling Rose 750ml</t>
+          <t>Acrobat Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>763955408108</t>
+          <t>768675085929</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sparkling</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Maverick Beverage Co., LLC - MN</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="F121" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="G121" t="n">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="H121" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I121" t="n">
         <v>2</v>
@@ -7951,61 +7955,61 @@
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>5.83</v>
+        <v>12.18</v>
       </c>
       <c r="N121" t="n">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="O121" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>ON AD - weekly special (buy to 4.5w)</t>
-        </is>
-      </c>
-      <c r="R121" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>In buy-month (Feb, Apr, May, Aug, Sep, Dec) - stock up ~4wks to next deal</t>
+        </is>
+      </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>Overstocked (22 wks on hand) - confirm before buying more; Seasonal - last year ~13/wk vs 7 now, buy ahead?</t>
+          <t>Buy-month stock-up ($146 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Acrobat Pinot Noir 750ml</t>
+          <t>Apothic Cabernet Sauv 750ml</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>768675085929</t>
+          <t>085000030967</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Cabernet</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="F122" t="n">
-        <v>21.8</v>
+        <v>25.7</v>
       </c>
       <c r="G122" t="n">
-        <v>26</v>
+        <v>-28</v>
       </c>
       <c r="H122" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I122" t="n">
         <v>3</v>
-      </c>
-      <c r="I122" t="n">
-        <v>2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -8017,193 +8021,193 @@
         <v>1</v>
       </c>
       <c r="M122" t="n">
-        <v>12.18</v>
+        <v>7.28</v>
       </c>
       <c r="N122" t="n">
-        <v>146</v>
+        <v>87</v>
       </c>
       <c r="O122" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, Apr, May, Aug, Sep, Dec) - stock up ~4wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($146 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($87 to next deal) - confirm; Seasonal - last year ~8/wk vs 5 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Apothic Cabernet Sauv 750ml</t>
+          <t>Belle Glos Dairyman Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>085000030967</t>
+          <t>855622000811</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Cabernet</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="F123" t="n">
         <v>25.7</v>
       </c>
       <c r="G123" t="n">
-        <v>-28</v>
+        <v>-5</v>
       </c>
       <c r="H123" t="n">
-        <v>7.8</v>
+        <v>1.2</v>
       </c>
       <c r="I123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
       </c>
       <c r="K123" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M123" t="n">
-        <v>7.28</v>
+        <v>31.9</v>
       </c>
       <c r="N123" t="n">
-        <v>87</v>
+        <v>766</v>
       </c>
       <c r="O123" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="Q123" t="inlineStr"/>
       <c r="R123" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($87 to next deal) - confirm; Seasonal - last year ~8/wk vs 5 now, buy ahead?</t>
+          <t>Buy-month stock-up ($766 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Belle Glos Dairyman Pinot Noir 750ml</t>
+          <t>Barefoot Bright &amp; Breezy Pinot Grigio 750ml</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>855622000811</t>
+          <t>085000032879</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Pinot Grigio/Gris</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F124" t="n">
-        <v>25.7</v>
+        <v>27.9</v>
       </c>
       <c r="G124" t="n">
-        <v>-5</v>
+        <v>6</v>
       </c>
       <c r="H124" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>31.9</v>
+        <v>4.5</v>
       </c>
       <c r="N124" t="n">
-        <v>766</v>
+        <v>54</v>
       </c>
       <c r="O124" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($766 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($54 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Barefoot Bright &amp; Breezy Pinot Grigio 750ml</t>
+          <t>Quilt Threadcount Red Blend 750ml</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>085000032879</t>
+          <t>860009046009</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Pinot Grigio/Gris</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F125" t="n">
-        <v>27.9</v>
+        <v>32.1</v>
       </c>
       <c r="G125" t="n">
-        <v>6</v>
+        <v>-40</v>
       </c>
       <c r="H125" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="I125" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -8215,61 +8219,61 @@
         <v>1</v>
       </c>
       <c r="M125" t="n">
-        <v>4.5</v>
+        <v>13.38</v>
       </c>
       <c r="N125" t="n">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="O125" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="Q125" t="inlineStr"/>
       <c r="R125" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Apr, Jun, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($54 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($161 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Quilt Threadcount Red Blend 750ml</t>
+          <t>Apothic Merlot 750ml</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>860009046009</t>
+          <t>085000032145</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Merlot</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Oxford Street Merchants</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>30</v>
+        <v>135</v>
       </c>
       <c r="F126" t="n">
-        <v>32.1</v>
+        <v>34</v>
       </c>
       <c r="G126" t="n">
-        <v>-40</v>
+        <v>2</v>
       </c>
       <c r="H126" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -8281,35 +8285,35 @@
         <v>1</v>
       </c>
       <c r="M126" t="n">
-        <v>13.38</v>
+        <v>7.37</v>
       </c>
       <c r="N126" t="n">
-        <v>161</v>
+        <v>88</v>
       </c>
       <c r="O126" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="Q126" t="inlineStr"/>
       <c r="R126" t="inlineStr">
         <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($161 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Apothic Merlot 750ml</t>
+          <t>Charles Smith Velvet Devil Merlot 750ml</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>085000032145</t>
+          <t>083120015055</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8319,23 +8323,23 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="F127" t="n">
-        <v>34</v>
+        <v>34.9</v>
       </c>
       <c r="G127" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="H127" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="I127" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -8347,18 +8351,18 @@
         <v>1</v>
       </c>
       <c r="M127" t="n">
-        <v>7.37</v>
+        <v>7.29</v>
       </c>
       <c r="N127" t="n">
         <v>88</v>
       </c>
       <c r="O127" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q127" t="inlineStr"/>
       <c r="R127" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~13wks to next deal</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
@@ -8370,38 +8374,38 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Charles Smith Velvet Devil Merlot 750ml</t>
+          <t>Apothic Dark 750ml</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>083120015055</t>
+          <t>085000022863</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Merlot</t>
+          <t>Red Blends</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Southern Glazer's Wine &amp; Spirits of MN</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106</v>
+        <v>26.75</v>
       </c>
       <c r="F128" t="n">
-        <v>34.9</v>
+        <v>38.2</v>
       </c>
       <c r="G128" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H128" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -8413,18 +8417,18 @@
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>7.29</v>
+        <v>7.37</v>
       </c>
       <c r="N128" t="n">
         <v>88</v>
       </c>
       <c r="O128" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="Q128" t="inlineStr"/>
       <c r="R128" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Jul, Aug, Nov) - stock up ~13wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
@@ -8436,17 +8440,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Apothic Dark 750ml</t>
+          <t>Apothic Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>085000022863</t>
+          <t>085000035405</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Red Blends</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8455,19 +8459,19 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>26.75</v>
+        <v>39</v>
       </c>
       <c r="F129" t="n">
-        <v>38.2</v>
+        <v>41.8</v>
       </c>
       <c r="G129" t="n">
-        <v>-10</v>
+        <v>20</v>
       </c>
       <c r="H129" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="I129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -8479,10 +8483,10 @@
         <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>7.37</v>
+        <v>7.69</v>
       </c>
       <c r="N129" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="O129" t="n">
         <v>38</v>
@@ -8495,19 +8499,19 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($88 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Apothic Chardonnay 750ml</t>
+          <t>Harken Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>085000035405</t>
+          <t>847159001812</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8517,26 +8521,26 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>39</v>
+        <v>231</v>
       </c>
       <c r="F130" t="n">
-        <v>41.8</v>
+        <v>45</v>
       </c>
       <c r="G130" t="n">
-        <v>20</v>
+        <v>-7</v>
       </c>
       <c r="H130" t="n">
-        <v>1.5</v>
+        <v>31</v>
       </c>
       <c r="I130" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K130" t="n">
         <v>12</v>
@@ -8545,64 +8549,64 @@
         <v>1</v>
       </c>
       <c r="M130" t="n">
-        <v>7.69</v>
+        <v>5.9</v>
       </c>
       <c r="N130" t="n">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="O130" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="Q130" t="inlineStr"/>
       <c r="R130" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Jan, Mar, Jul, Aug) - stock up ~22wks to next deal</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($92 to next deal) - confirm</t>
+          <t>Buy-month stock-up ($71 to next deal) - confirm; Seasonal - last year ~31/wk vs 5 now, buy ahead?</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Harken Chardonnay 750ml</t>
+          <t>Apothic Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>847159001812</t>
+          <t>085000032336</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chardonnay</t>
+          <t>Pinot Noir</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Breakthru Beverage Minnesota Wine &amp; Spirits, LLC</t>
+          <t>Johnson Brothers - St. Paul</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>231</v>
+        <v>144</v>
       </c>
       <c r="F131" t="n">
-        <v>45</v>
+        <v>56.1</v>
       </c>
       <c r="G131" t="n">
-        <v>-7</v>
+        <v>-31</v>
       </c>
       <c r="H131" t="n">
-        <v>31</v>
+        <v>3.2</v>
       </c>
       <c r="I131" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
         <v>12</v>
@@ -8611,61 +8615,61 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>5.9</v>
+        <v>7.14</v>
       </c>
       <c r="N131" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="O131" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr">
         <is>
-          <t>In buy-month (Jan, Mar, Jul, Aug) - stock up ~22wks to next deal</t>
+          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>Buy-month stock-up ($71 to next deal) - confirm; Seasonal - last year ~31/wk vs 5 now, buy ahead?</t>
+          <t>Buy-month stock-up ($86 to next deal) - confirm</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Apothic Pinot Noir 750ml</t>
+          <t>Quilt Napa Chardonnay 750ml</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>085000032336</t>
+          <t>859889006210</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Pinot Noir</t>
+          <t>Chardonnay</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Johnson Brothers - St. Paul</t>
+          <t>Oxford Street Merchants</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="F132" t="n">
-        <v>56.1</v>
+        <v>61.1</v>
       </c>
       <c r="G132" t="n">
-        <v>-31</v>
+        <v>-54</v>
       </c>
       <c r="H132" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -8677,87 +8681,21 @@
         <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>7.14</v>
+        <v>21.22</v>
       </c>
       <c r="N132" t="n">
-        <v>86</v>
+        <v>255</v>
       </c>
       <c r="O132" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr">
         <is>
-          <t>In buy-month (Feb, May, Aug, Oct, Dec) - stock up ~9wks to next deal</t>
+          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
-        <is>
-          <t>Buy-month stock-up ($86 to next deal) - confirm</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Quilt Napa Chardonnay 750ml</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>859889006210</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Chardonnay</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Oxford Street Merchants</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
-        <v>57</v>
-      </c>
-      <c r="F133" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="G133" t="n">
-        <v>-54</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I133" t="n">
-        <v>2</v>
-      </c>
-      <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="n">
-        <v>12</v>
-      </c>
-      <c r="L133" t="n">
-        <v>1</v>
-      </c>
-      <c r="M133" t="n">
-        <v>21.22</v>
-      </c>
-      <c r="N133" t="n">
-        <v>255</v>
-      </c>
-      <c r="O133" t="n">
-        <v>32</v>
-      </c>
-      <c r="Q133" t="inlineStr"/>
-      <c r="R133" t="inlineStr">
-        <is>
-          <t>In buy-month (Apr, Jun, Aug) - stock up ~35wks to next deal</t>
-        </is>
-      </c>
-      <c r="S133" t="inlineStr">
         <is>
           <t>Buy-month stock-up ($255 to next deal) - confirm</t>
         </is>
